--- a/research/traditional_assets/database/data/indonesia/indonesia_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_software_entertainment.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-104</v>
+        <v>-0.4694776589049717</v>
       </c>
       <c r="H2">
-        <v>-104</v>
+        <v>-0.4694776589049717</v>
       </c>
       <c r="I2">
-        <v>-107.5</v>
+        <v>-0.551604782882316</v>
       </c>
       <c r="J2">
-        <v>-107.5</v>
+        <v>-0.551604782882316</v>
       </c>
       <c r="K2">
-        <v>-0.417</v>
+        <v>-1.937</v>
       </c>
       <c r="L2">
-        <v>-104.25</v>
+        <v>-0.6095028319697924</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.78</v>
+        <v>0.541</v>
       </c>
       <c r="V2">
-        <v>0.2</v>
+        <v>0.06078651685393258</v>
       </c>
       <c r="W2">
-        <v>-0.4508108108108108</v>
+        <v>-0.7519792813532179</v>
       </c>
       <c r="X2">
-        <v>0.09038695922993849</v>
+        <v>0.1828273676106642</v>
       </c>
       <c r="Y2">
-        <v>-0.5411977700407492</v>
+        <v>-0.9348066489638821</v>
       </c>
       <c r="Z2">
-        <v>0.005305039787798408</v>
+        <v>1.092471639738742</v>
       </c>
       <c r="AA2">
-        <v>-0.5702917771883289</v>
+        <v>-0.6104466098854519</v>
       </c>
       <c r="AB2">
-        <v>0.09038695922993849</v>
+        <v>0.1744516030462336</v>
       </c>
       <c r="AC2">
-        <v>-0.6606787364182674</v>
+        <v>-0.7848982129316855</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.8220000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.8220000000000001</v>
       </c>
       <c r="AG2">
-        <v>-0.78</v>
+        <v>0.281</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.08455050401152026</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.4241486068111456</v>
       </c>
       <c r="AJ2">
-        <v>-0.25</v>
+        <v>0.03060668772464873</v>
       </c>
       <c r="AK2">
-        <v>-0.6724137931034484</v>
+        <v>0.2011453113815319</v>
       </c>
       <c r="AL2">
-        <v>0.002</v>
+        <v>0.093</v>
       </c>
       <c r="AM2">
-        <v>-0.006999999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>-0.4683760683760684</v>
       </c>
       <c r="AO2">
-        <v>-215</v>
+        <v>-18.8494623655914</v>
       </c>
       <c r="AP2">
-        <v>1.839622641509434</v>
+        <v>-0.1601139601139601</v>
       </c>
       <c r="AQ2">
-        <v>61.42857142857143</v>
+        <v>-19.69662921348315</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Tourindo Guide Indonesia Tbk (IDX:PGJO)</t>
+          <t>PT Arkadia Digital Media Tbk (IDX:DIGI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-104</v>
+        <v>-0.277</v>
       </c>
       <c r="H3">
-        <v>-104</v>
+        <v>-0.277</v>
       </c>
       <c r="I3">
-        <v>-107.5</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="J3">
-        <v>-107.5</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="K3">
-        <v>-0.417</v>
+        <v>-1.11</v>
       </c>
       <c r="L3">
-        <v>-104.25</v>
+        <v>-0.3700000000000001</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,198 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.78</v>
+        <v>0.023</v>
       </c>
       <c r="V3">
-        <v>0.2</v>
+        <v>0.004423076923076923</v>
       </c>
       <c r="W3">
-        <v>-0.4508108108108108</v>
+        <v>-1.077669902912621</v>
       </c>
       <c r="X3">
-        <v>0.09038695922993849</v>
+        <v>0.1915727186530134</v>
       </c>
       <c r="Y3">
-        <v>-0.5411977700407492</v>
+        <v>-1.269242621565635</v>
       </c>
       <c r="Z3">
-        <v>0.005305039787798408</v>
+        <v>1.715265866209263</v>
       </c>
       <c r="AA3">
-        <v>-0.5702917771883289</v>
+        <v>-0.5717552887364209</v>
       </c>
       <c r="AB3">
-        <v>0.09038695922993849</v>
+        <v>0.1751583654269307</v>
       </c>
       <c r="AC3">
-        <v>-0.6606787364182674</v>
+        <v>-0.7469136541633515</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AG3">
-        <v>-0.78</v>
+        <v>0.787</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.13477537437604</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.163793103448276</v>
       </c>
       <c r="AJ3">
-        <v>-0.25</v>
+        <v>0.1314514782027727</v>
       </c>
       <c r="AK3">
-        <v>-0.6724137931034484</v>
+        <v>1.169390787518574</v>
       </c>
       <c r="AL3">
+        <v>0.091</v>
+      </c>
+      <c r="AM3">
+        <v>0.091</v>
+      </c>
+      <c r="AN3">
+        <v>-0.801980198019802</v>
+      </c>
+      <c r="AO3">
+        <v>-10.98901098901099</v>
+      </c>
+      <c r="AP3">
+        <v>-0.7792079207920792</v>
+      </c>
+      <c r="AQ3">
+        <v>-10.98901098901099</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PT Tourindo Guide Indonesia Tbk (IDX:PGJO)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Software (Entertainment)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-3.713483146067416</v>
+      </c>
+      <c r="H4">
+        <v>-3.713483146067416</v>
+      </c>
+      <c r="I4">
+        <v>-4.230337078651686</v>
+      </c>
+      <c r="J4">
+        <v>-4.230337078651686</v>
+      </c>
+      <c r="K4">
+        <v>-0.827</v>
+      </c>
+      <c r="L4">
+        <v>-4.646067415730337</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.518</v>
+      </c>
+      <c r="V4">
+        <v>0.14</v>
+      </c>
+      <c r="W4">
+        <v>-0.4262886597938144</v>
+      </c>
+      <c r="X4">
+        <v>0.174082016568315</v>
+      </c>
+      <c r="Y4">
+        <v>-0.6003706763621294</v>
+      </c>
+      <c r="Z4">
+        <v>0.153448275862069</v>
+      </c>
+      <c r="AA4">
+        <v>-0.6491379310344828</v>
+      </c>
+      <c r="AB4">
+        <v>0.1737448406655366</v>
+      </c>
+      <c r="AC4">
+        <v>-0.8228827717000194</v>
+      </c>
+      <c r="AD4">
+        <v>0.012</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.012</v>
+      </c>
+      <c r="AG4">
+        <v>-0.506</v>
+      </c>
+      <c r="AH4">
+        <v>0.003232758620689655</v>
+      </c>
+      <c r="AI4">
+        <v>0.00966183574879227</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.158422041327489</v>
+      </c>
+      <c r="AK4">
+        <v>-0.6988950276243094</v>
+      </c>
+      <c r="AL4">
         <v>0.002</v>
       </c>
-      <c r="AM3">
-        <v>-0.006999999999999999</v>
-      </c>
-      <c r="AN3">
-        <v>-0</v>
-      </c>
-      <c r="AO3">
-        <v>-215</v>
-      </c>
-      <c r="AP3">
-        <v>1.839622641509434</v>
-      </c>
-      <c r="AQ3">
-        <v>61.42857142857143</v>
+      <c r="AM4">
+        <v>-0.002</v>
+      </c>
+      <c r="AN4">
+        <v>-0.01610738255033557</v>
+      </c>
+      <c r="AO4">
+        <v>-376.5</v>
+      </c>
+      <c r="AP4">
+        <v>0.6791946308724832</v>
+      </c>
+      <c r="AQ4">
+        <v>376.5</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_software_entertainment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="idx_awan" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,32 +589,35 @@
           <t>Software (Entertainment)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.131</v>
+      </c>
       <c r="G2">
-        <v>-0.4694776589049717</v>
+        <v>-0.178991140842524</v>
       </c>
       <c r="H2">
-        <v>-0.4694776589049717</v>
+        <v>-0.178991140842524</v>
       </c>
       <c r="I2">
-        <v>-0.551604782882316</v>
+        <v>-0.1348761525944676</v>
       </c>
       <c r="J2">
-        <v>-0.551604782882316</v>
+        <v>-0.112396793828723</v>
       </c>
       <c r="K2">
-        <v>-1.937</v>
+        <v>-0.958</v>
       </c>
       <c r="L2">
-        <v>-0.6095028319697924</v>
+        <v>-0.1732055686132707</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.002189485065549399</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.1691022964509395</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +629,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.162</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.541</v>
+        <v>3.193</v>
       </c>
       <c r="V2">
-        <v>0.06078651685393258</v>
+        <v>0.04315448033518043</v>
       </c>
       <c r="W2">
-        <v>-0.7519792813532179</v>
+        <v>0.02116788321167883</v>
       </c>
       <c r="X2">
-        <v>0.1828273676106642</v>
+        <v>0.1389314719362177</v>
       </c>
       <c r="Y2">
-        <v>-0.9348066489638821</v>
+        <v>-0.1177635887245388</v>
       </c>
       <c r="Z2">
-        <v>1.092471639738742</v>
+        <v>2.754482071713147</v>
       </c>
       <c r="AA2">
-        <v>-0.6104466098854519</v>
+        <v>-0.3363095238095238</v>
       </c>
       <c r="AB2">
-        <v>0.1744516030462336</v>
+        <v>0.1387908884386853</v>
       </c>
       <c r="AC2">
-        <v>-0.7848982129316855</v>
+        <v>-0.4729753465186154</v>
       </c>
       <c r="AD2">
-        <v>0.8220000000000001</v>
+        <v>0.923</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.8220000000000001</v>
+        <v>0.923</v>
       </c>
       <c r="AG2">
-        <v>0.281</v>
+        <v>-2.27</v>
       </c>
       <c r="AH2">
-        <v>0.08455050401152026</v>
+        <v>0.0123209589790824</v>
       </c>
       <c r="AI2">
-        <v>0.4241486068111456</v>
+        <v>0.1326721287911456</v>
       </c>
       <c r="AJ2">
-        <v>0.03060668772464873</v>
+        <v>-0.03165086447295036</v>
       </c>
       <c r="AK2">
-        <v>0.2011453113815319</v>
+        <v>-0.6030818278427206</v>
       </c>
       <c r="AL2">
-        <v>0.093</v>
+        <v>0.083</v>
       </c>
       <c r="AM2">
-        <v>0.089</v>
+        <v>0.03100000000000001</v>
       </c>
       <c r="AN2">
-        <v>-0.4683760683760684</v>
+        <v>-1.51063829787234</v>
       </c>
       <c r="AO2">
-        <v>-18.8494623655914</v>
+        <v>-8.987951807228916</v>
       </c>
       <c r="AP2">
-        <v>-0.1601139601139601</v>
+        <v>3.715220949263502</v>
       </c>
       <c r="AQ2">
-        <v>-19.69662921348315</v>
+        <v>-24.06451612903225</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Arkadia Digital Media Tbk (IDX:DIGI)</t>
+          <t>PT Era Digital Media Tbk (IDX:AWAN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,31 +721,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.277</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="H3">
-        <v>-0.277</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="I3">
-        <v>-0.3333333333333333</v>
+        <v>0.03172043010752688</v>
       </c>
       <c r="J3">
-        <v>-0.3333333333333333</v>
+        <v>0.01586021505376344</v>
       </c>
       <c r="K3">
-        <v>-1.11</v>
+        <v>0.029</v>
       </c>
       <c r="L3">
-        <v>-0.3700000000000001</v>
+        <v>0.01559139784946236</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.162</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.002354651162790698</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>5.586206896551724</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,79 +754,82 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.162</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.023</v>
+        <v>2.79</v>
       </c>
       <c r="V3">
-        <v>0.004423076923076923</v>
+        <v>0.04055232558139535</v>
       </c>
       <c r="W3">
-        <v>-1.077669902912621</v>
+        <v>0.02116788321167883</v>
       </c>
       <c r="X3">
-        <v>0.1915727186530134</v>
+        <v>0.1389285127540503</v>
       </c>
       <c r="Y3">
-        <v>-1.269242621565635</v>
+        <v>-0.1177606295423715</v>
       </c>
       <c r="Z3">
-        <v>1.715265866209263</v>
+        <v>2.990353697749196</v>
       </c>
       <c r="AA3">
-        <v>-0.5717552887364209</v>
+        <v>0.04742765273311896</v>
       </c>
       <c r="AB3">
-        <v>0.1751583654269307</v>
+        <v>0.1387945195489544</v>
       </c>
       <c r="AC3">
-        <v>-0.7469136541633515</v>
+        <v>-0.09136686681583547</v>
       </c>
       <c r="AD3">
-        <v>0.8100000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.8100000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="AG3">
-        <v>0.787</v>
+        <v>-2.676</v>
       </c>
       <c r="AH3">
-        <v>0.13477537437604</v>
+        <v>0.001654235714078417</v>
       </c>
       <c r="AI3">
-        <v>1.163793103448276</v>
+        <v>0.01901901901901902</v>
       </c>
       <c r="AJ3">
-        <v>0.1314514782027727</v>
+        <v>-0.04046942108765351</v>
       </c>
       <c r="AK3">
-        <v>1.169390787518574</v>
+        <v>-0.8352059925093634</v>
       </c>
       <c r="AL3">
-        <v>0.091</v>
+        <v>0.014</v>
       </c>
       <c r="AM3">
-        <v>0.091</v>
+        <v>-0.033</v>
       </c>
       <c r="AN3">
-        <v>-0.801980198019802</v>
+        <v>0.4730290456431536</v>
       </c>
       <c r="AO3">
-        <v>-10.98901098901099</v>
+        <v>4.214285714285714</v>
       </c>
       <c r="AP3">
-        <v>-0.7792079207920792</v>
+        <v>-11.10373443983403</v>
       </c>
       <c r="AQ3">
-        <v>-10.98901098901099</v>
+        <v>-1.787878787878788</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +840,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Tourindo Guide Indonesia Tbk (IDX:PGJO)</t>
+          <t>PT Arkadia Digital Media Tbk (IDX:DIGI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,23 +848,26 @@
           <t>Software (Entertainment)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.131</v>
+      </c>
       <c r="G4">
-        <v>-3.713483146067416</v>
+        <v>-0.2115492957746479</v>
       </c>
       <c r="H4">
-        <v>-3.713483146067416</v>
+        <v>-0.2115492957746479</v>
       </c>
       <c r="I4">
-        <v>-4.230337078651686</v>
+        <v>-0.06366197183098592</v>
       </c>
       <c r="J4">
-        <v>-4.230337078651686</v>
+        <v>-0.06366197183098592</v>
       </c>
       <c r="K4">
-        <v>-0.827</v>
+        <v>-0.421</v>
       </c>
       <c r="L4">
-        <v>-4.646067415730337</v>
+        <v>-0.1185915492957746</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,73 +891,8970 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.518</v>
+        <v>0.065</v>
       </c>
       <c r="V4">
+        <v>0.06132075471698113</v>
+      </c>
+      <c r="W4">
+        <v>3.660869565217391</v>
+      </c>
+      <c r="X4">
+        <v>0.1978139327536262</v>
+      </c>
+      <c r="Y4">
+        <v>3.463055632463765</v>
+      </c>
+      <c r="Z4">
+        <v>5.282738095238095</v>
+      </c>
+      <c r="AA4">
+        <v>-0.3363095238095238</v>
+      </c>
+      <c r="AB4">
+        <v>0.1366658227090916</v>
+      </c>
+      <c r="AC4">
+        <v>-0.4729753465186154</v>
+      </c>
+      <c r="AD4">
+        <v>0.802</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.802</v>
+      </c>
+      <c r="AG4">
+        <v>0.7370000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.4307196562835661</v>
+      </c>
+      <c r="AI4">
+        <v>2.823943661971831</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4101279910962716</v>
+      </c>
+      <c r="AK4">
+        <v>3.365296803652967</v>
+      </c>
+      <c r="AL4">
+        <v>0.067</v>
+      </c>
+      <c r="AM4">
+        <v>0.066</v>
+      </c>
+      <c r="AN4">
+        <v>-5.418918918918919</v>
+      </c>
+      <c r="AO4">
+        <v>-3.373134328358209</v>
+      </c>
+      <c r="AP4">
+        <v>-4.979729729729731</v>
+      </c>
+      <c r="AQ4">
+        <v>-3.424242424242424</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PT Tourindo Guide Indonesia Tbk (IDX:PGJO)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Software (Entertainment)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-5.446280991735538</v>
+      </c>
+      <c r="H5">
+        <v>-5.446280991735538</v>
+      </c>
+      <c r="I5">
+        <v>-4.785123966942148</v>
+      </c>
+      <c r="J5">
+        <v>-4.785123966942148</v>
+      </c>
+      <c r="K5">
+        <v>-0.5659999999999999</v>
+      </c>
+      <c r="L5">
+        <v>-4.677685950413223</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.338</v>
+      </c>
+      <c r="V5">
+        <v>0.08184019370460049</v>
+      </c>
+      <c r="W5">
+        <v>-0.4639344262295081</v>
+      </c>
+      <c r="X5">
+        <v>0.1389314719362177</v>
+      </c>
+      <c r="Y5">
+        <v>-0.6028658981657258</v>
+      </c>
+      <c r="Z5">
+        <v>0.1694677871148459</v>
+      </c>
+      <c r="AA5">
+        <v>-0.8109243697478992</v>
+      </c>
+      <c r="AB5">
+        <v>0.1387908884386853</v>
+      </c>
+      <c r="AC5">
+        <v>-0.9497152581865845</v>
+      </c>
+      <c r="AD5">
+        <v>0.007</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0.007</v>
+      </c>
+      <c r="AG5">
+        <v>-0.331</v>
+      </c>
+      <c r="AH5">
+        <v>0.001692047377326565</v>
+      </c>
+      <c r="AI5">
+        <v>0.01030927835051546</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.08712819162937616</v>
+      </c>
+      <c r="AK5">
+        <v>-0.9706744868035191</v>
+      </c>
+      <c r="AL5">
+        <v>0.002</v>
+      </c>
+      <c r="AM5">
+        <v>-0.002</v>
+      </c>
+      <c r="AN5">
+        <v>-0.00994318181818182</v>
+      </c>
+      <c r="AO5">
+        <v>-289.5</v>
+      </c>
+      <c r="AP5">
+        <v>0.4701704545454546</v>
+      </c>
+      <c r="AQ5">
+        <v>289.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PT Era Digital Media Tbk (IDX:AWAN)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IDX:AWAN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Software (Entertainment)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>12.4285714285714</v>
+      </c>
+      <c r="F2">
+        <v>5.72387844403026</v>
+      </c>
+      <c r="G2">
+        <v>0.473029045643154</v>
+      </c>
+      <c r="H2">
+        <v>2.8595020746888</v>
+      </c>
+      <c r="I2">
+        <v>0.00165423571407842</v>
+      </c>
+      <c r="J2">
+        <v>0.01</v>
+      </c>
+      <c r="K2">
+        <v>68.8</v>
+      </c>
+      <c r="L2">
+        <v>68.3615157993607</v>
+      </c>
+      <c r="M2">
+        <v>66.124</v>
+      </c>
+      <c r="N2">
+        <v>66.26065579936071</v>
+      </c>
+      <c r="O2">
+        <v>0.114</v>
+      </c>
+      <c r="P2">
+        <v>0.68914</v>
+      </c>
+      <c r="Q2">
+        <v>0.138794519548954</v>
+      </c>
+      <c r="R2">
+        <v>0.13858829111919</v>
+      </c>
+      <c r="S2">
+        <v>0.0579284448946194</v>
+      </c>
+      <c r="T2">
+        <v>0.039702</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.13892851275405</v>
+      </c>
+      <c r="X2">
+        <v>0.139587142544637</v>
+      </c>
+      <c r="Y2">
+        <v>1.35589980615096</v>
+      </c>
+      <c r="Z2">
+        <v>1.36481870428315</v>
+      </c>
+      <c r="AA2">
+        <v>0.114</v>
+      </c>
+      <c r="AB2">
+        <v>0.07426723704438384</v>
+      </c>
+      <c r="AC2">
+        <v>12.42857142857143</v>
+      </c>
+      <c r="AD2">
+        <v>0.114</v>
+      </c>
+      <c r="AE2">
+        <v>0.014</v>
+      </c>
+      <c r="AF2">
+        <v>0.067</v>
+      </c>
+      <c r="AG2">
+        <v>0.241</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>68.8</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.22</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.436</v>
+      </c>
+      <c r="AR2">
+        <v>0.014</v>
+      </c>
+      <c r="AS2">
+        <v>0.114</v>
+      </c>
+      <c r="AT2">
+        <v>2.79</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1387992695121169</v>
+      </c>
+      <c r="C2">
+        <v>68.91085911141465</v>
+      </c>
+      <c r="D2">
+        <v>66.12085911141465</v>
+      </c>
+      <c r="E2">
+        <v>-0.114</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.79</v>
+      </c>
+      <c r="H2">
+        <v>68.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K2">
+        <v>0.067</v>
+      </c>
+      <c r="L2">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="O2">
+        <v>0.04417111111111111</v>
+      </c>
+      <c r="P2">
+        <v>0.1566066666666667</v>
+      </c>
+      <c r="Q2">
+        <v>0.2236066666666667</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1387992695121169</v>
+      </c>
+      <c r="T2">
+        <v>1.354149646462541</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.034866</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1385882911191902</v>
+      </c>
+      <c r="C3">
+        <v>68.36151579936067</v>
+      </c>
+      <c r="D3">
+        <v>66.26065579936066</v>
+      </c>
+      <c r="E3">
+        <v>0.57514</v>
+      </c>
+      <c r="F3">
+        <v>0.68914</v>
+      </c>
+      <c r="G3">
+        <v>2.79</v>
+      </c>
+      <c r="H3">
+        <v>68.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K3">
+        <v>0.067</v>
+      </c>
+      <c r="L3">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M3">
+        <v>0.035077226</v>
+      </c>
+      <c r="N3">
+        <v>0.1657005517777778</v>
+      </c>
+      <c r="O3">
+        <v>0.03645412139111111</v>
+      </c>
+      <c r="P3">
+        <v>0.1292464303866667</v>
+      </c>
+      <c r="Q3">
+        <v>0.1962464303866667</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1395871425446366</v>
+      </c>
+      <c r="T3">
+        <v>1.364818704283155</v>
+      </c>
+      <c r="U3">
+        <v>0.0509</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.039702</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>5.723878444030261</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1390059927262636</v>
+      </c>
+      <c r="C4">
+        <v>67.39617293304376</v>
+      </c>
+      <c r="D4">
+        <v>65.98445293304376</v>
+      </c>
+      <c r="E4">
+        <v>1.26428</v>
+      </c>
+      <c r="F4">
+        <v>1.37828</v>
+      </c>
+      <c r="G4">
+        <v>2.79</v>
+      </c>
+      <c r="H4">
+        <v>68.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K4">
+        <v>0.067</v>
+      </c>
+      <c r="L4">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M4">
+        <v>0.125699136</v>
+      </c>
+      <c r="N4">
+        <v>0.07507864177777779</v>
+      </c>
+      <c r="O4">
+        <v>0.01651730119111111</v>
+      </c>
+      <c r="P4">
+        <v>0.05856134058666668</v>
+      </c>
+      <c r="Q4">
+        <v>0.1255613405866667</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1403910946186363</v>
+      </c>
+      <c r="T4">
+        <v>1.375705497977659</v>
+      </c>
+      <c r="U4">
+        <v>0.0912</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.071136</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>1.597288447374672</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1438899028928874</v>
+      </c>
+      <c r="C5">
+        <v>63.64049531479829</v>
+      </c>
+      <c r="D5">
+        <v>62.91791531479828</v>
+      </c>
+      <c r="E5">
+        <v>1.95342</v>
+      </c>
+      <c r="F5">
+        <v>2.06742</v>
+      </c>
+      <c r="G5">
+        <v>2.79</v>
+      </c>
+      <c r="H5">
+        <v>68.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K5">
+        <v>0.067</v>
+      </c>
+      <c r="L5">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M5">
+        <v>0.493699896</v>
+      </c>
+      <c r="N5">
+        <v>-0.2929221182222222</v>
+      </c>
+      <c r="O5">
+        <v>-0.06444286600888888</v>
+      </c>
+      <c r="P5">
+        <v>-0.2284792522133333</v>
+      </c>
+      <c r="Q5">
+        <v>-0.1614792522133333</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1416153224753092</v>
+      </c>
+      <c r="T5">
+        <v>1.392283496270959</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>0.08946955725328148</v>
+      </c>
+      <c r="W5">
+        <v>0.2174346697279164</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>0.406679805696734</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1458899028928874</v>
+      </c>
+      <c r="C6">
+        <v>61.77630680667273</v>
+      </c>
+      <c r="D6">
+        <v>61.74286680667273</v>
+      </c>
+      <c r="E6">
+        <v>2.64256</v>
+      </c>
+      <c r="F6">
+        <v>2.75656</v>
+      </c>
+      <c r="G6">
+        <v>2.79</v>
+      </c>
+      <c r="H6">
+        <v>68.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K6">
+        <v>0.067</v>
+      </c>
+      <c r="L6">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M6">
+        <v>0.658266528</v>
+      </c>
+      <c r="N6">
+        <v>-0.4574887502222222</v>
+      </c>
+      <c r="O6">
+        <v>-0.1006475250488889</v>
+      </c>
+      <c r="P6">
+        <v>-0.3568412251733333</v>
+      </c>
+      <c r="Q6">
+        <v>-0.2898412251733333</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1426863154177603</v>
+      </c>
+      <c r="T6">
+        <v>1.406786449357115</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>0.06710216793996111</v>
+      </c>
+      <c r="W6">
+        <v>0.2227760022959373</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>0.3050098542725506</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1478899028928874</v>
+      </c>
+      <c r="C7">
+        <v>59.95520380791022</v>
+      </c>
+      <c r="D7">
+        <v>60.61090380791022</v>
+      </c>
+      <c r="E7">
+        <v>3.331700000000001</v>
+      </c>
+      <c r="F7">
+        <v>3.4457</v>
+      </c>
+      <c r="G7">
+        <v>2.79</v>
+      </c>
+      <c r="H7">
+        <v>68.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K7">
+        <v>0.067</v>
+      </c>
+      <c r="L7">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M7">
+        <v>0.8228331600000002</v>
+      </c>
+      <c r="N7">
+        <v>-0.6220553822222223</v>
+      </c>
+      <c r="O7">
+        <v>-0.1368521840888889</v>
+      </c>
+      <c r="P7">
+        <v>-0.4852031981333335</v>
+      </c>
+      <c r="Q7">
+        <v>-0.4182031981333335</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1437798555800525</v>
+      </c>
+      <c r="T7">
+        <v>1.4215947277714</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>0.05368173435196887</v>
+      </c>
+      <c r="W7">
+        <v>0.2259808018367498</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>0.2440078834180404</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1498899028928874</v>
+      </c>
+      <c r="C8">
+        <v>58.17485925682962</v>
+      </c>
+      <c r="D8">
+        <v>59.51969925682962</v>
+      </c>
+      <c r="E8">
+        <v>4.02084</v>
+      </c>
+      <c r="F8">
+        <v>4.13484</v>
+      </c>
+      <c r="G8">
+        <v>2.79</v>
+      </c>
+      <c r="H8">
+        <v>68.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K8">
+        <v>0.067</v>
+      </c>
+      <c r="L8">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M8">
+        <v>0.9873997919999999</v>
+      </c>
+      <c r="N8">
+        <v>-0.7866220142222222</v>
+      </c>
+      <c r="O8">
+        <v>-0.1730568431288889</v>
+      </c>
+      <c r="P8">
+        <v>-0.6135651710933333</v>
+      </c>
+      <c r="Q8">
+        <v>-0.5465651710933332</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1448966625543084</v>
+      </c>
+      <c r="T8">
+        <v>1.436718075939181</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>0.04473477862664074</v>
+      </c>
+      <c r="W8">
+        <v>0.2281173348639582</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.203339902848367</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1518899028928874</v>
+      </c>
+      <c r="C9">
+        <v>56.43311070851026</v>
+      </c>
+      <c r="D9">
+        <v>58.46709070851026</v>
+      </c>
+      <c r="E9">
+        <v>4.709980000000001</v>
+      </c>
+      <c r="F9">
+        <v>4.823980000000001</v>
+      </c>
+      <c r="G9">
+        <v>2.79</v>
+      </c>
+      <c r="H9">
+        <v>68.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K9">
+        <v>0.067</v>
+      </c>
+      <c r="L9">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M9">
+        <v>1.151966424</v>
+      </c>
+      <c r="N9">
+        <v>-0.9511886462222225</v>
+      </c>
+      <c r="O9">
+        <v>-0.209261502168889</v>
+      </c>
+      <c r="P9">
+        <v>-0.7419271440533336</v>
+      </c>
+      <c r="Q9">
+        <v>-0.6749271440533335</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1460374868828493</v>
+      </c>
+      <c r="T9">
+        <v>1.452166657400893</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>0.03834409596569206</v>
+      </c>
+      <c r="W9">
+        <v>0.2296434298833927</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.1742913452986002</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1538899028928874</v>
+      </c>
+      <c r="C10">
+        <v>54.72794603147277</v>
+      </c>
+      <c r="D10">
+        <v>57.45106603147277</v>
+      </c>
+      <c r="E10">
+        <v>5.39912</v>
+      </c>
+      <c r="F10">
+        <v>5.51312</v>
+      </c>
+      <c r="G10">
+        <v>2.79</v>
+      </c>
+      <c r="H10">
+        <v>68.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K10">
+        <v>0.067</v>
+      </c>
+      <c r="L10">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M10">
+        <v>1.316533056</v>
+      </c>
+      <c r="N10">
+        <v>-1.115755278222222</v>
+      </c>
+      <c r="O10">
+        <v>-0.2454661612088889</v>
+      </c>
+      <c r="P10">
+        <v>-0.8702891170133333</v>
+      </c>
+      <c r="Q10">
+        <v>-0.8032891170133334</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1472031117402716</v>
+      </c>
+      <c r="T10">
+        <v>1.467951077590033</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>0.03355108396998056</v>
+      </c>
+      <c r="W10">
+        <v>0.2307880011479687</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.1525049271362752</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1558899028928874</v>
+      </c>
+      <c r="C11">
+        <v>53.05749057024077</v>
+      </c>
+      <c r="D11">
+        <v>56.46975057024077</v>
+      </c>
+      <c r="E11">
+        <v>6.08826</v>
+      </c>
+      <c r="F11">
+        <v>6.20226</v>
+      </c>
+      <c r="G11">
+        <v>2.79</v>
+      </c>
+      <c r="H11">
+        <v>68.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K11">
+        <v>0.067</v>
+      </c>
+      <c r="L11">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M11">
+        <v>1.481099688</v>
+      </c>
+      <c r="N11">
+        <v>-1.280321910222222</v>
+      </c>
+      <c r="O11">
+        <v>-0.2816708202488889</v>
+      </c>
+      <c r="P11">
+        <v>-0.9986510899733334</v>
+      </c>
+      <c r="Q11">
+        <v>-0.9316510899733335</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1483943547264284</v>
+      </c>
+      <c r="T11">
+        <v>1.484082408113</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0.02982318575109382</v>
+      </c>
+      <c r="W11">
+        <v>0.2316782232426388</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.1355599352322446</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1578899028928874</v>
+      </c>
+      <c r="C12">
+        <v>51.41999560145671</v>
+      </c>
+      <c r="D12">
+        <v>55.5213956014567</v>
+      </c>
+      <c r="E12">
+        <v>6.777400000000001</v>
+      </c>
+      <c r="F12">
+        <v>6.891400000000001</v>
+      </c>
+      <c r="G12">
+        <v>2.79</v>
+      </c>
+      <c r="H12">
+        <v>68.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K12">
+        <v>0.067</v>
+      </c>
+      <c r="L12">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M12">
+        <v>1.64566632</v>
+      </c>
+      <c r="N12">
+        <v>-1.444888542222223</v>
+      </c>
+      <c r="O12">
+        <v>-0.317875479288889</v>
+      </c>
+      <c r="P12">
+        <v>-1.127013062933334</v>
+      </c>
+      <c r="Q12">
+        <v>-1.060013062933334</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1496120697789443</v>
+      </c>
+      <c r="T12">
+        <v>1.500572212647589</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0.02684086717598444</v>
+      </c>
+      <c r="W12">
+        <v>0.2323904009183749</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.1220039417090202</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1598899028928874</v>
+      </c>
+      <c r="C13">
+        <v>49.81382793399595</v>
+      </c>
+      <c r="D13">
+        <v>54.60436793399595</v>
+      </c>
+      <c r="E13">
+        <v>7.46654</v>
+      </c>
+      <c r="F13">
+        <v>7.58054</v>
+      </c>
+      <c r="G13">
+        <v>2.79</v>
+      </c>
+      <c r="H13">
+        <v>68.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K13">
+        <v>0.067</v>
+      </c>
+      <c r="L13">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M13">
+        <v>1.810232952</v>
+      </c>
+      <c r="N13">
+        <v>-1.609455174222222</v>
+      </c>
+      <c r="O13">
+        <v>-0.3540801383288889</v>
+      </c>
+      <c r="P13">
+        <v>-1.255375035893333</v>
+      </c>
+      <c r="Q13">
+        <v>-1.188375035893333</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1508571492146628</v>
+      </c>
+      <c r="T13">
+        <v>1.51743257458745</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.02440078834180404</v>
+      </c>
+      <c r="W13">
+        <v>0.2329730917439772</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.1109126742809274</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1618899028928874</v>
+      </c>
+      <c r="C14">
+        <v>48.23746052296267</v>
+      </c>
+      <c r="D14">
+        <v>53.71714052296267</v>
+      </c>
+      <c r="E14">
+        <v>8.155679999999998</v>
+      </c>
+      <c r="F14">
+        <v>8.269679999999999</v>
+      </c>
+      <c r="G14">
+        <v>2.79</v>
+      </c>
+      <c r="H14">
+        <v>68.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K14">
+        <v>0.067</v>
+      </c>
+      <c r="L14">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M14">
+        <v>1.974799584</v>
+      </c>
+      <c r="N14">
+        <v>-1.774021806222222</v>
+      </c>
+      <c r="O14">
+        <v>-0.3902847973688889</v>
+      </c>
+      <c r="P14">
+        <v>-1.383737008853333</v>
+      </c>
+      <c r="Q14">
+        <v>-1.316737008853333</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.152130525910284</v>
+      </c>
+      <c r="T14">
+        <v>1.534676126571398</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.02236738931332037</v>
+      </c>
+      <c r="W14">
+        <v>0.2334586674319791</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.1016699514241834</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1638899028928874</v>
+      </c>
+      <c r="C15">
+        <v>46.68946398409464</v>
+      </c>
+      <c r="D15">
+        <v>52.85828398409464</v>
+      </c>
+      <c r="E15">
+        <v>8.84482</v>
+      </c>
+      <c r="F15">
+        <v>8.958820000000001</v>
+      </c>
+      <c r="G15">
+        <v>2.79</v>
+      </c>
+      <c r="H15">
+        <v>68.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K15">
+        <v>0.067</v>
+      </c>
+      <c r="L15">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M15">
+        <v>2.139366216</v>
+      </c>
+      <c r="N15">
+        <v>-1.938588438222223</v>
+      </c>
+      <c r="O15">
+        <v>-0.426489456408889</v>
+      </c>
+      <c r="P15">
+        <v>-1.512098981813334</v>
+      </c>
+      <c r="Q15">
+        <v>-1.445098981813334</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1534331756333907</v>
+      </c>
+      <c r="T15">
+        <v>1.55231608204923</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.02064682090460341</v>
+      </c>
+      <c r="W15">
+        <v>0.2338695391679807</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.09384918593001546</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
         <v>0.14</v>
       </c>
-      <c r="W4">
-        <v>-0.4262886597938144</v>
-      </c>
-      <c r="X4">
-        <v>0.174082016568315</v>
-      </c>
-      <c r="Y4">
-        <v>-0.6003706763621294</v>
-      </c>
-      <c r="Z4">
-        <v>0.153448275862069</v>
-      </c>
-      <c r="AA4">
-        <v>-0.6491379310344828</v>
-      </c>
-      <c r="AB4">
-        <v>0.1737448406655366</v>
-      </c>
-      <c r="AC4">
-        <v>-0.8228827717000194</v>
-      </c>
-      <c r="AD4">
-        <v>0.012</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0.012</v>
-      </c>
-      <c r="AG4">
-        <v>-0.506</v>
-      </c>
-      <c r="AH4">
-        <v>0.003232758620689655</v>
-      </c>
-      <c r="AI4">
-        <v>0.00966183574879227</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.158422041327489</v>
-      </c>
-      <c r="AK4">
-        <v>-0.6988950276243094</v>
-      </c>
-      <c r="AL4">
-        <v>0.002</v>
-      </c>
-      <c r="AM4">
-        <v>-0.002</v>
-      </c>
-      <c r="AN4">
-        <v>-0.01610738255033557</v>
-      </c>
-      <c r="AO4">
-        <v>-376.5</v>
-      </c>
-      <c r="AP4">
-        <v>0.6791946308724832</v>
-      </c>
-      <c r="AQ4">
-        <v>376.5</v>
+      <c r="B16">
+        <v>0.1658899028928874</v>
+      </c>
+      <c r="C16">
+        <v>45.16849890938914</v>
+      </c>
+      <c r="D16">
+        <v>52.02645890938914</v>
+      </c>
+      <c r="E16">
+        <v>9.53396</v>
+      </c>
+      <c r="F16">
+        <v>9.647960000000001</v>
+      </c>
+      <c r="G16">
+        <v>2.79</v>
+      </c>
+      <c r="H16">
+        <v>68.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K16">
+        <v>0.067</v>
+      </c>
+      <c r="L16">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M16">
+        <v>2.303932848000001</v>
+      </c>
+      <c r="N16">
+        <v>-2.103155070222223</v>
+      </c>
+      <c r="O16">
+        <v>-0.462694115448889</v>
+      </c>
+      <c r="P16">
+        <v>-1.640460954773334</v>
+      </c>
+      <c r="Q16">
+        <v>-1.573460954773334</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1547661195361045</v>
+      </c>
+      <c r="T16">
+        <v>1.570366269049803</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.01917204798284603</v>
+      </c>
+      <c r="W16">
+        <v>0.2342217149416964</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.08714567264930007</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1678899028928874</v>
+      </c>
+      <c r="C17">
+        <v>43.67330889705693</v>
+      </c>
+      <c r="D17">
+        <v>51.22040889705693</v>
+      </c>
+      <c r="E17">
+        <v>10.2231</v>
+      </c>
+      <c r="F17">
+        <v>10.3371</v>
+      </c>
+      <c r="G17">
+        <v>2.79</v>
+      </c>
+      <c r="H17">
+        <v>68.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K17">
+        <v>0.067</v>
+      </c>
+      <c r="L17">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M17">
+        <v>2.46849948</v>
+      </c>
+      <c r="N17">
+        <v>-2.267721702222222</v>
+      </c>
+      <c r="O17">
+        <v>-0.4988987744888889</v>
+      </c>
+      <c r="P17">
+        <v>-1.768822927733334</v>
+      </c>
+      <c r="Q17">
+        <v>-1.701822927733334</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1561304268247646</v>
+      </c>
+      <c r="T17">
+        <v>1.588841166332741</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.0178939114506563</v>
+      </c>
+      <c r="W17">
+        <v>0.2345269339455833</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.08133596113934682</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1698899028928874</v>
+      </c>
+      <c r="C18">
+        <v>42.20271421951539</v>
+      </c>
+      <c r="D18">
+        <v>50.43895421951539</v>
+      </c>
+      <c r="E18">
+        <v>10.91224</v>
+      </c>
+      <c r="F18">
+        <v>11.02624</v>
+      </c>
+      <c r="G18">
+        <v>2.79</v>
+      </c>
+      <c r="H18">
+        <v>68.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K18">
+        <v>0.067</v>
+      </c>
+      <c r="L18">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M18">
+        <v>2.633066112</v>
+      </c>
+      <c r="N18">
+        <v>-2.432288334222222</v>
+      </c>
+      <c r="O18">
+        <v>-0.5351034335288889</v>
+      </c>
+      <c r="P18">
+        <v>-1.897184900693333</v>
+      </c>
+      <c r="Q18">
+        <v>-1.830184900693333</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1575272176202975</v>
+      </c>
+      <c r="T18">
+        <v>1.607755942122417</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.01677554198499028</v>
+      </c>
+      <c r="W18">
+        <v>0.2347940005739843</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.07625246356813764</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1718899028928874</v>
+      </c>
+      <c r="C19">
+        <v>40.75560606230498</v>
+      </c>
+      <c r="D19">
+        <v>49.68098606230499</v>
+      </c>
+      <c r="E19">
+        <v>11.60138</v>
+      </c>
+      <c r="F19">
+        <v>11.71538</v>
+      </c>
+      <c r="G19">
+        <v>2.79</v>
+      </c>
+      <c r="H19">
+        <v>68.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K19">
+        <v>0.067</v>
+      </c>
+      <c r="L19">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M19">
+        <v>2.797632744</v>
+      </c>
+      <c r="N19">
+        <v>-2.596854966222223</v>
+      </c>
+      <c r="O19">
+        <v>-0.571308092568889</v>
+      </c>
+      <c r="P19">
+        <v>-2.025546873653334</v>
+      </c>
+      <c r="Q19">
+        <v>-1.958546873653334</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1589576660253613</v>
+      </c>
+      <c r="T19">
+        <v>1.627126495641964</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.01578874539763791</v>
+      </c>
+      <c r="W19">
+        <v>0.2350296475990441</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.07176702453471773</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1738899028928874</v>
+      </c>
+      <c r="C20">
+        <v>39.33094127476115</v>
+      </c>
+      <c r="D20">
+        <v>48.94546127476115</v>
+      </c>
+      <c r="E20">
+        <v>12.29052</v>
+      </c>
+      <c r="F20">
+        <v>12.40452</v>
+      </c>
+      <c r="G20">
+        <v>2.79</v>
+      </c>
+      <c r="H20">
+        <v>68.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K20">
+        <v>0.067</v>
+      </c>
+      <c r="L20">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M20">
+        <v>2.962199376</v>
+      </c>
+      <c r="N20">
+        <v>-2.761421598222222</v>
+      </c>
+      <c r="O20">
+        <v>-0.607512751608889</v>
+      </c>
+      <c r="P20">
+        <v>-2.153908846613334</v>
+      </c>
+      <c r="Q20">
+        <v>-2.086908846613333</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1604230034159145</v>
+      </c>
+      <c r="T20">
+        <v>1.646969501686378</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.01491159287554691</v>
+      </c>
+      <c r="W20">
+        <v>0.2352391116213194</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.06777996761612226</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1758899028928874</v>
+      </c>
+      <c r="C21">
+        <v>37.9277375801796</v>
+      </c>
+      <c r="D21">
+        <v>48.2313975801796</v>
+      </c>
+      <c r="E21">
+        <v>12.97966</v>
+      </c>
+      <c r="F21">
+        <v>13.09366</v>
+      </c>
+      <c r="G21">
+        <v>2.79</v>
+      </c>
+      <c r="H21">
+        <v>68.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K21">
+        <v>0.067</v>
+      </c>
+      <c r="L21">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M21">
+        <v>3.126766008</v>
+      </c>
+      <c r="N21">
+        <v>-2.925988230222222</v>
+      </c>
+      <c r="O21">
+        <v>-0.643717410648889</v>
+      </c>
+      <c r="P21">
+        <v>-2.282270819573333</v>
+      </c>
+      <c r="Q21">
+        <v>-2.215270819573333</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1619245219766048</v>
+      </c>
+      <c r="T21">
+        <v>1.667302458497321</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.01412677219788655</v>
+      </c>
+      <c r="W21">
+        <v>0.2354265267991447</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.06421260089948433</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1778899028928874</v>
+      </c>
+      <c r="C22">
+        <v>36.54506919922554</v>
+      </c>
+      <c r="D22">
+        <v>47.53786919922555</v>
+      </c>
+      <c r="E22">
+        <v>13.6688</v>
+      </c>
+      <c r="F22">
+        <v>13.7828</v>
+      </c>
+      <c r="G22">
+        <v>2.79</v>
+      </c>
+      <c r="H22">
+        <v>68.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K22">
+        <v>0.067</v>
+      </c>
+      <c r="L22">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M22">
+        <v>3.291332640000001</v>
+      </c>
+      <c r="N22">
+        <v>-3.090554862222223</v>
+      </c>
+      <c r="O22">
+        <v>-0.679922069688889</v>
+      </c>
+      <c r="P22">
+        <v>-2.410632792533334</v>
+      </c>
+      <c r="Q22">
+        <v>-2.343632792533334</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1634635785013124</v>
+      </c>
+      <c r="T22">
+        <v>1.688143739228538</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.01342043358799222</v>
+      </c>
+      <c r="W22">
+        <v>0.2355952004591875</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.06100197085451009</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1798899028928874</v>
+      </c>
+      <c r="C23">
+        <v>35.1820628455813</v>
+      </c>
+      <c r="D23">
+        <v>46.8640028455813</v>
+      </c>
+      <c r="E23">
+        <v>14.35794</v>
+      </c>
+      <c r="F23">
+        <v>14.47194</v>
+      </c>
+      <c r="G23">
+        <v>2.79</v>
+      </c>
+      <c r="H23">
+        <v>68.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K23">
+        <v>0.067</v>
+      </c>
+      <c r="L23">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M23">
+        <v>3.455899272</v>
+      </c>
+      <c r="N23">
+        <v>-3.255121494222223</v>
+      </c>
+      <c r="O23">
+        <v>-0.7161267287288889</v>
+      </c>
+      <c r="P23">
+        <v>-2.538994765493334</v>
+      </c>
+      <c r="Q23">
+        <v>-2.471994765493334</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1650415984823416</v>
+      </c>
+      <c r="T23">
+        <v>1.709512647320038</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.01278136532189735</v>
+      </c>
+      <c r="W23">
+        <v>0.2357478099611309</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.05809711509953341</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1818899028928874</v>
+      </c>
+      <c r="C24">
+        <v>33.8378940574122</v>
+      </c>
+      <c r="D24">
+        <v>46.2089740574122</v>
+      </c>
+      <c r="E24">
+        <v>15.04708</v>
+      </c>
+      <c r="F24">
+        <v>15.16108</v>
+      </c>
+      <c r="G24">
+        <v>2.79</v>
+      </c>
+      <c r="H24">
+        <v>68.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K24">
+        <v>0.067</v>
+      </c>
+      <c r="L24">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M24">
+        <v>3.620465904</v>
+      </c>
+      <c r="N24">
+        <v>-3.419688126222222</v>
+      </c>
+      <c r="O24">
+        <v>-0.7523313877688889</v>
+      </c>
+      <c r="P24">
+        <v>-2.667356738453333</v>
+      </c>
+      <c r="Q24">
+        <v>-2.600356738453333</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1666600805141665</v>
+      </c>
+      <c r="T24">
+        <v>1.731429476131833</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.01220039417090202</v>
+      </c>
+      <c r="W24">
+        <v>0.2358865458719886</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.05545633714046372</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1838899028928874</v>
+      </c>
+      <c r="C25">
+        <v>32.51178383224738</v>
+      </c>
+      <c r="D25">
+        <v>45.57200383224738</v>
+      </c>
+      <c r="E25">
+        <v>15.73622</v>
+      </c>
+      <c r="F25">
+        <v>15.85022</v>
+      </c>
+      <c r="G25">
+        <v>2.79</v>
+      </c>
+      <c r="H25">
+        <v>68.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K25">
+        <v>0.067</v>
+      </c>
+      <c r="L25">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M25">
+        <v>3.785032536</v>
+      </c>
+      <c r="N25">
+        <v>-3.584254758222222</v>
+      </c>
+      <c r="O25">
+        <v>-0.7885360468088889</v>
+      </c>
+      <c r="P25">
+        <v>-2.795718711413334</v>
+      </c>
+      <c r="Q25">
+        <v>-2.728718711413333</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1683206010403245</v>
+      </c>
+      <c r="T25">
+        <v>1.753915573224455</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.01166994225042802</v>
+      </c>
+      <c r="W25">
+        <v>0.2360132177905978</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.0530451920474001</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1858899028928874</v>
+      </c>
+      <c r="C26">
+        <v>31.20299553639618</v>
+      </c>
+      <c r="D26">
+        <v>44.95235553639618</v>
+      </c>
+      <c r="E26">
+        <v>16.42536</v>
+      </c>
+      <c r="F26">
+        <v>16.53936</v>
+      </c>
+      <c r="G26">
+        <v>2.79</v>
+      </c>
+      <c r="H26">
+        <v>68.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K26">
+        <v>0.067</v>
+      </c>
+      <c r="L26">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M26">
+        <v>3.949599168</v>
+      </c>
+      <c r="N26">
+        <v>-3.748821390222222</v>
+      </c>
+      <c r="O26">
+        <v>-0.8247407058488888</v>
+      </c>
+      <c r="P26">
+        <v>-2.924080684373333</v>
+      </c>
+      <c r="Q26">
+        <v>-2.857080684373333</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1700248194750656</v>
+      </c>
+      <c r="T26">
+        <v>1.77699340971425</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.01118369465666019</v>
+      </c>
+      <c r="W26">
+        <v>0.2361293337159896</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.05083497571209172</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1878899028928874</v>
+      </c>
+      <c r="C27">
+        <v>29.91083206312058</v>
+      </c>
+      <c r="D27">
+        <v>44.34933206312058</v>
+      </c>
+      <c r="E27">
+        <v>17.1145</v>
+      </c>
+      <c r="F27">
+        <v>17.2285</v>
+      </c>
+      <c r="G27">
+        <v>2.79</v>
+      </c>
+      <c r="H27">
+        <v>68.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K27">
+        <v>0.067</v>
+      </c>
+      <c r="L27">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M27">
+        <v>4.1141658</v>
+      </c>
+      <c r="N27">
+        <v>-3.913388022222223</v>
+      </c>
+      <c r="O27">
+        <v>-0.860945364888889</v>
+      </c>
+      <c r="P27">
+        <v>-3.052442657333334</v>
+      </c>
+      <c r="Q27">
+        <v>-2.985442657333333</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1717744837347332</v>
+      </c>
+      <c r="T27">
+        <v>1.800686655177107</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.01073634687039378</v>
+      </c>
+      <c r="W27">
+        <v>0.23623616036735</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.04880157668360807</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1898899028928874</v>
+      </c>
+      <c r="C28">
+        <v>28.63463321651371</v>
+      </c>
+      <c r="D28">
+        <v>43.76227321651371</v>
+      </c>
+      <c r="E28">
+        <v>17.80364</v>
+      </c>
+      <c r="F28">
+        <v>17.91764</v>
+      </c>
+      <c r="G28">
+        <v>2.79</v>
+      </c>
+      <c r="H28">
+        <v>68.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K28">
+        <v>0.067</v>
+      </c>
+      <c r="L28">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M28">
+        <v>4.278732432000001</v>
+      </c>
+      <c r="N28">
+        <v>-4.077954654222223</v>
+      </c>
+      <c r="O28">
+        <v>-0.8971500239288891</v>
+      </c>
+      <c r="P28">
+        <v>-3.180804630293334</v>
+      </c>
+      <c r="Q28">
+        <v>-3.113804630293334</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.173571436217635</v>
+      </c>
+      <c r="T28">
+        <v>1.825020258625446</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.01032341045230171</v>
+      </c>
+      <c r="W28">
+        <v>0.2363347695839904</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.04692459296500773</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1918899028928874</v>
+      </c>
+      <c r="C29">
+        <v>27.37377330044409</v>
+      </c>
+      <c r="D29">
+        <v>43.19055330044409</v>
+      </c>
+      <c r="E29">
+        <v>18.49278</v>
+      </c>
+      <c r="F29">
+        <v>18.60678</v>
+      </c>
+      <c r="G29">
+        <v>2.79</v>
+      </c>
+      <c r="H29">
+        <v>68.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K29">
+        <v>0.067</v>
+      </c>
+      <c r="L29">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M29">
+        <v>4.443299064000001</v>
+      </c>
+      <c r="N29">
+        <v>-4.242521286222223</v>
+      </c>
+      <c r="O29">
+        <v>-0.933354682968889</v>
+      </c>
+      <c r="P29">
+        <v>-3.309166603253334</v>
+      </c>
+      <c r="Q29">
+        <v>-3.242166603253334</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1754176202754108</v>
+      </c>
+      <c r="T29">
+        <v>1.850020536140863</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.009941061917031275</v>
+      </c>
+      <c r="W29">
+        <v>0.236426074414213</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.04518664507741488</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1938899028928874</v>
+      </c>
+      <c r="C30">
+        <v>26.12765889405383</v>
+      </c>
+      <c r="D30">
+        <v>42.63357889405383</v>
+      </c>
+      <c r="E30">
+        <v>19.18192</v>
+      </c>
+      <c r="F30">
+        <v>19.29592</v>
+      </c>
+      <c r="G30">
+        <v>2.79</v>
+      </c>
+      <c r="H30">
+        <v>68.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K30">
+        <v>0.067</v>
+      </c>
+      <c r="L30">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M30">
+        <v>4.607865696000001</v>
+      </c>
+      <c r="N30">
+        <v>-4.407087918222223</v>
+      </c>
+      <c r="O30">
+        <v>-0.9695593420088892</v>
+      </c>
+      <c r="P30">
+        <v>-3.437528576213334</v>
+      </c>
+      <c r="Q30">
+        <v>-3.370528576213334</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1773150872236804</v>
+      </c>
+      <c r="T30">
+        <v>1.875715265809486</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.009586023991423014</v>
+      </c>
+      <c r="W30">
+        <v>0.2365108574708482</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.04357283632465003</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1958899028928874</v>
+      </c>
+      <c r="C31">
+        <v>24.89572679718529</v>
+      </c>
+      <c r="D31">
+        <v>42.09078679718529</v>
+      </c>
+      <c r="E31">
+        <v>19.87106</v>
+      </c>
+      <c r="F31">
+        <v>19.98506</v>
+      </c>
+      <c r="G31">
+        <v>2.79</v>
+      </c>
+      <c r="H31">
+        <v>68.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K31">
+        <v>0.067</v>
+      </c>
+      <c r="L31">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M31">
+        <v>4.772432328000001</v>
+      </c>
+      <c r="N31">
+        <v>-4.571654550222223</v>
+      </c>
+      <c r="O31">
+        <v>-1.005764001048889</v>
+      </c>
+      <c r="P31">
+        <v>-3.565890549173334</v>
+      </c>
+      <c r="Q31">
+        <v>-3.498890549173334</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1792660039451407</v>
+      </c>
+      <c r="T31">
+        <v>1.902133790680043</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.009255471439994634</v>
+      </c>
+      <c r="W31">
+        <v>0.2365897934201293</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.04207032472724836</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1978899028928874</v>
+      </c>
+      <c r="C32">
+        <v>23.67744213078211</v>
+      </c>
+      <c r="D32">
+        <v>41.56164213078211</v>
+      </c>
+      <c r="E32">
+        <v>20.5602</v>
+      </c>
+      <c r="F32">
+        <v>20.6742</v>
+      </c>
+      <c r="G32">
+        <v>2.79</v>
+      </c>
+      <c r="H32">
+        <v>68.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K32">
+        <v>0.067</v>
+      </c>
+      <c r="L32">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M32">
+        <v>4.93699896</v>
+      </c>
+      <c r="N32">
+        <v>-4.736221182222223</v>
+      </c>
+      <c r="O32">
+        <v>-1.041968660088889</v>
+      </c>
+      <c r="P32">
+        <v>-3.694252522133334</v>
+      </c>
+      <c r="Q32">
+        <v>-3.627252522133333</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.181272661144357</v>
+      </c>
+      <c r="T32">
+        <v>1.9293071305469</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.008946955725328148</v>
+      </c>
+      <c r="W32">
+        <v>0.2366634669727917</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.04066798056967336</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1998899028928874</v>
+      </c>
+      <c r="C33">
+        <v>22.47229657879642</v>
+      </c>
+      <c r="D33">
+        <v>41.04563657879643</v>
+      </c>
+      <c r="E33">
+        <v>21.24934</v>
+      </c>
+      <c r="F33">
+        <v>21.36334</v>
+      </c>
+      <c r="G33">
+        <v>2.79</v>
+      </c>
+      <c r="H33">
+        <v>68.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K33">
+        <v>0.067</v>
+      </c>
+      <c r="L33">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M33">
+        <v>5.101565592</v>
+      </c>
+      <c r="N33">
+        <v>-4.900787814222222</v>
+      </c>
+      <c r="O33">
+        <v>-1.078173319128889</v>
+      </c>
+      <c r="P33">
+        <v>-3.822614495093333</v>
+      </c>
+      <c r="Q33">
+        <v>-3.755614495093333</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1833374823203621</v>
+      </c>
+      <c r="T33">
+        <v>1.957268103453377</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.008658344250317562</v>
+      </c>
+      <c r="W33">
+        <v>0.2367323873930242</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.03935611022871621</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2018899028928874</v>
+      </c>
+      <c r="C34">
+        <v>21.27980675945471</v>
+      </c>
+      <c r="D34">
+        <v>40.54228675945471</v>
+      </c>
+      <c r="E34">
+        <v>21.93848</v>
+      </c>
+      <c r="F34">
+        <v>22.05248</v>
+      </c>
+      <c r="G34">
+        <v>2.79</v>
+      </c>
+      <c r="H34">
+        <v>68.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K34">
+        <v>0.067</v>
+      </c>
+      <c r="L34">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M34">
+        <v>5.266132224</v>
+      </c>
+      <c r="N34">
+        <v>-5.065354446222222</v>
+      </c>
+      <c r="O34">
+        <v>-1.114377978168889</v>
+      </c>
+      <c r="P34">
+        <v>-3.950976468053333</v>
+      </c>
+      <c r="Q34">
+        <v>-3.883976468053333</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1854630335309557</v>
+      </c>
+      <c r="T34">
+        <v>1.986051457915927</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.008387770992495139</v>
+      </c>
+      <c r="W34">
+        <v>0.2367970002869922</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.03812623178406882</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2038899028928874</v>
+      </c>
+      <c r="C35">
+        <v>20.09951271491258</v>
+      </c>
+      <c r="D35">
+        <v>40.05113271491258</v>
+      </c>
+      <c r="E35">
+        <v>22.62762</v>
+      </c>
+      <c r="F35">
+        <v>22.74162</v>
+      </c>
+      <c r="G35">
+        <v>2.79</v>
+      </c>
+      <c r="H35">
+        <v>68.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K35">
+        <v>0.067</v>
+      </c>
+      <c r="L35">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M35">
+        <v>5.430698856</v>
+      </c>
+      <c r="N35">
+        <v>-5.229921078222223</v>
+      </c>
+      <c r="O35">
+        <v>-1.150582637208889</v>
+      </c>
+      <c r="P35">
+        <v>-4.079338441013333</v>
+      </c>
+      <c r="Q35">
+        <v>-4.012338441013333</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1876520340314177</v>
+      </c>
+      <c r="T35">
+        <v>2.015694016989299</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.008133596113934679</v>
+      </c>
+      <c r="W35">
+        <v>0.2368576972479924</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.03697089142697585</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2058899028928874</v>
+      </c>
+      <c r="C36">
+        <v>18.930976509379</v>
+      </c>
+      <c r="D36">
+        <v>39.571736509379</v>
+      </c>
+      <c r="E36">
+        <v>23.31676</v>
+      </c>
+      <c r="F36">
+        <v>23.43076</v>
+      </c>
+      <c r="G36">
+        <v>2.79</v>
+      </c>
+      <c r="H36">
+        <v>68.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K36">
+        <v>0.067</v>
+      </c>
+      <c r="L36">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M36">
+        <v>5.595265488000001</v>
+      </c>
+      <c r="N36">
+        <v>-5.394487710222223</v>
+      </c>
+      <c r="O36">
+        <v>-1.186787296248889</v>
+      </c>
+      <c r="P36">
+        <v>-4.207700413973334</v>
+      </c>
+      <c r="Q36">
+        <v>-4.140700413973334</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1899073678803786</v>
+      </c>
+      <c r="T36">
+        <v>2.046234835428531</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.007894372698818953</v>
+      </c>
+      <c r="W36">
+        <v>0.236914823799522</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.03588351226735886</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2078899028928874</v>
+      </c>
+      <c r="C37">
+        <v>17.77378092672902</v>
+      </c>
+      <c r="D37">
+        <v>39.10368092672903</v>
+      </c>
+      <c r="E37">
+        <v>24.0059</v>
+      </c>
+      <c r="F37">
+        <v>24.1199</v>
+      </c>
+      <c r="G37">
+        <v>2.79</v>
+      </c>
+      <c r="H37">
+        <v>68.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K37">
+        <v>0.067</v>
+      </c>
+      <c r="L37">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M37">
+        <v>5.75983212</v>
+      </c>
+      <c r="N37">
+        <v>-5.559054342222223</v>
+      </c>
+      <c r="O37">
+        <v>-1.222991955288889</v>
+      </c>
+      <c r="P37">
+        <v>-4.336062386933333</v>
+      </c>
+      <c r="Q37">
+        <v>-4.269062386933333</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1922320966169998</v>
+      </c>
+      <c r="T37">
+        <v>2.077715371358201</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.007668819193138412</v>
+      </c>
+      <c r="W37">
+        <v>0.2369686859766786</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.03485826905972</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2098899028928874</v>
+      </c>
+      <c r="C38">
+        <v>16.62752825946413</v>
+      </c>
+      <c r="D38">
+        <v>38.64656825946413</v>
+      </c>
+      <c r="E38">
+        <v>24.69504</v>
+      </c>
+      <c r="F38">
+        <v>24.80904</v>
+      </c>
+      <c r="G38">
+        <v>2.79</v>
+      </c>
+      <c r="H38">
+        <v>68.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K38">
+        <v>0.067</v>
+      </c>
+      <c r="L38">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M38">
+        <v>5.924398752</v>
+      </c>
+      <c r="N38">
+        <v>-5.723620974222222</v>
+      </c>
+      <c r="O38">
+        <v>-1.259196614328889</v>
+      </c>
+      <c r="P38">
+        <v>-4.464424359893334</v>
+      </c>
+      <c r="Q38">
+        <v>-4.397424359893334</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1946294731266404</v>
+      </c>
+      <c r="T38">
+        <v>2.110179674035672</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.007455796437773456</v>
+      </c>
+      <c r="W38">
+        <v>0.2370195558106597</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.03388998380806119</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2118899028928874</v>
+      </c>
+      <c r="C39">
+        <v>15.49183918163169</v>
+      </c>
+      <c r="D39">
+        <v>38.20001918163169</v>
+      </c>
+      <c r="E39">
+        <v>25.38418</v>
+      </c>
+      <c r="F39">
+        <v>25.49818</v>
+      </c>
+      <c r="G39">
+        <v>2.79</v>
+      </c>
+      <c r="H39">
+        <v>68.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K39">
+        <v>0.067</v>
+      </c>
+      <c r="L39">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M39">
+        <v>6.088965384000001</v>
+      </c>
+      <c r="N39">
+        <v>-5.888187606222223</v>
+      </c>
+      <c r="O39">
+        <v>-1.295401273368889</v>
+      </c>
+      <c r="P39">
+        <v>-4.592786332853334</v>
+      </c>
+      <c r="Q39">
+        <v>-4.525786332853333</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1971029568270633</v>
+      </c>
+      <c r="T39">
+        <v>2.143674589496556</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.00725428842594174</v>
+      </c>
+      <c r="W39">
+        <v>0.2370676759238851</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.03297403829973522</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2138899028928874</v>
+      </c>
+      <c r="C40">
+        <v>14.36635169899014</v>
+      </c>
+      <c r="D40">
+        <v>37.76367169899014</v>
+      </c>
+      <c r="E40">
+        <v>26.07332</v>
+      </c>
+      <c r="F40">
+        <v>26.18732</v>
+      </c>
+      <c r="G40">
+        <v>2.79</v>
+      </c>
+      <c r="H40">
+        <v>68.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K40">
+        <v>0.067</v>
+      </c>
+      <c r="L40">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M40">
+        <v>6.253532016</v>
+      </c>
+      <c r="N40">
+        <v>-6.052754238222223</v>
+      </c>
+      <c r="O40">
+        <v>-1.331605932408889</v>
+      </c>
+      <c r="P40">
+        <v>-4.721148305813333</v>
+      </c>
+      <c r="Q40">
+        <v>-4.654148305813333</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.199656230324274</v>
+      </c>
+      <c r="T40">
+        <v>2.178249986101339</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.007063386098943275</v>
+      </c>
+      <c r="W40">
+        <v>0.2371132633995723</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.03210630044974216</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2158899028928874</v>
+      </c>
+      <c r="C41">
+        <v>13.25072017031353</v>
+      </c>
+      <c r="D41">
+        <v>37.33718017031353</v>
+      </c>
+      <c r="E41">
+        <v>26.76246</v>
+      </c>
+      <c r="F41">
+        <v>26.87646</v>
+      </c>
+      <c r="G41">
+        <v>2.79</v>
+      </c>
+      <c r="H41">
+        <v>68.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K41">
+        <v>0.067</v>
+      </c>
+      <c r="L41">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M41">
+        <v>6.418098648000001</v>
+      </c>
+      <c r="N41">
+        <v>-6.217320870222223</v>
+      </c>
+      <c r="O41">
+        <v>-1.367810591448889</v>
+      </c>
+      <c r="P41">
+        <v>-4.849510278773334</v>
+      </c>
+      <c r="Q41">
+        <v>-4.782510278773334</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2022932177066391</v>
+      </c>
+      <c r="T41">
+        <v>2.213959002266935</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.006882273634867805</v>
+      </c>
+      <c r="W41">
+        <v>0.2371565130559936</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.03128306197667186</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2178899028928874</v>
+      </c>
+      <c r="C42">
+        <v>12.14461439427371</v>
+      </c>
+      <c r="D42">
+        <v>36.92021439427371</v>
+      </c>
+      <c r="E42">
+        <v>27.4516</v>
+      </c>
+      <c r="F42">
+        <v>27.5656</v>
+      </c>
+      <c r="G42">
+        <v>2.79</v>
+      </c>
+      <c r="H42">
+        <v>68.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K42">
+        <v>0.067</v>
+      </c>
+      <c r="L42">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M42">
+        <v>6.582665280000001</v>
+      </c>
+      <c r="N42">
+        <v>-6.381887502222224</v>
+      </c>
+      <c r="O42">
+        <v>-1.404015250488889</v>
+      </c>
+      <c r="P42">
+        <v>-4.977872251733334</v>
+      </c>
+      <c r="Q42">
+        <v>-4.910872251733334</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2050181046684165</v>
+      </c>
+      <c r="T42">
+        <v>2.250858318971384</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.006710216793996109</v>
+      </c>
+      <c r="W42">
+        <v>0.2371976002295937</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.03050098542725499</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2198899028928874</v>
+      </c>
+      <c r="C43">
+        <v>11.0477187568309</v>
+      </c>
+      <c r="D43">
+        <v>36.5124587568309</v>
+      </c>
+      <c r="E43">
+        <v>28.14074</v>
+      </c>
+      <c r="F43">
+        <v>28.25474</v>
+      </c>
+      <c r="G43">
+        <v>2.79</v>
+      </c>
+      <c r="H43">
+        <v>68.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K43">
+        <v>0.067</v>
+      </c>
+      <c r="L43">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M43">
+        <v>6.747231912000001</v>
+      </c>
+      <c r="N43">
+        <v>-6.546454134222223</v>
+      </c>
+      <c r="O43">
+        <v>-1.440219909528889</v>
+      </c>
+      <c r="P43">
+        <v>-5.106234224693334</v>
+      </c>
+      <c r="Q43">
+        <v>-5.039234224693334</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2078353606797456</v>
+      </c>
+      <c r="T43">
+        <v>2.289008459970899</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.006546552969752302</v>
+      </c>
+      <c r="W43">
+        <v>0.2372366831508232</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.02975705895341951</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2218899028928874</v>
+      </c>
+      <c r="C44">
+        <v>9.959731434505407</v>
+      </c>
+      <c r="D44">
+        <v>36.11361143450541</v>
+      </c>
+      <c r="E44">
+        <v>28.82988</v>
+      </c>
+      <c r="F44">
+        <v>28.94388</v>
+      </c>
+      <c r="G44">
+        <v>2.79</v>
+      </c>
+      <c r="H44">
+        <v>68.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K44">
+        <v>0.067</v>
+      </c>
+      <c r="L44">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M44">
+        <v>6.911798544000001</v>
+      </c>
+      <c r="N44">
+        <v>-6.711020766222223</v>
+      </c>
+      <c r="O44">
+        <v>-1.476424568568889</v>
+      </c>
+      <c r="P44">
+        <v>-5.234596197653334</v>
+      </c>
+      <c r="Q44">
+        <v>-5.167596197653333</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.210749763450086</v>
+      </c>
+      <c r="T44">
+        <v>2.328474123073845</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.006390682660948676</v>
+      </c>
+      <c r="W44">
+        <v>0.2372739049805655</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.02904855754976665</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2238899028928874</v>
+      </c>
+      <c r="C45">
+        <v>8.88036364930413</v>
+      </c>
+      <c r="D45">
+        <v>35.72338364930413</v>
+      </c>
+      <c r="E45">
+        <v>29.51902</v>
+      </c>
+      <c r="F45">
+        <v>29.63302</v>
+      </c>
+      <c r="G45">
+        <v>2.79</v>
+      </c>
+      <c r="H45">
+        <v>68.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K45">
+        <v>0.067</v>
+      </c>
+      <c r="L45">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M45">
+        <v>7.076365176000001</v>
+      </c>
+      <c r="N45">
+        <v>-6.875587398222224</v>
+      </c>
+      <c r="O45">
+        <v>-1.512629227608889</v>
+      </c>
+      <c r="P45">
+        <v>-5.362958170613334</v>
+      </c>
+      <c r="Q45">
+        <v>-5.295958170613334</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2137664259667542</v>
+      </c>
+      <c r="T45">
+        <v>2.369324546285667</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.006242062133949869</v>
+      </c>
+      <c r="W45">
+        <v>0.2373093955624128</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.02837300969977208</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2258899028928874</v>
+      </c>
+      <c r="C46">
+        <v>7.809338971436116</v>
+      </c>
+      <c r="D46">
+        <v>35.34149897143612</v>
+      </c>
+      <c r="E46">
+        <v>30.20816</v>
+      </c>
+      <c r="F46">
+        <v>30.32216</v>
+      </c>
+      <c r="G46">
+        <v>2.79</v>
+      </c>
+      <c r="H46">
+        <v>68.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K46">
+        <v>0.067</v>
+      </c>
+      <c r="L46">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M46">
+        <v>7.240931808</v>
+      </c>
+      <c r="N46">
+        <v>-7.040154030222222</v>
+      </c>
+      <c r="O46">
+        <v>-1.548833886648889</v>
+      </c>
+      <c r="P46">
+        <v>-5.491320143573334</v>
+      </c>
+      <c r="Q46">
+        <v>-5.424320143573333</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2168908264304462</v>
+      </c>
+      <c r="T46">
+        <v>2.411633913183625</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.00610019708545101</v>
+      </c>
+      <c r="W46">
+        <v>0.2373432729359943</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.02772816857023186</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2278899028928874</v>
+      </c>
+      <c r="C47">
+        <v>6.746392666279188</v>
+      </c>
+      <c r="D47">
+        <v>34.96769266627919</v>
+      </c>
+      <c r="E47">
+        <v>30.8973</v>
+      </c>
+      <c r="F47">
+        <v>31.0113</v>
+      </c>
+      <c r="G47">
+        <v>2.79</v>
+      </c>
+      <c r="H47">
+        <v>68.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K47">
+        <v>0.067</v>
+      </c>
+      <c r="L47">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M47">
+        <v>7.405498440000001</v>
+      </c>
+      <c r="N47">
+        <v>-7.204720662222223</v>
+      </c>
+      <c r="O47">
+        <v>-1.585038545688889</v>
+      </c>
+      <c r="P47">
+        <v>-5.619682116533333</v>
+      </c>
+      <c r="Q47">
+        <v>-5.552682116533333</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2201288414564543</v>
+      </c>
+      <c r="T47">
+        <v>2.455481802514237</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.005964637150218765</v>
+      </c>
+      <c r="W47">
+        <v>0.2373756446485278</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.0271119870464489</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2298899028928874</v>
+      </c>
+      <c r="C48">
+        <v>5.691271082355527</v>
+      </c>
+      <c r="D48">
+        <v>34.60171108235553</v>
+      </c>
+      <c r="E48">
+        <v>31.58644</v>
+      </c>
+      <c r="F48">
+        <v>31.70044</v>
+      </c>
+      <c r="G48">
+        <v>2.79</v>
+      </c>
+      <c r="H48">
+        <v>68.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K48">
+        <v>0.067</v>
+      </c>
+      <c r="L48">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M48">
+        <v>7.570065072</v>
+      </c>
+      <c r="N48">
+        <v>-7.369287294222223</v>
+      </c>
+      <c r="O48">
+        <v>-1.621243204728889</v>
+      </c>
+      <c r="P48">
+        <v>-5.748044089493334</v>
+      </c>
+      <c r="Q48">
+        <v>-5.681044089493334</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2234867829649071</v>
+      </c>
+      <c r="T48">
+        <v>2.500953687745981</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.005834971125214009</v>
+      </c>
+      <c r="W48">
+        <v>0.2374066088952989</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.0265225960237</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2318899028928874</v>
+      </c>
+      <c r="C49">
+        <v>4.643731077342835</v>
+      </c>
+      <c r="D49">
+        <v>34.24331107734284</v>
+      </c>
+      <c r="E49">
+        <v>32.27558000000001</v>
+      </c>
+      <c r="F49">
+        <v>32.38958</v>
+      </c>
+      <c r="G49">
+        <v>2.79</v>
+      </c>
+      <c r="H49">
+        <v>68.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K49">
+        <v>0.067</v>
+      </c>
+      <c r="L49">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M49">
+        <v>7.734631704000001</v>
+      </c>
+      <c r="N49">
+        <v>-7.533853926222223</v>
+      </c>
+      <c r="O49">
+        <v>-1.657447863768889</v>
+      </c>
+      <c r="P49">
+        <v>-5.876406062453334</v>
+      </c>
+      <c r="Q49">
+        <v>-5.809406062453334</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2269714392472639</v>
+      </c>
+      <c r="T49">
+        <v>2.548141493175151</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.005710822803400945</v>
+      </c>
+      <c r="W49">
+        <v>0.2374362555145479</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.02595828547000434</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2338899028928874</v>
+      </c>
+      <c r="C50">
+        <v>3.603539479391671</v>
+      </c>
+      <c r="D50">
+        <v>33.89225947939167</v>
+      </c>
+      <c r="E50">
+        <v>32.96472</v>
+      </c>
+      <c r="F50">
+        <v>33.07872</v>
+      </c>
+      <c r="G50">
+        <v>2.79</v>
+      </c>
+      <c r="H50">
+        <v>68.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K50">
+        <v>0.067</v>
+      </c>
+      <c r="L50">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M50">
+        <v>7.899198336</v>
+      </c>
+      <c r="N50">
+        <v>-7.698420558222222</v>
+      </c>
+      <c r="O50">
+        <v>-1.693652522808889</v>
+      </c>
+      <c r="P50">
+        <v>-6.004768035413333</v>
+      </c>
+      <c r="Q50">
+        <v>-5.937768035413333</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2305901207712498</v>
+      </c>
+      <c r="T50">
+        <v>2.59714421419775</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.005591847328330093</v>
+      </c>
+      <c r="W50">
+        <v>0.2374646668579948</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.02541748785604592</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2358899028928874</v>
+      </c>
+      <c r="C51">
+        <v>2.570472581240921</v>
+      </c>
+      <c r="D51">
+        <v>33.54833258124092</v>
+      </c>
+      <c r="E51">
+        <v>33.65386</v>
+      </c>
+      <c r="F51">
+        <v>33.76786</v>
+      </c>
+      <c r="G51">
+        <v>2.79</v>
+      </c>
+      <c r="H51">
+        <v>68.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K51">
+        <v>0.067</v>
+      </c>
+      <c r="L51">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M51">
+        <v>8.063764968000001</v>
+      </c>
+      <c r="N51">
+        <v>-7.862987190222223</v>
+      </c>
+      <c r="O51">
+        <v>-1.729857181848889</v>
+      </c>
+      <c r="P51">
+        <v>-6.133130008373334</v>
+      </c>
+      <c r="Q51">
+        <v>-6.066130008373334</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2343507113746076</v>
+      </c>
+      <c r="T51">
+        <v>2.648068610554569</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.005477727995098865</v>
+      </c>
+      <c r="W51">
+        <v>0.2374919185547704</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.02489876361408572</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2378899028928874</v>
+      </c>
+      <c r="C52">
+        <v>1.544315664825127</v>
+      </c>
+      <c r="D52">
+        <v>33.21131566482513</v>
+      </c>
+      <c r="E52">
+        <v>34.343</v>
+      </c>
+      <c r="F52">
+        <v>34.457</v>
+      </c>
+      <c r="G52">
+        <v>2.79</v>
+      </c>
+      <c r="H52">
+        <v>68.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K52">
+        <v>0.067</v>
+      </c>
+      <c r="L52">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M52">
+        <v>8.228331600000001</v>
+      </c>
+      <c r="N52">
+        <v>-8.027553822222222</v>
+      </c>
+      <c r="O52">
+        <v>-1.766061840888889</v>
+      </c>
+      <c r="P52">
+        <v>-6.261491981333333</v>
+      </c>
+      <c r="Q52">
+        <v>-6.194491981333333</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2382617256020997</v>
+      </c>
+      <c r="T52">
+        <v>2.70102998276566</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.005368173435196888</v>
+      </c>
+      <c r="W52">
+        <v>0.237518080183675</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.02440078834180415</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2398899028928874</v>
+      </c>
+      <c r="C53">
+        <v>0.5248625542507313</v>
+      </c>
+      <c r="D53">
+        <v>32.88100255425073</v>
+      </c>
+      <c r="E53">
+        <v>35.03214000000001</v>
+      </c>
+      <c r="F53">
+        <v>35.14614</v>
+      </c>
+      <c r="G53">
+        <v>2.79</v>
+      </c>
+      <c r="H53">
+        <v>68.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K53">
+        <v>0.067</v>
+      </c>
+      <c r="L53">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M53">
+        <v>8.392898232</v>
+      </c>
+      <c r="N53">
+        <v>-8.192120454222222</v>
+      </c>
+      <c r="O53">
+        <v>-1.802266499928889</v>
+      </c>
+      <c r="P53">
+        <v>-6.389853954293333</v>
+      </c>
+      <c r="Q53">
+        <v>-6.322853954293333</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2423323730633671</v>
+      </c>
+      <c r="T53">
+        <v>2.756153043638429</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.005262915132545969</v>
+      </c>
+      <c r="W53">
+        <v>0.2375432158663481</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.02392234151157269</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2418899028928874</v>
+      </c>
+      <c r="C54">
+        <v>-0.488084804814207</v>
+      </c>
+      <c r="D54">
+        <v>32.5571951951858</v>
+      </c>
+      <c r="E54">
+        <v>35.72128000000001</v>
+      </c>
+      <c r="F54">
+        <v>35.83528</v>
+      </c>
+      <c r="G54">
+        <v>2.79</v>
+      </c>
+      <c r="H54">
+        <v>68.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K54">
+        <v>0.067</v>
+      </c>
+      <c r="L54">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M54">
+        <v>8.557464864000002</v>
+      </c>
+      <c r="N54">
+        <v>-8.356687086222223</v>
+      </c>
+      <c r="O54">
+        <v>-1.838471158968889</v>
+      </c>
+      <c r="P54">
+        <v>-6.518215927253334</v>
+      </c>
+      <c r="Q54">
+        <v>-6.451215927253334</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2465726308355206</v>
+      </c>
+      <c r="T54">
+        <v>2.81357289871423</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.005161705226150853</v>
+      </c>
+      <c r="W54">
+        <v>0.2375673847919952</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.02346229648250397</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2438899028928874</v>
+      </c>
+      <c r="C55">
+        <v>-1.494716741140195</v>
+      </c>
+      <c r="D55">
+        <v>32.23970325885981</v>
+      </c>
+      <c r="E55">
+        <v>36.41042</v>
+      </c>
+      <c r="F55">
+        <v>36.52442</v>
+      </c>
+      <c r="G55">
+        <v>2.79</v>
+      </c>
+      <c r="H55">
+        <v>68.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K55">
+        <v>0.067</v>
+      </c>
+      <c r="L55">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M55">
+        <v>8.722031496</v>
+      </c>
+      <c r="N55">
+        <v>-8.521253718222221</v>
+      </c>
+      <c r="O55">
+        <v>-1.874675818008889</v>
+      </c>
+      <c r="P55">
+        <v>-6.646577900213332</v>
+      </c>
+      <c r="Q55">
+        <v>-6.579577900213332</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2509933251086168</v>
+      </c>
+      <c r="T55">
+        <v>2.873436151878362</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.005064314561506499</v>
+      </c>
+      <c r="W55">
+        <v>0.2375906416827123</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.02301961164321142</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2458899028928874</v>
+      </c>
+      <c r="C56">
+        <v>-2.495216230989726</v>
+      </c>
+      <c r="D56">
+        <v>31.92834376901027</v>
+      </c>
+      <c r="E56">
+        <v>37.09956</v>
+      </c>
+      <c r="F56">
+        <v>37.21356</v>
+      </c>
+      <c r="G56">
+        <v>2.79</v>
+      </c>
+      <c r="H56">
+        <v>68.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K56">
+        <v>0.067</v>
+      </c>
+      <c r="L56">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M56">
+        <v>8.886598128000001</v>
+      </c>
+      <c r="N56">
+        <v>-8.685820350222222</v>
+      </c>
+      <c r="O56">
+        <v>-1.910880477048889</v>
+      </c>
+      <c r="P56">
+        <v>-6.774939873173333</v>
+      </c>
+      <c r="Q56">
+        <v>-6.707939873173333</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2556062234805432</v>
+      </c>
+      <c r="T56">
+        <v>2.935902155180066</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.004970530958515637</v>
+      </c>
+      <c r="W56">
+        <v>0.2376130372071065</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.02259332253870749</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2478899028928874</v>
+      </c>
+      <c r="C57">
+        <v>-3.489759249760723</v>
+      </c>
+      <c r="D57">
+        <v>31.62294075023928</v>
+      </c>
+      <c r="E57">
+        <v>37.78870000000001</v>
+      </c>
+      <c r="F57">
+        <v>37.9027</v>
+      </c>
+      <c r="G57">
+        <v>2.79</v>
+      </c>
+      <c r="H57">
+        <v>68.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K57">
+        <v>0.067</v>
+      </c>
+      <c r="L57">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M57">
+        <v>9.051164760000001</v>
+      </c>
+      <c r="N57">
+        <v>-8.850386982222222</v>
+      </c>
+      <c r="O57">
+        <v>-1.947085136088889</v>
+      </c>
+      <c r="P57">
+        <v>-6.903301846133333</v>
+      </c>
+      <c r="Q57">
+        <v>-6.836301846133333</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2604241395578887</v>
+      </c>
+      <c r="T57">
+        <v>3.001144425295179</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.004880157668360807</v>
+      </c>
+      <c r="W57">
+        <v>0.2376346183487955</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.0221825348561856</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2498899028928874</v>
+      </c>
+      <c r="C58">
+        <v>-4.478515103639673</v>
+      </c>
+      <c r="D58">
+        <v>31.32332489636033</v>
+      </c>
+      <c r="E58">
+        <v>38.47784000000001</v>
+      </c>
+      <c r="F58">
+        <v>38.59184</v>
+      </c>
+      <c r="G58">
+        <v>2.79</v>
+      </c>
+      <c r="H58">
+        <v>68.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K58">
+        <v>0.067</v>
+      </c>
+      <c r="L58">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M58">
+        <v>9.215731392000002</v>
+      </c>
+      <c r="N58">
+        <v>-9.014953614222224</v>
+      </c>
+      <c r="O58">
+        <v>-1.983289795128889</v>
+      </c>
+      <c r="P58">
+        <v>-7.031663819093334</v>
+      </c>
+      <c r="Q58">
+        <v>-6.964663819093334</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2654610518205679</v>
+      </c>
+      <c r="T58">
+        <v>3.069352253142796</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.004793011995711507</v>
+      </c>
+      <c r="W58">
+        <v>0.2376554287354241</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.02178641816232507</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2518899028928874</v>
+      </c>
+      <c r="C59">
+        <v>-5.461646742578154</v>
+      </c>
+      <c r="D59">
+        <v>31.02933325742185</v>
+      </c>
+      <c r="E59">
+        <v>39.16698000000001</v>
+      </c>
+      <c r="F59">
+        <v>39.28098000000001</v>
+      </c>
+      <c r="G59">
+        <v>2.79</v>
+      </c>
+      <c r="H59">
+        <v>68.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K59">
+        <v>0.067</v>
+      </c>
+      <c r="L59">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M59">
+        <v>9.380298024000002</v>
+      </c>
+      <c r="N59">
+        <v>-9.179520246222223</v>
+      </c>
+      <c r="O59">
+        <v>-2.019494454168889</v>
+      </c>
+      <c r="P59">
+        <v>-7.160025792053334</v>
+      </c>
+      <c r="Q59">
+        <v>-7.093025792053334</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2707322390722091</v>
+      </c>
+      <c r="T59">
+        <v>3.140732538099606</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.004708924065962183</v>
+      </c>
+      <c r="W59">
+        <v>0.2376755089330483</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.02140420029982815</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2538899028928874</v>
+      </c>
+      <c r="C60">
+        <v>-6.439311055807991</v>
+      </c>
+      <c r="D60">
+        <v>30.74080894419201</v>
+      </c>
+      <c r="E60">
+        <v>39.85612</v>
+      </c>
+      <c r="F60">
+        <v>39.97012</v>
+      </c>
+      <c r="G60">
+        <v>2.79</v>
+      </c>
+      <c r="H60">
+        <v>68.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K60">
+        <v>0.067</v>
+      </c>
+      <c r="L60">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M60">
+        <v>9.544864656000001</v>
+      </c>
+      <c r="N60">
+        <v>-9.344086878222223</v>
+      </c>
+      <c r="O60">
+        <v>-2.055699113208889</v>
+      </c>
+      <c r="P60">
+        <v>-7.288387765013334</v>
+      </c>
+      <c r="Q60">
+        <v>-7.221387765013334</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.276254435240595</v>
+      </c>
+      <c r="T60">
+        <v>3.215511884244834</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.004627735719997317</v>
+      </c>
+      <c r="W60">
+        <v>0.2376948967100647</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.02103516236362424</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2558899028928874</v>
+      </c>
+      <c r="C61">
+        <v>-7.41165915102151</v>
+      </c>
+      <c r="D61">
+        <v>30.45760084897849</v>
+      </c>
+      <c r="E61">
+        <v>40.54526</v>
+      </c>
+      <c r="F61">
+        <v>40.65926</v>
+      </c>
+      <c r="G61">
+        <v>2.79</v>
+      </c>
+      <c r="H61">
+        <v>68.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K61">
+        <v>0.067</v>
+      </c>
+      <c r="L61">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M61">
+        <v>9.709431287999999</v>
+      </c>
+      <c r="N61">
+        <v>-9.508653510222221</v>
+      </c>
+      <c r="O61">
+        <v>-2.091903772248889</v>
+      </c>
+      <c r="P61">
+        <v>-7.416749737973332</v>
+      </c>
+      <c r="Q61">
+        <v>-7.349749737973331</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.282046006831829</v>
+      </c>
+      <c r="T61">
+        <v>3.293939003372756</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.004549299521353296</v>
+      </c>
+      <c r="W61">
+        <v>0.2377136272743008</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.02067863418796956</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2578899028928874</v>
+      </c>
+      <c r="C62">
+        <v>-8.378836618260422</v>
+      </c>
+      <c r="D62">
+        <v>30.17956338173957</v>
+      </c>
+      <c r="E62">
+        <v>41.2344</v>
+      </c>
+      <c r="F62">
+        <v>41.3484</v>
+      </c>
+      <c r="G62">
+        <v>2.79</v>
+      </c>
+      <c r="H62">
+        <v>68.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K62">
+        <v>0.067</v>
+      </c>
+      <c r="L62">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M62">
+        <v>9.873997920000001</v>
+      </c>
+      <c r="N62">
+        <v>-9.673220142222222</v>
+      </c>
+      <c r="O62">
+        <v>-2.128108431288889</v>
+      </c>
+      <c r="P62">
+        <v>-7.545111710933334</v>
+      </c>
+      <c r="Q62">
+        <v>-7.478111710933334</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2881271570026247</v>
+      </c>
+      <c r="T62">
+        <v>3.376287478457075</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.004473477862664074</v>
+      </c>
+      <c r="W62">
+        <v>0.2377317334863958</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.02033399028483673</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2598899028928874</v>
+      </c>
+      <c r="C63">
+        <v>-9.340983779481725</v>
+      </c>
+      <c r="D63">
+        <v>29.90655622051828</v>
+      </c>
+      <c r="E63">
+        <v>41.92354</v>
+      </c>
+      <c r="F63">
+        <v>42.03754</v>
+      </c>
+      <c r="G63">
+        <v>2.79</v>
+      </c>
+      <c r="H63">
+        <v>68.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K63">
+        <v>0.067</v>
+      </c>
+      <c r="L63">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M63">
+        <v>10.038564552</v>
+      </c>
+      <c r="N63">
+        <v>-9.837786774222222</v>
+      </c>
+      <c r="O63">
+        <v>-2.164313090328889</v>
+      </c>
+      <c r="P63">
+        <v>-7.673473683893333</v>
+      </c>
+      <c r="Q63">
+        <v>-7.606473683893332</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.294520161028333</v>
+      </c>
+      <c r="T63">
+        <v>3.462858952263667</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.004400142159997449</v>
+      </c>
+      <c r="W63">
+        <v>0.2377492460521926</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.02000064618180664</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2618899028928874</v>
+      </c>
+      <c r="C64">
+        <v>-10.2982359246995</v>
+      </c>
+      <c r="D64">
+        <v>29.6384440753005</v>
+      </c>
+      <c r="E64">
+        <v>42.61268</v>
+      </c>
+      <c r="F64">
+        <v>42.72668</v>
+      </c>
+      <c r="G64">
+        <v>2.79</v>
+      </c>
+      <c r="H64">
+        <v>68.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K64">
+        <v>0.067</v>
+      </c>
+      <c r="L64">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M64">
+        <v>10.203131184</v>
+      </c>
+      <c r="N64">
+        <v>-10.00235340622222</v>
+      </c>
+      <c r="O64">
+        <v>-2.200517749368889</v>
+      </c>
+      <c r="P64">
+        <v>-7.801835656853333</v>
+      </c>
+      <c r="Q64">
+        <v>-7.734835656853333</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3012496389501312</v>
+      </c>
+      <c r="T64">
+        <v>3.5539868194285</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.004329172125158781</v>
+      </c>
+      <c r="W64">
+        <v>0.2377661936965121</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.01967805511435816</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2638899028928874</v>
+      </c>
+      <c r="C65">
+        <v>-11.2507235355375</v>
+      </c>
+      <c r="D65">
+        <v>29.3750964644625</v>
+      </c>
+      <c r="E65">
+        <v>43.30182000000001</v>
+      </c>
+      <c r="F65">
+        <v>43.41582</v>
+      </c>
+      <c r="G65">
+        <v>2.79</v>
+      </c>
+      <c r="H65">
+        <v>68.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K65">
+        <v>0.067</v>
+      </c>
+      <c r="L65">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M65">
+        <v>10.367697816</v>
+      </c>
+      <c r="N65">
+        <v>-10.16692003822222</v>
+      </c>
+      <c r="O65">
+        <v>-2.236722408408889</v>
+      </c>
+      <c r="P65">
+        <v>-7.930197629813334</v>
+      </c>
+      <c r="Q65">
+        <v>-7.863197629813333</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.30834287243527</v>
+      </c>
+      <c r="T65">
+        <v>3.650040517250893</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.004260455107299117</v>
+      </c>
+      <c r="W65">
+        <v>0.237782603320377</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.01936570503317792</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2658899028928874</v>
+      </c>
+      <c r="C66">
+        <v>-12.19857249696867</v>
+      </c>
+      <c r="D66">
+        <v>29.11638750303133</v>
+      </c>
+      <c r="E66">
+        <v>43.99096</v>
+      </c>
+      <c r="F66">
+        <v>44.10496</v>
+      </c>
+      <c r="G66">
+        <v>2.79</v>
+      </c>
+      <c r="H66">
+        <v>68.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K66">
+        <v>0.067</v>
+      </c>
+      <c r="L66">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M66">
+        <v>10.532264448</v>
+      </c>
+      <c r="N66">
+        <v>-10.33148667022222</v>
+      </c>
+      <c r="O66">
+        <v>-2.272927067448888</v>
+      </c>
+      <c r="P66">
+        <v>-8.058559602773332</v>
+      </c>
+      <c r="Q66">
+        <v>-7.991559602773332</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3158301744473608</v>
+      </c>
+      <c r="T66">
+        <v>3.751430531618973</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.00419388549624757</v>
+      </c>
+      <c r="W66">
+        <v>0.2377985001434961</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.01906311589203447</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2678899028928874</v>
+      </c>
+      <c r="C67">
+        <v>-13.14190429796346</v>
+      </c>
+      <c r="D67">
+        <v>28.86219570203654</v>
+      </c>
+      <c r="E67">
+        <v>44.6801</v>
+      </c>
+      <c r="F67">
+        <v>44.7941</v>
+      </c>
+      <c r="G67">
+        <v>2.79</v>
+      </c>
+      <c r="H67">
+        <v>68.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K67">
+        <v>0.067</v>
+      </c>
+      <c r="L67">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M67">
+        <v>10.69683108</v>
+      </c>
+      <c r="N67">
+        <v>-10.49605330222222</v>
+      </c>
+      <c r="O67">
+        <v>-2.309131726488889</v>
+      </c>
+      <c r="P67">
+        <v>-8.186921575733333</v>
+      </c>
+      <c r="Q67">
+        <v>-8.119921575733333</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3237453222887139</v>
+      </c>
+      <c r="T67">
+        <v>3.858614261093801</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.004129364180920684</v>
+      </c>
+      <c r="W67">
+        <v>0.2378139078335962</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.01876983718600322</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2698899028928874</v>
+      </c>
+      <c r="C68">
+        <v>-14.0808362217189</v>
+      </c>
+      <c r="D68">
+        <v>28.6124037782811</v>
+      </c>
+      <c r="E68">
+        <v>45.36924</v>
+      </c>
+      <c r="F68">
+        <v>45.48324</v>
+      </c>
+      <c r="G68">
+        <v>2.79</v>
+      </c>
+      <c r="H68">
+        <v>68.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K68">
+        <v>0.067</v>
+      </c>
+      <c r="L68">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M68">
+        <v>10.861397712</v>
+      </c>
+      <c r="N68">
+        <v>-10.66061993422222</v>
+      </c>
+      <c r="O68">
+        <v>-2.345336385528889</v>
+      </c>
+      <c r="P68">
+        <v>-8.315283548693333</v>
+      </c>
+      <c r="Q68">
+        <v>-8.248283548693333</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3321260670619114</v>
+      </c>
+      <c r="T68">
+        <v>3.972102915831854</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.00406679805696734</v>
+      </c>
+      <c r="W68">
+        <v>0.2378288486239962</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.01848544571348798</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2718899028928874</v>
+      </c>
+      <c r="C69">
+        <v>-15.01548152609436</v>
+      </c>
+      <c r="D69">
+        <v>28.36689847390565</v>
+      </c>
+      <c r="E69">
+        <v>46.05838000000001</v>
+      </c>
+      <c r="F69">
+        <v>46.17238</v>
+      </c>
+      <c r="G69">
+        <v>2.79</v>
+      </c>
+      <c r="H69">
+        <v>68.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K69">
+        <v>0.067</v>
+      </c>
+      <c r="L69">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M69">
+        <v>11.025964344</v>
+      </c>
+      <c r="N69">
+        <v>-10.82518656622222</v>
+      </c>
+      <c r="O69">
+        <v>-2.381541044568889</v>
+      </c>
+      <c r="P69">
+        <v>-8.443645521653334</v>
+      </c>
+      <c r="Q69">
+        <v>-8.376645521653334</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3410147357607572</v>
+      </c>
+      <c r="T69">
+        <v>4.092469670857062</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.00400609957850514</v>
+      </c>
+      <c r="W69">
+        <v>0.237843343420653</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.01820954353865978</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2738899028928874</v>
+      </c>
+      <c r="C70">
+        <v>-15.94594961483691</v>
+      </c>
+      <c r="D70">
+        <v>28.1255703851631</v>
+      </c>
+      <c r="E70">
+        <v>46.74752000000001</v>
+      </c>
+      <c r="F70">
+        <v>46.86152000000001</v>
+      </c>
+      <c r="G70">
+        <v>2.79</v>
+      </c>
+      <c r="H70">
+        <v>68.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K70">
+        <v>0.067</v>
+      </c>
+      <c r="L70">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M70">
+        <v>11.190530976</v>
+      </c>
+      <c r="N70">
+        <v>-10.98975319822222</v>
+      </c>
+      <c r="O70">
+        <v>-2.417745703608889</v>
+      </c>
+      <c r="P70">
+        <v>-8.572007494613334</v>
+      </c>
+      <c r="Q70">
+        <v>-8.505007494613334</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3504589462532809</v>
+      </c>
+      <c r="T70">
+        <v>4.220359348071345</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.003947186349409476</v>
+      </c>
+      <c r="W70">
+        <v>0.237857411899761</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.01794175613367954</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2758899028928874</v>
+      </c>
+      <c r="C71">
+        <v>-16.8723462001405</v>
+      </c>
+      <c r="D71">
+        <v>27.88831379985951</v>
+      </c>
+      <c r="E71">
+        <v>47.43666000000001</v>
+      </c>
+      <c r="F71">
+        <v>47.55066000000001</v>
+      </c>
+      <c r="G71">
+        <v>2.79</v>
+      </c>
+      <c r="H71">
+        <v>68.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K71">
+        <v>0.067</v>
+      </c>
+      <c r="L71">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M71">
+        <v>11.355097608</v>
+      </c>
+      <c r="N71">
+        <v>-11.15431983022222</v>
+      </c>
+      <c r="O71">
+        <v>-2.453950362648889</v>
+      </c>
+      <c r="P71">
+        <v>-8.700369467573335</v>
+      </c>
+      <c r="Q71">
+        <v>-8.633369467573335</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.360512460648548</v>
+      </c>
+      <c r="T71">
+        <v>4.356499972202679</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.003889980750142672</v>
+      </c>
+      <c r="W71">
+        <v>0.2378710725968659</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.01768173068246681</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2778899028928874</v>
+      </c>
+      <c r="C72">
+        <v>-17.79477345704614</v>
+      </c>
+      <c r="D72">
+        <v>27.65502654295387</v>
+      </c>
+      <c r="E72">
+        <v>48.12580000000001</v>
+      </c>
+      <c r="F72">
+        <v>48.2398</v>
+      </c>
+      <c r="G72">
+        <v>2.79</v>
+      </c>
+      <c r="H72">
+        <v>68.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K72">
+        <v>0.067</v>
+      </c>
+      <c r="L72">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M72">
+        <v>11.51966424</v>
+      </c>
+      <c r="N72">
+        <v>-11.31888646222222</v>
+      </c>
+      <c r="O72">
+        <v>-2.490155021688889</v>
+      </c>
+      <c r="P72">
+        <v>-8.828731440533334</v>
+      </c>
+      <c r="Q72">
+        <v>-8.761731440533334</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.371236209336833</v>
+      </c>
+      <c r="T72">
+        <v>4.501716637942768</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.003834409596569206</v>
+      </c>
+      <c r="W72">
+        <v>0.2378843429883393</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.01742913452986006</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2798899028928874</v>
+      </c>
+      <c r="C73">
+        <v>-18.71333017015701</v>
+      </c>
+      <c r="D73">
+        <v>27.42560982984298</v>
+      </c>
+      <c r="E73">
+        <v>48.81494</v>
+      </c>
+      <c r="F73">
+        <v>48.92894</v>
+      </c>
+      <c r="G73">
+        <v>2.79</v>
+      </c>
+      <c r="H73">
+        <v>68.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K73">
+        <v>0.067</v>
+      </c>
+      <c r="L73">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M73">
+        <v>11.684230872</v>
+      </c>
+      <c r="N73">
+        <v>-11.48345309422222</v>
+      </c>
+      <c r="O73">
+        <v>-2.526359680728889</v>
+      </c>
+      <c r="P73">
+        <v>-8.957093413493332</v>
+      </c>
+      <c r="Q73">
+        <v>-8.890093413493332</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3826995269001719</v>
+      </c>
+      <c r="T73">
+        <v>4.65694824614769</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.003780403827603442</v>
+      </c>
+      <c r="W73">
+        <v>0.2378972395659683</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.01718365376183395</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2818899028928874</v>
+      </c>
+      <c r="C74">
+        <v>-19.62811187311107</v>
+      </c>
+      <c r="D74">
+        <v>27.19996812688893</v>
+      </c>
+      <c r="E74">
+        <v>49.50408</v>
+      </c>
+      <c r="F74">
+        <v>49.61808</v>
+      </c>
+      <c r="G74">
+        <v>2.79</v>
+      </c>
+      <c r="H74">
+        <v>68.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K74">
+        <v>0.067</v>
+      </c>
+      <c r="L74">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M74">
+        <v>11.848797504</v>
+      </c>
+      <c r="N74">
+        <v>-11.64801972622222</v>
+      </c>
+      <c r="O74">
+        <v>-2.562564339768889</v>
+      </c>
+      <c r="P74">
+        <v>-9.085455386453333</v>
+      </c>
+      <c r="Q74">
+        <v>-9.018455386453333</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3949816528608924</v>
+      </c>
+      <c r="T74">
+        <v>4.82326782636725</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.003727898218886728</v>
+      </c>
+      <c r="W74">
+        <v>0.2379097779053299</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.01694499190403065</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2838899028928874</v>
+      </c>
+      <c r="C75">
+        <v>-20.53921098122477</v>
+      </c>
+      <c r="D75">
+        <v>26.97800901877524</v>
+      </c>
+      <c r="E75">
+        <v>50.19322</v>
+      </c>
+      <c r="F75">
+        <v>50.30722</v>
+      </c>
+      <c r="G75">
+        <v>2.79</v>
+      </c>
+      <c r="H75">
+        <v>68.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K75">
+        <v>0.067</v>
+      </c>
+      <c r="L75">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M75">
+        <v>12.013364136</v>
+      </c>
+      <c r="N75">
+        <v>-11.81258635822222</v>
+      </c>
+      <c r="O75">
+        <v>-2.598768998808889</v>
+      </c>
+      <c r="P75">
+        <v>-9.213817359413333</v>
+      </c>
+      <c r="Q75">
+        <v>-9.146817359413333</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4081735659298143</v>
+      </c>
+      <c r="T75">
+        <v>5.001907375491963</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.003676831119997868</v>
+      </c>
+      <c r="W75">
+        <v>0.2379219727285445</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.01671286872726307</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2858899028928874</v>
+      </c>
+      <c r="C76">
+        <v>-21.44671691769503</v>
+      </c>
+      <c r="D76">
+        <v>26.75964308230497</v>
+      </c>
+      <c r="E76">
+        <v>50.88236000000001</v>
+      </c>
+      <c r="F76">
+        <v>50.99636</v>
+      </c>
+      <c r="G76">
+        <v>2.79</v>
+      </c>
+      <c r="H76">
+        <v>68.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K76">
+        <v>0.067</v>
+      </c>
+      <c r="L76">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M76">
+        <v>12.177930768</v>
+      </c>
+      <c r="N76">
+        <v>-11.97715299022222</v>
+      </c>
+      <c r="O76">
+        <v>-2.634973657848889</v>
+      </c>
+      <c r="P76">
+        <v>-9.342179332373334</v>
+      </c>
+      <c r="Q76">
+        <v>-9.275179332373334</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4223802415424995</v>
+      </c>
+      <c r="T76">
+        <v>5.194288428395501</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.00362714421297087</v>
+      </c>
+      <c r="W76">
+        <v>0.2379338379619426</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.01648701914986761</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2878899028928874</v>
+      </c>
+      <c r="C77">
+        <v>-22.35071623372127</v>
+      </c>
+      <c r="D77">
+        <v>26.54478376627874</v>
+      </c>
+      <c r="E77">
+        <v>51.57150000000001</v>
+      </c>
+      <c r="F77">
+        <v>51.6855</v>
+      </c>
+      <c r="G77">
+        <v>2.79</v>
+      </c>
+      <c r="H77">
+        <v>68.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K77">
+        <v>0.067</v>
+      </c>
+      <c r="L77">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M77">
+        <v>12.3424974</v>
+      </c>
+      <c r="N77">
+        <v>-12.14171962222222</v>
+      </c>
+      <c r="O77">
+        <v>-2.671178316888889</v>
+      </c>
+      <c r="P77">
+        <v>-9.470541305333334</v>
+      </c>
+      <c r="Q77">
+        <v>-9.403541305333334</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4377234512041995</v>
+      </c>
+      <c r="T77">
+        <v>5.40205996553132</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.003578782290131259</v>
+      </c>
+      <c r="W77">
+        <v>0.2379453867891166</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.01626719222786943</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2898899028928874</v>
+      </c>
+      <c r="C78">
+        <v>-23.25129272288669</v>
+      </c>
+      <c r="D78">
+        <v>26.33334727711331</v>
+      </c>
+      <c r="E78">
+        <v>52.26064</v>
+      </c>
+      <c r="F78">
+        <v>52.37464</v>
+      </c>
+      <c r="G78">
+        <v>2.79</v>
+      </c>
+      <c r="H78">
+        <v>68.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K78">
+        <v>0.067</v>
+      </c>
+      <c r="L78">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M78">
+        <v>12.507064032</v>
+      </c>
+      <c r="N78">
+        <v>-12.30628625422222</v>
+      </c>
+      <c r="O78">
+        <v>-2.707382975928889</v>
+      </c>
+      <c r="P78">
+        <v>-9.598903278293333</v>
+      </c>
+      <c r="Q78">
+        <v>-9.531903278293333</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4543452616710412</v>
+      </c>
+      <c r="T78">
+        <v>5.62714579742846</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.003531693049471638</v>
+      </c>
+      <c r="W78">
+        <v>0.2379566316997862</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.01605315022487119</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2918899028928874</v>
+      </c>
+      <c r="C79">
+        <v>-24.14852753011618</v>
+      </c>
+      <c r="D79">
+        <v>26.12525246988382</v>
+      </c>
+      <c r="E79">
+        <v>52.94978</v>
+      </c>
+      <c r="F79">
+        <v>53.06378</v>
+      </c>
+      <c r="G79">
+        <v>2.79</v>
+      </c>
+      <c r="H79">
+        <v>68.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K79">
+        <v>0.067</v>
+      </c>
+      <c r="L79">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M79">
+        <v>12.671630664</v>
+      </c>
+      <c r="N79">
+        <v>-12.47085288622222</v>
+      </c>
+      <c r="O79">
+        <v>-2.743587634968889</v>
+      </c>
+      <c r="P79">
+        <v>-9.727265251253332</v>
+      </c>
+      <c r="Q79">
+        <v>-9.660265251253332</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4724124469610865</v>
+      </c>
+      <c r="T79">
+        <v>5.871804310360131</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.003485826905972006</v>
+      </c>
+      <c r="W79">
+        <v>0.2379675845348539</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.01584466775441828</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2938899028928874</v>
+      </c>
+      <c r="C80">
+        <v>-25.04249925550873</v>
+      </c>
+      <c r="D80">
+        <v>25.92042074449127</v>
+      </c>
+      <c r="E80">
+        <v>53.63892000000001</v>
+      </c>
+      <c r="F80">
+        <v>53.75292</v>
+      </c>
+      <c r="G80">
+        <v>2.79</v>
+      </c>
+      <c r="H80">
+        <v>68.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K80">
+        <v>0.067</v>
+      </c>
+      <c r="L80">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M80">
+        <v>12.836197296</v>
+      </c>
+      <c r="N80">
+        <v>-12.63541951822222</v>
+      </c>
+      <c r="O80">
+        <v>-2.779792294008889</v>
+      </c>
+      <c r="P80">
+        <v>-9.855627224213334</v>
+      </c>
+      <c r="Q80">
+        <v>-9.788627224213334</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4921221036411359</v>
+      </c>
+      <c r="T80">
+        <v>6.138704506285593</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.003441136817433903</v>
+      </c>
+      <c r="W80">
+        <v>0.2379782565279968</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.01564153098833598</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2958899028928874</v>
+      </c>
+      <c r="C81">
+        <v>-25.93328405332322</v>
+      </c>
+      <c r="D81">
+        <v>25.71877594667679</v>
+      </c>
+      <c r="E81">
+        <v>54.32806000000001</v>
+      </c>
+      <c r="F81">
+        <v>54.44206000000001</v>
+      </c>
+      <c r="G81">
+        <v>2.79</v>
+      </c>
+      <c r="H81">
+        <v>68.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K81">
+        <v>0.067</v>
+      </c>
+      <c r="L81">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M81">
+        <v>13.000763928</v>
+      </c>
+      <c r="N81">
+        <v>-12.79998615022222</v>
+      </c>
+      <c r="O81">
+        <v>-2.815996953048889</v>
+      </c>
+      <c r="P81">
+        <v>-9.983989197173333</v>
+      </c>
+      <c r="Q81">
+        <v>-9.916989197173333</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.51370887048119</v>
+      </c>
+      <c r="T81">
+        <v>6.431023768489668</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.003397578123542334</v>
+      </c>
+      <c r="W81">
+        <v>0.2379886583440981</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.01544353692519251</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2978899028928874</v>
+      </c>
+      <c r="C82">
+        <v>-26.82095572637965</v>
+      </c>
+      <c r="D82">
+        <v>25.52024427362036</v>
+      </c>
+      <c r="E82">
+        <v>55.01720000000001</v>
+      </c>
+      <c r="F82">
+        <v>55.13120000000001</v>
+      </c>
+      <c r="G82">
+        <v>2.79</v>
+      </c>
+      <c r="H82">
+        <v>68.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K82">
+        <v>0.067</v>
+      </c>
+      <c r="L82">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M82">
+        <v>13.16533056</v>
+      </c>
+      <c r="N82">
+        <v>-12.96455278222222</v>
+      </c>
+      <c r="O82">
+        <v>-2.852201612088889</v>
+      </c>
+      <c r="P82">
+        <v>-10.11235117013334</v>
+      </c>
+      <c r="Q82">
+        <v>-10.04535117013334</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5374543140052495</v>
+      </c>
+      <c r="T82">
+        <v>6.752574956914152</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.003355108396998055</v>
+      </c>
+      <c r="W82">
+        <v>0.2379988001147969</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.01525049271362755</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2998899028928874</v>
+      </c>
+      <c r="C83">
+        <v>-27.70558581612157</v>
+      </c>
+      <c r="D83">
+        <v>25.32475418387843</v>
+      </c>
+      <c r="E83">
+        <v>55.70634</v>
+      </c>
+      <c r="F83">
+        <v>55.82034</v>
+      </c>
+      <c r="G83">
+        <v>2.79</v>
+      </c>
+      <c r="H83">
+        <v>68.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K83">
+        <v>0.067</v>
+      </c>
+      <c r="L83">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M83">
+        <v>13.329897192</v>
+      </c>
+      <c r="N83">
+        <v>-13.12911941422222</v>
+      </c>
+      <c r="O83">
+        <v>-2.888406271128889</v>
+      </c>
+      <c r="P83">
+        <v>-10.24071314309333</v>
+      </c>
+      <c r="Q83">
+        <v>-10.17371314309333</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5636992779002628</v>
+      </c>
+      <c r="T83">
+        <v>7.107973638857003</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.003313687305677091</v>
+      </c>
+      <c r="W83">
+        <v>0.2380086914714043</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.01506221502580507</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3018899028928874</v>
+      </c>
+      <c r="C84">
+        <v>-28.58724368857059</v>
+      </c>
+      <c r="D84">
+        <v>25.13223631142942</v>
+      </c>
+      <c r="E84">
+        <v>56.39548000000001</v>
+      </c>
+      <c r="F84">
+        <v>56.50948</v>
+      </c>
+      <c r="G84">
+        <v>2.79</v>
+      </c>
+      <c r="H84">
+        <v>68.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K84">
+        <v>0.067</v>
+      </c>
+      <c r="L84">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M84">
+        <v>13.494463824</v>
+      </c>
+      <c r="N84">
+        <v>-13.29368604622222</v>
+      </c>
+      <c r="O84">
+        <v>-2.924610930168889</v>
+      </c>
+      <c r="P84">
+        <v>-10.36907511605333</v>
+      </c>
+      <c r="Q84">
+        <v>-10.30207511605333</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5928603488947217</v>
+      </c>
+      <c r="T84">
+        <v>7.502861063237947</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.003273276484876151</v>
+      </c>
+      <c r="W84">
+        <v>0.2380183415754116</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.01487852947670987</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3038899028928874</v>
+      </c>
+      <c r="C85">
+        <v>-29.46599661638991</v>
+      </c>
+      <c r="D85">
+        <v>24.9426233836101</v>
+      </c>
+      <c r="E85">
+        <v>57.08462000000001</v>
+      </c>
+      <c r="F85">
+        <v>57.19862000000001</v>
+      </c>
+      <c r="G85">
+        <v>2.79</v>
+      </c>
+      <c r="H85">
+        <v>68.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K85">
+        <v>0.067</v>
+      </c>
+      <c r="L85">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M85">
+        <v>13.659030456</v>
+      </c>
+      <c r="N85">
+        <v>-13.45825267822222</v>
+      </c>
+      <c r="O85">
+        <v>-2.960815589208889</v>
+      </c>
+      <c r="P85">
+        <v>-10.49743708901334</v>
+      </c>
+      <c r="Q85">
+        <v>-10.43043708901333</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6254521341238231</v>
+      </c>
+      <c r="T85">
+        <v>7.944205831663711</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.003233839418793306</v>
+      </c>
+      <c r="W85">
+        <v>0.2380277591467922</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.01469927008542415</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3058899028928874</v>
+      </c>
+      <c r="C86">
+        <v>-30.34190985726088</v>
+      </c>
+      <c r="D86">
+        <v>24.75585014273912</v>
+      </c>
+      <c r="E86">
+        <v>57.77376</v>
+      </c>
+      <c r="F86">
+        <v>57.88776</v>
+      </c>
+      <c r="G86">
+        <v>2.79</v>
+      </c>
+      <c r="H86">
+        <v>68.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K86">
+        <v>0.067</v>
+      </c>
+      <c r="L86">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M86">
+        <v>13.823597088</v>
+      </c>
+      <c r="N86">
+        <v>-13.62281931022222</v>
+      </c>
+      <c r="O86">
+        <v>-2.997020248248889</v>
+      </c>
+      <c r="P86">
+        <v>-10.62579906197333</v>
+      </c>
+      <c r="Q86">
+        <v>-10.55879906197333</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6621178925065616</v>
+      </c>
+      <c r="T86">
+        <v>8.440718696142687</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.003195341330474338</v>
+      </c>
+      <c r="W86">
+        <v>0.2380369524902827</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.01452427877488338</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3078899028928874</v>
+      </c>
+      <c r="C87">
+        <v>-31.21504672876441</v>
+      </c>
+      <c r="D87">
+        <v>24.57185327123559</v>
+      </c>
+      <c r="E87">
+        <v>58.4629</v>
+      </c>
+      <c r="F87">
+        <v>58.5769</v>
+      </c>
+      <c r="G87">
+        <v>2.79</v>
+      </c>
+      <c r="H87">
+        <v>68.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K87">
+        <v>0.067</v>
+      </c>
+      <c r="L87">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M87">
+        <v>13.98816372</v>
+      </c>
+      <c r="N87">
+        <v>-13.78738594222222</v>
+      </c>
+      <c r="O87">
+        <v>-3.033224907288889</v>
+      </c>
+      <c r="P87">
+        <v>-10.75416103493333</v>
+      </c>
+      <c r="Q87">
+        <v>-10.68716103493333</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.7036724186736658</v>
+      </c>
+      <c r="T87">
+        <v>9.003433275885534</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.003157749079527581</v>
+      </c>
+      <c r="W87">
+        <v>0.2380459295198088</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.01435340490694359</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3098899028928874</v>
+      </c>
+      <c r="C88">
+        <v>-32.08546867994755</v>
+      </c>
+      <c r="D88">
+        <v>24.39057132005245</v>
+      </c>
+      <c r="E88">
+        <v>59.15204000000001</v>
+      </c>
+      <c r="F88">
+        <v>59.26604</v>
+      </c>
+      <c r="G88">
+        <v>2.79</v>
+      </c>
+      <c r="H88">
+        <v>68.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K88">
+        <v>0.067</v>
+      </c>
+      <c r="L88">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M88">
+        <v>14.152730352</v>
+      </c>
+      <c r="N88">
+        <v>-13.95195257422222</v>
+      </c>
+      <c r="O88">
+        <v>-3.069429566328889</v>
+      </c>
+      <c r="P88">
+        <v>-10.88252300789333</v>
+      </c>
+      <c r="Q88">
+        <v>-10.81552300789333</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7511633057217848</v>
+      </c>
+      <c r="T88">
+        <v>9.646535652734499</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.003121031066974935</v>
+      </c>
+      <c r="W88">
+        <v>0.2380546977812064</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.01418650484988615</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3118899028928874</v>
+      </c>
+      <c r="C89">
+        <v>-32.95323535974551</v>
+      </c>
+      <c r="D89">
+        <v>24.21194464025449</v>
+      </c>
+      <c r="E89">
+        <v>59.84118</v>
+      </c>
+      <c r="F89">
+        <v>59.95518</v>
+      </c>
+      <c r="G89">
+        <v>2.79</v>
+      </c>
+      <c r="H89">
+        <v>68.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K89">
+        <v>0.067</v>
+      </c>
+      <c r="L89">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M89">
+        <v>14.317296984</v>
+      </c>
+      <c r="N89">
+        <v>-14.11651920622222</v>
+      </c>
+      <c r="O89">
+        <v>-3.105634225368889</v>
+      </c>
+      <c r="P89">
+        <v>-11.01088498085333</v>
+      </c>
+      <c r="Q89">
+        <v>-10.94388498085333</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8059604830849989</v>
+      </c>
+      <c r="T89">
+        <v>10.388576856791</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.003085157146664878</v>
+      </c>
+      <c r="W89">
+        <v>0.2380632644733764</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.01402344157574953</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3138899028928874</v>
+      </c>
+      <c r="C90">
+        <v>-33.81840468241885</v>
+      </c>
+      <c r="D90">
+        <v>24.03591531758115</v>
+      </c>
+      <c r="E90">
+        <v>60.53032</v>
+      </c>
+      <c r="F90">
+        <v>60.64432</v>
+      </c>
+      <c r="G90">
+        <v>2.79</v>
+      </c>
+      <c r="H90">
+        <v>68.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K90">
+        <v>0.067</v>
+      </c>
+      <c r="L90">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M90">
+        <v>14.481863616</v>
+      </c>
+      <c r="N90">
+        <v>-14.28108583822222</v>
+      </c>
+      <c r="O90">
+        <v>-3.141838884408889</v>
+      </c>
+      <c r="P90">
+        <v>-11.13924695381333</v>
+      </c>
+      <c r="Q90">
+        <v>-11.07224695381333</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.8698905233420824</v>
+      </c>
+      <c r="T90">
+        <v>11.25429159485692</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.003050098542725505</v>
+      </c>
+      <c r="W90">
+        <v>0.2380716364679971</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.01386408428511599</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3158899028928874</v>
+      </c>
+      <c r="C91">
+        <v>-34.68103289015678</v>
+      </c>
+      <c r="D91">
+        <v>23.86242710984322</v>
+      </c>
+      <c r="E91">
+        <v>61.21946000000001</v>
+      </c>
+      <c r="F91">
+        <v>61.33346</v>
+      </c>
+      <c r="G91">
+        <v>2.79</v>
+      </c>
+      <c r="H91">
+        <v>68.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K91">
+        <v>0.067</v>
+      </c>
+      <c r="L91">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M91">
+        <v>14.646430248</v>
+      </c>
+      <c r="N91">
+        <v>-14.44565247022222</v>
+      </c>
+      <c r="O91">
+        <v>-3.178043543448889</v>
+      </c>
+      <c r="P91">
+        <v>-11.26760892677333</v>
+      </c>
+      <c r="Q91">
+        <v>-11.20060892677333</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.9454442072822717</v>
+      </c>
+      <c r="T91">
+        <v>12.27740901257118</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.003015827772582521</v>
+      </c>
+      <c r="W91">
+        <v>0.2380798203279073</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.01370830805719336</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3178899028928874</v>
+      </c>
+      <c r="C92">
+        <v>-35.54117461298873</v>
+      </c>
+      <c r="D92">
+        <v>23.69142538701127</v>
+      </c>
+      <c r="E92">
+        <v>61.90860000000001</v>
+      </c>
+      <c r="F92">
+        <v>62.0226</v>
+      </c>
+      <c r="G92">
+        <v>2.79</v>
+      </c>
+      <c r="H92">
+        <v>68.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K92">
+        <v>0.067</v>
+      </c>
+      <c r="L92">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M92">
+        <v>14.81099688</v>
+      </c>
+      <c r="N92">
+        <v>-14.61021910222222</v>
+      </c>
+      <c r="O92">
+        <v>-3.214248202488889</v>
+      </c>
+      <c r="P92">
+        <v>-11.39597089973333</v>
+      </c>
+      <c r="Q92">
+        <v>-11.32897089973333</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.036108628010499</v>
+      </c>
+      <c r="T92">
+        <v>13.5051499138283</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.002982318575109383</v>
+      </c>
+      <c r="W92">
+        <v>0.2380878223242639</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.01355599352322456</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3198899028928873</v>
+      </c>
+      <c r="C93">
+        <v>-36.39888292613827</v>
+      </c>
+      <c r="D93">
+        <v>23.52285707386174</v>
+      </c>
+      <c r="E93">
+        <v>62.59774000000001</v>
+      </c>
+      <c r="F93">
+        <v>62.71174000000001</v>
+      </c>
+      <c r="G93">
+        <v>2.79</v>
+      </c>
+      <c r="H93">
+        <v>68.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K93">
+        <v>0.067</v>
+      </c>
+      <c r="L93">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M93">
+        <v>14.975563512</v>
+      </c>
+      <c r="N93">
+        <v>-14.77478573422222</v>
+      </c>
+      <c r="O93">
+        <v>-3.250452861528889</v>
+      </c>
+      <c r="P93">
+        <v>-11.52433287269334</v>
+      </c>
+      <c r="Q93">
+        <v>-11.45733287269334</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.146920697789443</v>
+      </c>
+      <c r="T93">
+        <v>15.00572212647589</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.002949545843514773</v>
+      </c>
+      <c r="W93">
+        <v>0.2380956484525687</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.01340702656143089</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3218899028928874</v>
+      </c>
+      <c r="C94">
+        <v>-37.25420940494577</v>
+      </c>
+      <c r="D94">
+        <v>23.35667059505424</v>
+      </c>
+      <c r="E94">
+        <v>63.28688</v>
+      </c>
+      <c r="F94">
+        <v>63.40088</v>
+      </c>
+      <c r="G94">
+        <v>2.79</v>
+      </c>
+      <c r="H94">
+        <v>68.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K94">
+        <v>0.067</v>
+      </c>
+      <c r="L94">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M94">
+        <v>15.140130144</v>
+      </c>
+      <c r="N94">
+        <v>-14.93935236622222</v>
+      </c>
+      <c r="O94">
+        <v>-3.286657520568889</v>
+      </c>
+      <c r="P94">
+        <v>-11.65269484565333</v>
+      </c>
+      <c r="Q94">
+        <v>-11.58569484565333</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.285435785013124</v>
+      </c>
+      <c r="T94">
+        <v>16.88143739228539</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.002917485562607004</v>
+      </c>
+      <c r="W94">
+        <v>0.2381033044476495</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.01326129801185005</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3238899028928874</v>
+      </c>
+      <c r="C95">
+        <v>-38.10720417747926</v>
+      </c>
+      <c r="D95">
+        <v>23.19281582252075</v>
+      </c>
+      <c r="E95">
+        <v>63.97602000000001</v>
+      </c>
+      <c r="F95">
+        <v>64.09002000000001</v>
+      </c>
+      <c r="G95">
+        <v>2.79</v>
+      </c>
+      <c r="H95">
+        <v>68.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K95">
+        <v>0.067</v>
+      </c>
+      <c r="L95">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M95">
+        <v>15.304696776</v>
+      </c>
+      <c r="N95">
+        <v>-15.10391899822223</v>
+      </c>
+      <c r="O95">
+        <v>-3.32286217960889</v>
+      </c>
+      <c r="P95">
+        <v>-11.78105681861333</v>
+      </c>
+      <c r="Q95">
+        <v>-11.71405681861333</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.463526611443571</v>
+      </c>
+      <c r="T95">
+        <v>19.29307130546902</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.002886114750105853</v>
+      </c>
+      <c r="W95">
+        <v>0.2381107957976747</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.01311870340957211</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3258899028928874</v>
+      </c>
+      <c r="C96">
+        <v>-38.95791597494629</v>
+      </c>
+      <c r="D96">
+        <v>23.03124402505371</v>
+      </c>
+      <c r="E96">
+        <v>64.66516</v>
+      </c>
+      <c r="F96">
+        <v>64.77916</v>
+      </c>
+      <c r="G96">
+        <v>2.79</v>
+      </c>
+      <c r="H96">
+        <v>68.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K96">
+        <v>0.067</v>
+      </c>
+      <c r="L96">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M96">
+        <v>15.469263408</v>
+      </c>
+      <c r="N96">
+        <v>-15.26848563022222</v>
+      </c>
+      <c r="O96">
+        <v>-3.359066838648889</v>
+      </c>
+      <c r="P96">
+        <v>-11.90941879157333</v>
+      </c>
+      <c r="Q96">
+        <v>-11.84241879157333</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.700981046684166</v>
+      </c>
+      <c r="T96">
+        <v>22.50858318971386</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.002855411401700472</v>
+      </c>
+      <c r="W96">
+        <v>0.238118127757274</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.01297914273500222</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3278899028928874</v>
+      </c>
+      <c r="C97">
+        <v>-39.80639218001317</v>
+      </c>
+      <c r="D97">
+        <v>22.87190781998683</v>
+      </c>
+      <c r="E97">
+        <v>65.35429999999999</v>
+      </c>
+      <c r="F97">
+        <v>65.4683</v>
+      </c>
+      <c r="G97">
+        <v>2.79</v>
+      </c>
+      <c r="H97">
+        <v>68.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K97">
+        <v>0.067</v>
+      </c>
+      <c r="L97">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M97">
+        <v>15.63383004</v>
+      </c>
+      <c r="N97">
+        <v>-15.43305226222222</v>
+      </c>
+      <c r="O97">
+        <v>-3.395271497688889</v>
+      </c>
+      <c r="P97">
+        <v>-12.03778076453333</v>
+      </c>
+      <c r="Q97">
+        <v>-11.97078076453333</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.033417256021</v>
+      </c>
+      <c r="T97">
+        <v>27.01029982765664</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.002825354439577309</v>
+      </c>
+      <c r="W97">
+        <v>0.238125305359829</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.01284252017989695</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3298899028928874</v>
+      </c>
+      <c r="C98">
+        <v>-40.65267887313226</v>
+      </c>
+      <c r="D98">
+        <v>22.71476112686774</v>
+      </c>
+      <c r="E98">
+        <v>66.04343999999999</v>
+      </c>
+      <c r="F98">
+        <v>66.15743999999999</v>
+      </c>
+      <c r="G98">
+        <v>2.79</v>
+      </c>
+      <c r="H98">
+        <v>68.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K98">
+        <v>0.067</v>
+      </c>
+      <c r="L98">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M98">
+        <v>15.798396672</v>
+      </c>
+      <c r="N98">
+        <v>-15.59761889422222</v>
+      </c>
+      <c r="O98">
+        <v>-3.431476156728889</v>
+      </c>
+      <c r="P98">
+        <v>-12.16614273749333</v>
+      </c>
+      <c r="Q98">
+        <v>-12.09914273749333</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.532071570026245</v>
+      </c>
+      <c r="T98">
+        <v>33.76287478457073</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.002795923664165046</v>
+      </c>
+      <c r="W98">
+        <v>0.2381323334289974</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.01270874392802301</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3318899028928874</v>
+      </c>
+      <c r="C99">
+        <v>-41.49682087697249</v>
+      </c>
+      <c r="D99">
+        <v>22.55975912302751</v>
+      </c>
+      <c r="E99">
+        <v>66.73258</v>
+      </c>
+      <c r="F99">
+        <v>66.84658</v>
+      </c>
+      <c r="G99">
+        <v>2.79</v>
+      </c>
+      <c r="H99">
+        <v>68.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K99">
+        <v>0.067</v>
+      </c>
+      <c r="L99">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M99">
+        <v>15.962963304</v>
+      </c>
+      <c r="N99">
+        <v>-15.76218552622222</v>
+      </c>
+      <c r="O99">
+        <v>-3.467680815768889</v>
+      </c>
+      <c r="P99">
+        <v>-12.29450471045334</v>
+      </c>
+      <c r="Q99">
+        <v>-12.22750471045333</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.363162093368327</v>
+      </c>
+      <c r="T99">
+        <v>45.01716637942764</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.002767099708864375</v>
+      </c>
+      <c r="W99">
+        <v>0.2381392165895232</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.01257772594938356</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3338899028928874</v>
+      </c>
+      <c r="C100">
+        <v>-42.33886179904312</v>
+      </c>
+      <c r="D100">
+        <v>22.40685820095688</v>
+      </c>
+      <c r="E100">
+        <v>67.42171999999999</v>
+      </c>
+      <c r="F100">
+        <v>67.53572</v>
+      </c>
+      <c r="G100">
+        <v>2.79</v>
+      </c>
+      <c r="H100">
+        <v>68.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K100">
+        <v>0.067</v>
+      </c>
+      <c r="L100">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M100">
+        <v>16.127529936</v>
+      </c>
+      <c r="N100">
+        <v>-15.92675215822222</v>
+      </c>
+      <c r="O100">
+        <v>-3.503885474808889</v>
+      </c>
+      <c r="P100">
+        <v>-12.42286668341333</v>
+      </c>
+      <c r="Q100">
+        <v>-12.35586668341333</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.02534314005249</v>
+      </c>
+      <c r="T100">
+        <v>67.52574956914145</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.002738863997549433</v>
+      </c>
+      <c r="W100">
+        <v>0.2381459592773852</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.01244938180704291</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3358899028928874</v>
+      </c>
+      <c r="C101">
+        <v>-43.17884407259582</v>
+      </c>
+      <c r="D101">
+        <v>22.25601592740418</v>
+      </c>
+      <c r="E101">
+        <v>68.11086</v>
+      </c>
+      <c r="F101">
+        <v>68.22486000000001</v>
+      </c>
+      <c r="G101">
+        <v>2.79</v>
+      </c>
+      <c r="H101">
+        <v>68.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.2677777777777778</v>
+      </c>
+      <c r="K101">
+        <v>0.067</v>
+      </c>
+      <c r="L101">
+        <v>0.2007777777777778</v>
+      </c>
+      <c r="M101">
+        <v>16.292096568</v>
+      </c>
+      <c r="N101">
+        <v>-16.09131879022222</v>
+      </c>
+      <c r="O101">
+        <v>-3.540090133848889</v>
+      </c>
+      <c r="P101">
+        <v>-12.55122865637334</v>
+      </c>
+      <c r="Q101">
+        <v>-12.48422865637334</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>10.01188628010498</v>
+      </c>
+      <c r="T101">
+        <v>135.0514991382829</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.002711198704644893</v>
+      </c>
+      <c r="W101">
+        <v>0.2381525657493308</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.01232363047565854</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_software_entertainment.xlsx
@@ -1516,7 +1516,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1653,22 +1653,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1388609110097019</v>
+        <v>0.1386022170054805</v>
       </c>
       <c r="C2">
-        <v>73.76945545333216</v>
+        <v>73.23469856988635</v>
       </c>
       <c r="D2">
-        <v>72.75945545333215</v>
+        <v>72.96227856988634</v>
       </c>
       <c r="E2">
-        <v>-0.058</v>
+        <v>0.6795800000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7375800000000001</v>
       </c>
       <c r="G2">
         <v>1.01</v>
@@ -1689,45 +1689,45 @@
         <v>0.397</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.038206644</v>
       </c>
       <c r="N2">
-        <v>0.397</v>
+        <v>0.358793356</v>
       </c>
       <c r="O2">
-        <v>0.08734</v>
+        <v>0.07893453832</v>
       </c>
       <c r="P2">
-        <v>0.30966</v>
+        <v>0.27985881768</v>
       </c>
       <c r="Q2">
-        <v>0.42366</v>
+        <v>0.39385881768</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1388609110097019</v>
+        <v>0.1395941181873541</v>
       </c>
       <c r="T2">
-        <v>1.354149646462541</v>
+        <v>1.364818704283155</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V2">
         <v>0.22</v>
       </c>
       <c r="W2">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>10.3908629085559</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1735,22 +1735,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1386022170054805</v>
+        <v>0.1383981230012592</v>
       </c>
       <c r="C3">
-        <v>73.23469856988635</v>
+        <v>72.65793353144056</v>
       </c>
       <c r="D3">
-        <v>72.96227856988634</v>
+        <v>73.12309353144056</v>
       </c>
       <c r="E3">
-        <v>0.6795800000000001</v>
+        <v>1.41716</v>
       </c>
       <c r="F3">
-        <v>0.7375800000000001</v>
+        <v>1.47516</v>
       </c>
       <c r="G3">
         <v>1.01</v>
@@ -1771,45 +1771,45 @@
         <v>0.397</v>
       </c>
       <c r="M3">
-        <v>0.038206644</v>
+        <v>0.08157634800000002</v>
       </c>
       <c r="N3">
-        <v>0.358793356</v>
+        <v>0.315423652</v>
       </c>
       <c r="O3">
-        <v>0.07893453832</v>
+        <v>0.06939320344</v>
       </c>
       <c r="P3">
-        <v>0.27985881768</v>
+        <v>0.24603044856</v>
       </c>
       <c r="Q3">
-        <v>0.39385881768</v>
+        <v>0.36003044856</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1395941181873541</v>
+        <v>0.1403422887767951</v>
       </c>
       <c r="T3">
-        <v>1.364818704283155</v>
+        <v>1.375705497977659</v>
       </c>
       <c r="U3">
-        <v>0.0518</v>
+        <v>0.0553</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.040404</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y3">
-        <v>10.3908629085559</v>
+        <v>4.866606678690739</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1817,22 +1817,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1383981230012592</v>
+        <v>0.1386464289970379</v>
       </c>
       <c r="C4">
-        <v>72.65793353144056</v>
+        <v>71.72479509424616</v>
       </c>
       <c r="D4">
-        <v>73.12309353144056</v>
+        <v>72.92753509424615</v>
       </c>
       <c r="E4">
-        <v>1.41716</v>
+        <v>2.15474</v>
       </c>
       <c r="F4">
-        <v>1.47516</v>
+        <v>2.21274</v>
       </c>
       <c r="G4">
         <v>1.01</v>
@@ -1853,45 +1853,45 @@
         <v>0.397</v>
       </c>
       <c r="M4">
-        <v>0.08157634800000002</v>
+        <v>0.167725692</v>
       </c>
       <c r="N4">
-        <v>0.315423652</v>
+        <v>0.229274308</v>
       </c>
       <c r="O4">
-        <v>0.06939320344</v>
+        <v>0.05044034776</v>
       </c>
       <c r="P4">
-        <v>0.24603044856</v>
+        <v>0.17883396024</v>
       </c>
       <c r="Q4">
-        <v>0.36003044856</v>
+        <v>0.29283396024</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1403422887767951</v>
+        <v>0.1411058855639566</v>
       </c>
       <c r="T4">
-        <v>1.375705497977659</v>
+        <v>1.386816761645246</v>
       </c>
       <c r="U4">
-        <v>0.0553</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.04313400000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y4">
-        <v>4.866606678690739</v>
+        <v>2.366959976531204</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1386464289970379</v>
+        <v>0.1409661047721235</v>
       </c>
       <c r="C5">
-        <v>71.72479509424616</v>
+        <v>69.20960491570717</v>
       </c>
       <c r="D5">
-        <v>72.92753509424615</v>
+        <v>71.14992491570717</v>
       </c>
       <c r="E5">
-        <v>2.15474</v>
+        <v>2.892320000000001</v>
       </c>
       <c r="F5">
-        <v>2.21274</v>
+        <v>2.95032</v>
       </c>
       <c r="G5">
         <v>1.01</v>
@@ -1935,45 +1935,45 @@
         <v>0.397</v>
       </c>
       <c r="M5">
-        <v>0.167725692</v>
+        <v>0.4331069760000001</v>
       </c>
       <c r="N5">
-        <v>0.229274308</v>
+        <v>-0.03610697600000007</v>
       </c>
       <c r="O5">
-        <v>0.05044034776</v>
+        <v>-0.007943534720000015</v>
       </c>
       <c r="P5">
-        <v>0.17883396024</v>
+        <v>-0.02816344128000006</v>
       </c>
       <c r="Q5">
-        <v>0.29283396024</v>
+        <v>0.08583655871999996</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1411058855639566</v>
+        <v>0.1419565078220652</v>
       </c>
       <c r="T5">
-        <v>1.386816761645246</v>
+        <v>1.399194351952425</v>
       </c>
       <c r="U5">
-        <v>0.07580000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V5">
-        <v>0.22</v>
+        <v>0.2016591854664562</v>
       </c>
       <c r="W5">
-        <v>0.05912400000000001</v>
+        <v>0.1171964315735242</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y5">
-        <v>2.366959976531204</v>
+        <v>0.9166326612111645</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1981,22 +1981,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1409661047721235</v>
+        <v>0.1448779764306297</v>
       </c>
       <c r="C6">
-        <v>69.20960491570717</v>
+        <v>65.66282972612363</v>
       </c>
       <c r="D6">
-        <v>71.14992491570717</v>
+        <v>68.34072972612363</v>
       </c>
       <c r="E6">
-        <v>2.892320000000001</v>
+        <v>3.629900000000001</v>
       </c>
       <c r="F6">
-        <v>2.95032</v>
+        <v>3.687900000000001</v>
       </c>
       <c r="G6">
         <v>1.01</v>
@@ -2017,45 +2017,45 @@
         <v>0.397</v>
       </c>
       <c r="M6">
-        <v>0.4331069760000001</v>
+        <v>0.7405303200000002</v>
       </c>
       <c r="N6">
-        <v>-0.03610697600000007</v>
+        <v>-0.3435303200000002</v>
       </c>
       <c r="O6">
-        <v>-0.007943534720000015</v>
+        <v>-0.07557667040000003</v>
       </c>
       <c r="P6">
-        <v>-0.02816344128000006</v>
+        <v>-0.2679536496000001</v>
       </c>
       <c r="Q6">
-        <v>0.08583655871999996</v>
+        <v>-0.1539536496000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1419565078220652</v>
+        <v>0.1431811780712513</v>
       </c>
       <c r="T6">
-        <v>1.399194351952425</v>
+        <v>1.417014796293398</v>
       </c>
       <c r="U6">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V6">
-        <v>0.2016591854664562</v>
+        <v>0.1179425036911385</v>
       </c>
       <c r="W6">
-        <v>0.1171964315735242</v>
+        <v>0.1771171452588194</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y6">
-        <v>0.9166326612111645</v>
+        <v>0.536102289505175</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2063,22 +2063,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1448779764306297</v>
+        <v>0.1486094340831762</v>
       </c>
       <c r="C7">
-        <v>65.66282972612363</v>
+        <v>62.44483009157099</v>
       </c>
       <c r="D7">
-        <v>68.34072972612363</v>
+        <v>65.86031009157098</v>
       </c>
       <c r="E7">
-        <v>3.629900000000001</v>
+        <v>4.367480000000001</v>
       </c>
       <c r="F7">
-        <v>3.687900000000001</v>
+        <v>4.425480000000001</v>
       </c>
       <c r="G7">
         <v>1.01</v>
@@ -2099,45 +2099,45 @@
         <v>0.397</v>
       </c>
       <c r="M7">
-        <v>0.7405303200000002</v>
+        <v>1.043528184</v>
       </c>
       <c r="N7">
-        <v>-0.3435303200000002</v>
+        <v>-0.6465281840000003</v>
       </c>
       <c r="O7">
-        <v>-0.07557667040000003</v>
+        <v>-0.1422362004800001</v>
       </c>
       <c r="P7">
-        <v>-0.2679536496000001</v>
+        <v>-0.5042919835200003</v>
       </c>
       <c r="Q7">
-        <v>-0.1539536496000001</v>
+        <v>-0.3902919835200003</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1431811780712513</v>
+        <v>0.1443038051279098</v>
       </c>
       <c r="T7">
-        <v>1.417014796293398</v>
+        <v>1.433350387847245</v>
       </c>
       <c r="U7">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.1179425036911385</v>
+        <v>0.08369682902594222</v>
       </c>
       <c r="W7">
-        <v>0.1771171452588194</v>
+        <v>0.2160642877156828</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y7">
-        <v>0.536102289505175</v>
+        <v>0.380440131936101</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2145,22 +2145,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1486094340831762</v>
+        <v>0.1505094340831762</v>
       </c>
       <c r="C8">
-        <v>62.44483009157099</v>
+        <v>60.51218500245416</v>
       </c>
       <c r="D8">
-        <v>65.86031009157098</v>
+        <v>64.66524500245416</v>
       </c>
       <c r="E8">
-        <v>4.36748</v>
+        <v>5.10506</v>
       </c>
       <c r="F8">
-        <v>4.42548</v>
+        <v>5.16306</v>
       </c>
       <c r="G8">
         <v>1.01</v>
@@ -2181,37 +2181,37 @@
         <v>0.397</v>
       </c>
       <c r="M8">
-        <v>1.043528184</v>
+        <v>1.217449548</v>
       </c>
       <c r="N8">
-        <v>-0.6465281840000001</v>
+        <v>-0.820449548</v>
       </c>
       <c r="O8">
-        <v>-0.14223620048</v>
+        <v>-0.18049890056</v>
       </c>
       <c r="P8">
-        <v>-0.5042919835200002</v>
+        <v>-0.6399506474400001</v>
       </c>
       <c r="Q8">
-        <v>-0.3902919835200002</v>
+        <v>-0.5259506474400001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1443038051279098</v>
+        <v>0.1453629858282099</v>
       </c>
       <c r="T8">
-        <v>1.433350387847245</v>
+        <v>1.448762757609043</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.08369682902594225</v>
+        <v>0.07174013916509336</v>
       </c>
       <c r="W8">
-        <v>0.2160642877156828</v>
+        <v>0.218883675184871</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.380440131936101</v>
+        <v>0.3260915416595153</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2227,22 +2227,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1505094340831762</v>
+        <v>0.1524094340831762</v>
       </c>
       <c r="C9">
-        <v>60.51218500245416</v>
+        <v>58.622136962817</v>
       </c>
       <c r="D9">
-        <v>64.66524500245416</v>
+        <v>63.51277696281701</v>
       </c>
       <c r="E9">
-        <v>5.105060000000002</v>
+        <v>5.842640000000001</v>
       </c>
       <c r="F9">
-        <v>5.163060000000002</v>
+        <v>5.900640000000001</v>
       </c>
       <c r="G9">
         <v>1.01</v>
@@ -2263,37 +2263,37 @@
         <v>0.397</v>
       </c>
       <c r="M9">
-        <v>1.217449548</v>
+        <v>1.391370912</v>
       </c>
       <c r="N9">
-        <v>-0.8204495480000005</v>
+        <v>-0.9943709120000002</v>
       </c>
       <c r="O9">
-        <v>-0.1804989005600001</v>
+        <v>-0.21876160064</v>
       </c>
       <c r="P9">
-        <v>-0.6399506474400004</v>
+        <v>-0.7756093113600001</v>
       </c>
       <c r="Q9">
-        <v>-0.5259506474400004</v>
+        <v>-0.6616093113600001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1453629858282099</v>
+        <v>0.1464451921959078</v>
       </c>
       <c r="T9">
-        <v>1.448762757609043</v>
+        <v>1.464510178887402</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.07174013916509334</v>
+        <v>0.06277262176945668</v>
       </c>
       <c r="W9">
-        <v>0.218883675184871</v>
+        <v>0.2209982157867621</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.3260915416595151</v>
+        <v>0.2853300989520758</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2309,22 +2309,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1524094340831762</v>
+        <v>0.1543094340831762</v>
       </c>
       <c r="C10">
-        <v>58.622136962817</v>
+        <v>56.77244834987511</v>
       </c>
       <c r="D10">
-        <v>63.51277696281701</v>
+        <v>62.40066834987511</v>
       </c>
       <c r="E10">
-        <v>5.842640000000001</v>
+        <v>6.580220000000001</v>
       </c>
       <c r="F10">
-        <v>5.900640000000001</v>
+        <v>6.63822</v>
       </c>
       <c r="G10">
         <v>1.01</v>
@@ -2345,37 +2345,37 @@
         <v>0.397</v>
       </c>
       <c r="M10">
-        <v>1.391370912</v>
+        <v>1.565292276</v>
       </c>
       <c r="N10">
-        <v>-0.9943709120000002</v>
+        <v>-1.168292276</v>
       </c>
       <c r="O10">
-        <v>-0.21876160064</v>
+        <v>-0.25702430072</v>
       </c>
       <c r="P10">
-        <v>-0.7756093113600001</v>
+        <v>-0.91126797528</v>
       </c>
       <c r="Q10">
-        <v>-0.6616093113600001</v>
+        <v>-0.79726797528</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1464451921959078</v>
+        <v>0.1475511833189398</v>
       </c>
       <c r="T10">
-        <v>1.464510178887402</v>
+        <v>1.480603697336714</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.06277262176945668</v>
+        <v>0.05579788601729483</v>
       </c>
       <c r="W10">
-        <v>0.2209982157867621</v>
+        <v>0.2226428584771219</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.2853300989520758</v>
+        <v>0.2536267546240674</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2391,22 +2391,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1543094340831762</v>
+        <v>0.1562094340831762</v>
       </c>
       <c r="C11">
-        <v>56.77244834987511</v>
+        <v>54.96103556693152</v>
       </c>
       <c r="D11">
-        <v>62.40066834987511</v>
+        <v>61.32683556693152</v>
       </c>
       <c r="E11">
-        <v>6.580220000000001</v>
+        <v>7.317800000000001</v>
       </c>
       <c r="F11">
-        <v>6.63822</v>
+        <v>7.375800000000001</v>
       </c>
       <c r="G11">
         <v>1.01</v>
@@ -2427,37 +2427,37 @@
         <v>0.397</v>
       </c>
       <c r="M11">
-        <v>1.565292276</v>
+        <v>1.73921364</v>
       </c>
       <c r="N11">
-        <v>-1.168292276</v>
+        <v>-1.34221364</v>
       </c>
       <c r="O11">
-        <v>-0.25702430072</v>
+        <v>-0.2952870008</v>
       </c>
       <c r="P11">
-        <v>-0.91126797528</v>
+        <v>-1.0469266392</v>
       </c>
       <c r="Q11">
-        <v>-0.79726797528</v>
+        <v>-0.9329266392000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1475511833189398</v>
+        <v>0.1486817520224836</v>
       </c>
       <c r="T11">
-        <v>1.480603697336714</v>
+        <v>1.497054849529345</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.05579788601729483</v>
+        <v>0.05021809741556534</v>
       </c>
       <c r="W11">
-        <v>0.2226428584771219</v>
+        <v>0.2239585726294097</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.2536267546240674</v>
+        <v>0.2282640791616607</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2473,22 +2473,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1562094340831762</v>
+        <v>0.1581094340831762</v>
       </c>
       <c r="C12">
-        <v>54.96103556693151</v>
+        <v>53.18595601465994</v>
       </c>
       <c r="D12">
-        <v>61.32683556693152</v>
+        <v>60.28933601465994</v>
       </c>
       <c r="E12">
-        <v>7.317800000000002</v>
+        <v>8.055380000000001</v>
       </c>
       <c r="F12">
-        <v>7.375800000000002</v>
+        <v>8.113380000000001</v>
       </c>
       <c r="G12">
         <v>1.01</v>
@@ -2509,37 +2509,37 @@
         <v>0.397</v>
       </c>
       <c r="M12">
-        <v>1.73921364</v>
+        <v>1.913135004</v>
       </c>
       <c r="N12">
-        <v>-1.34221364</v>
+        <v>-1.516135004</v>
       </c>
       <c r="O12">
-        <v>-0.2952870008000001</v>
+        <v>-0.3335497008800001</v>
       </c>
       <c r="P12">
-        <v>-1.0469266392</v>
+        <v>-1.18258530312</v>
       </c>
       <c r="Q12">
-        <v>-0.9329266392000003</v>
+        <v>-1.06858530312</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1486817520224836</v>
+        <v>0.1498377267643093</v>
       </c>
       <c r="T12">
-        <v>1.497054849529345</v>
+        <v>1.513875690535292</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.05021809741556534</v>
+        <v>0.04565281583233213</v>
       </c>
       <c r="W12">
-        <v>0.2239585726294097</v>
+        <v>0.2250350660267361</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.2282640791616606</v>
+        <v>0.2075127992378734</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2555,22 +2555,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1581094340831762</v>
+        <v>0.1600094340831762</v>
       </c>
       <c r="C13">
-        <v>53.18595601465994</v>
+        <v>51.44539636287015</v>
       </c>
       <c r="D13">
-        <v>60.28933601465994</v>
+        <v>59.28635636287015</v>
       </c>
       <c r="E13">
-        <v>8.055380000000001</v>
+        <v>8.792960000000001</v>
       </c>
       <c r="F13">
-        <v>8.113380000000001</v>
+        <v>8.850960000000001</v>
       </c>
       <c r="G13">
         <v>1.01</v>
@@ -2591,37 +2591,37 @@
         <v>0.397</v>
       </c>
       <c r="M13">
-        <v>1.913135004</v>
+        <v>2.087056368</v>
       </c>
       <c r="N13">
-        <v>-1.516135004</v>
+        <v>-1.690056368</v>
       </c>
       <c r="O13">
-        <v>-0.3335497008800001</v>
+        <v>-0.3718124009600001</v>
       </c>
       <c r="P13">
-        <v>-1.18258530312</v>
+        <v>-1.31824396704</v>
       </c>
       <c r="Q13">
-        <v>-1.06858530312</v>
+        <v>-1.20424396704</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1498377267643093</v>
+        <v>0.1510199736593582</v>
       </c>
       <c r="T13">
-        <v>1.513875690535292</v>
+        <v>1.531078823382284</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.04565281583233213</v>
+        <v>0.04184841451297112</v>
       </c>
       <c r="W13">
-        <v>0.2250350660267361</v>
+        <v>0.2259321438578414</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.2075127992378734</v>
+        <v>0.1902200659680505</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2637,22 +2637,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1600094340831762</v>
+        <v>0.1619094340831762</v>
       </c>
       <c r="C14">
-        <v>51.44539636287015</v>
+        <v>49.73766197378958</v>
       </c>
       <c r="D14">
-        <v>59.28635636287015</v>
+        <v>58.31620197378958</v>
       </c>
       <c r="E14">
-        <v>8.792960000000001</v>
+        <v>9.530540000000002</v>
       </c>
       <c r="F14">
-        <v>8.850960000000001</v>
+        <v>9.588540000000002</v>
       </c>
       <c r="G14">
         <v>1.01</v>
@@ -2673,37 +2673,37 @@
         <v>0.397</v>
       </c>
       <c r="M14">
-        <v>2.087056368</v>
+        <v>2.260977732000001</v>
       </c>
       <c r="N14">
-        <v>-1.690056368</v>
+        <v>-1.863977732000001</v>
       </c>
       <c r="O14">
-        <v>-0.3718124009600001</v>
+        <v>-0.4100751010400001</v>
       </c>
       <c r="P14">
-        <v>-1.31824396704</v>
+        <v>-1.45390263096</v>
       </c>
       <c r="Q14">
-        <v>-1.20424396704</v>
+        <v>-1.33990263096</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1510199736593582</v>
+        <v>0.1522293986439485</v>
       </c>
       <c r="T14">
-        <v>1.531078823382284</v>
+        <v>1.548677430547598</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.04184841451297112</v>
+        <v>0.03862930570428103</v>
       </c>
       <c r="W14">
-        <v>0.2259321438578414</v>
+        <v>0.2266912097149305</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.1902200659680505</v>
+        <v>0.1755877532012774</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2719,22 +2719,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1619094340831762</v>
+        <v>0.1638094340831762</v>
       </c>
       <c r="C15">
-        <v>49.73766197378958</v>
+        <v>48.0611673470818</v>
       </c>
       <c r="D15">
-        <v>58.31620197378958</v>
+        <v>57.3772873470818</v>
       </c>
       <c r="E15">
-        <v>9.530540000000002</v>
+        <v>10.26812</v>
       </c>
       <c r="F15">
-        <v>9.588540000000002</v>
+        <v>10.32612</v>
       </c>
       <c r="G15">
         <v>1.01</v>
@@ -2755,37 +2755,37 @@
         <v>0.397</v>
       </c>
       <c r="M15">
-        <v>2.260977732000001</v>
+        <v>2.434899096000001</v>
       </c>
       <c r="N15">
-        <v>-1.863977732000001</v>
+        <v>-2.037899096000001</v>
       </c>
       <c r="O15">
-        <v>-0.4100751010400001</v>
+        <v>-0.4483378011200003</v>
       </c>
       <c r="P15">
-        <v>-1.45390263096</v>
+        <v>-1.589561294880001</v>
       </c>
       <c r="Q15">
-        <v>-1.33990263096</v>
+        <v>-1.475561294880001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1522293986439485</v>
+        <v>0.1534669497909712</v>
       </c>
       <c r="T15">
-        <v>1.548677430547598</v>
+        <v>1.566685307646988</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.03862930570428103</v>
+        <v>0.03587006958254667</v>
       </c>
       <c r="W15">
-        <v>0.2266912097149305</v>
+        <v>0.2273418375924355</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.1755877532012774</v>
+        <v>0.1630457708297575</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2801,22 +2801,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1638094340831762</v>
+        <v>0.1657094340831762</v>
       </c>
       <c r="C16">
-        <v>48.0611673470818</v>
+        <v>46.41442747327375</v>
       </c>
       <c r="D16">
-        <v>57.3772873470818</v>
+        <v>56.46812747327375</v>
       </c>
       <c r="E16">
-        <v>10.26812</v>
+        <v>11.0057</v>
       </c>
       <c r="F16">
-        <v>10.32612</v>
+        <v>11.0637</v>
       </c>
       <c r="G16">
         <v>1.01</v>
@@ -2837,37 +2837,37 @@
         <v>0.397</v>
       </c>
       <c r="M16">
-        <v>2.434899096000001</v>
+        <v>2.608820460000001</v>
       </c>
       <c r="N16">
-        <v>-2.037899096000001</v>
+        <v>-2.211820460000001</v>
       </c>
       <c r="O16">
-        <v>-0.4483378011200003</v>
+        <v>-0.4866005012000003</v>
       </c>
       <c r="P16">
-        <v>-1.589561294880001</v>
+        <v>-1.725219958800001</v>
       </c>
       <c r="Q16">
-        <v>-1.475561294880001</v>
+        <v>-1.611219958800001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1534669497909712</v>
+        <v>0.1547336197885121</v>
       </c>
       <c r="T16">
-        <v>1.566685307646988</v>
+        <v>1.585116899501659</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.03587006958254667</v>
+        <v>0.03347873161037689</v>
       </c>
       <c r="W16">
-        <v>0.2273418375924355</v>
+        <v>0.2279057150862731</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.1630457708297575</v>
+        <v>0.1521760527744404</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2883,22 +2883,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1657094340831762</v>
+        <v>0.1676094340831762</v>
       </c>
       <c r="C17">
-        <v>46.41442747327376</v>
+        <v>44.79604999640544</v>
       </c>
       <c r="D17">
-        <v>56.46812747327376</v>
+        <v>55.58732999640544</v>
       </c>
       <c r="E17">
-        <v>11.0057</v>
+        <v>11.74328</v>
       </c>
       <c r="F17">
-        <v>11.0637</v>
+        <v>11.80128</v>
       </c>
       <c r="G17">
         <v>1.01</v>
@@ -2919,37 +2919,37 @@
         <v>0.397</v>
       </c>
       <c r="M17">
-        <v>2.60882046</v>
+        <v>2.782741824</v>
       </c>
       <c r="N17">
-        <v>-2.21182046</v>
+        <v>-2.385741824</v>
       </c>
       <c r="O17">
-        <v>-0.4866005012</v>
+        <v>-0.5248632012800001</v>
       </c>
       <c r="P17">
-        <v>-1.7252199588</v>
+        <v>-1.86087862272</v>
       </c>
       <c r="Q17">
-        <v>-1.6112199588</v>
+        <v>-1.74687862272</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1547336197885121</v>
+        <v>0.1560304485955181</v>
       </c>
       <c r="T17">
-        <v>1.585116899501659</v>
+        <v>1.60398733878144</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.03347873161037689</v>
+        <v>0.03138631088472834</v>
       </c>
       <c r="W17">
-        <v>0.2279057150862731</v>
+        <v>0.2283991078933811</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.1521760527744405</v>
+        <v>0.142665049476038</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1676094340831762</v>
+        <v>0.1695094340831762</v>
       </c>
       <c r="C18">
-        <v>44.79604999640544</v>
+        <v>43.20472809890261</v>
       </c>
       <c r="D18">
-        <v>55.58732999640544</v>
+        <v>54.73358809890261</v>
       </c>
       <c r="E18">
-        <v>11.74328</v>
+        <v>12.48086</v>
       </c>
       <c r="F18">
-        <v>11.80128</v>
+        <v>12.53886</v>
       </c>
       <c r="G18">
         <v>1.01</v>
@@ -3001,37 +3001,37 @@
         <v>0.397</v>
       </c>
       <c r="M18">
-        <v>2.782741824</v>
+        <v>2.956663188000001</v>
       </c>
       <c r="N18">
-        <v>-2.385741824</v>
+        <v>-2.559663188000001</v>
       </c>
       <c r="O18">
-        <v>-0.5248632012800001</v>
+        <v>-0.5631259013600002</v>
       </c>
       <c r="P18">
-        <v>-1.86087862272</v>
+        <v>-1.996537286640001</v>
       </c>
       <c r="Q18">
-        <v>-1.74687862272</v>
+        <v>-1.882537286640001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1560304485955181</v>
+        <v>0.1573585262894401</v>
       </c>
       <c r="T18">
-        <v>1.60398733878144</v>
+        <v>1.623312487441458</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.03138631088472834</v>
+        <v>0.02954005730327373</v>
       </c>
       <c r="W18">
-        <v>0.2283991078933811</v>
+        <v>0.2288344544878881</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.142665049476038</v>
+        <v>0.1342729877421532</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3047,22 +3047,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1695094340831762</v>
+        <v>0.1714094340831762</v>
       </c>
       <c r="C19">
-        <v>43.20472809890261</v>
+        <v>41.63923403220081</v>
       </c>
       <c r="D19">
-        <v>54.73358809890261</v>
+        <v>53.90567403220081</v>
       </c>
       <c r="E19">
-        <v>12.48086</v>
+        <v>13.21844</v>
       </c>
       <c r="F19">
-        <v>12.53886</v>
+        <v>13.27644</v>
       </c>
       <c r="G19">
         <v>1.01</v>
@@ -3083,37 +3083,37 @@
         <v>0.397</v>
       </c>
       <c r="M19">
-        <v>2.956663188000001</v>
+        <v>3.130584552000001</v>
       </c>
       <c r="N19">
-        <v>-2.559663188000001</v>
+        <v>-2.733584552000001</v>
       </c>
       <c r="O19">
-        <v>-0.5631259013600002</v>
+        <v>-0.6013886014400002</v>
       </c>
       <c r="P19">
-        <v>-1.996537286640001</v>
+        <v>-2.132195950560001</v>
       </c>
       <c r="Q19">
-        <v>-1.882537286640001</v>
+        <v>-2.018195950560001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1573585262894401</v>
+        <v>0.1587189961222381</v>
       </c>
       <c r="T19">
-        <v>1.623312487441458</v>
+        <v>1.643108981190744</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.02954005730327373</v>
+        <v>0.02789894300864741</v>
       </c>
       <c r="W19">
-        <v>0.2288344544878881</v>
+        <v>0.229221429238561</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.1342729877421532</v>
+        <v>0.1268133773120336</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3129,22 +3129,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1714094340831762</v>
+        <v>0.1733094340831762</v>
       </c>
       <c r="C20">
-        <v>41.63923403220081</v>
+        <v>40.09841322576471</v>
       </c>
       <c r="D20">
-        <v>53.90567403220081</v>
+        <v>53.10243322576471</v>
       </c>
       <c r="E20">
-        <v>13.21844</v>
+        <v>13.95602</v>
       </c>
       <c r="F20">
-        <v>13.27644</v>
+        <v>14.01402</v>
       </c>
       <c r="G20">
         <v>1.01</v>
@@ -3165,37 +3165,37 @@
         <v>0.397</v>
       </c>
       <c r="M20">
-        <v>3.130584552</v>
+        <v>3.304505916000001</v>
       </c>
       <c r="N20">
-        <v>-2.733584552</v>
+        <v>-2.907505916000001</v>
       </c>
       <c r="O20">
-        <v>-0.6013886014399999</v>
+        <v>-0.6396513015200002</v>
       </c>
       <c r="P20">
-        <v>-2.13219595056</v>
+        <v>-2.26785461448</v>
       </c>
       <c r="Q20">
-        <v>-2.01819595056</v>
+        <v>-2.153854614480001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1587189961222381</v>
+        <v>0.1601130578027595</v>
       </c>
       <c r="T20">
-        <v>1.643108981190744</v>
+        <v>1.663394277254827</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.02789894300864742</v>
+        <v>0.02643057758713965</v>
       </c>
       <c r="W20">
-        <v>0.229221429238561</v>
+        <v>0.2295676698049525</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.1268133773120338</v>
+        <v>0.1201389890324529</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3211,22 +3211,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1733094340831762</v>
+        <v>0.1752094340831762</v>
       </c>
       <c r="C21">
-        <v>40.09841322576471</v>
+        <v>38.58117891505884</v>
       </c>
       <c r="D21">
-        <v>53.10243322576471</v>
+        <v>52.32277891505885</v>
       </c>
       <c r="E21">
-        <v>13.95602</v>
+        <v>14.6936</v>
       </c>
       <c r="F21">
-        <v>14.01402</v>
+        <v>14.7516</v>
       </c>
       <c r="G21">
         <v>1.01</v>
@@ -3247,37 +3247,37 @@
         <v>0.397</v>
       </c>
       <c r="M21">
-        <v>3.304505916000001</v>
+        <v>3.478427280000001</v>
       </c>
       <c r="N21">
-        <v>-2.907505916000001</v>
+        <v>-3.081427280000001</v>
       </c>
       <c r="O21">
-        <v>-0.6396513015200002</v>
+        <v>-0.6779140016000001</v>
       </c>
       <c r="P21">
-        <v>-2.26785461448</v>
+        <v>-2.403513278400001</v>
       </c>
       <c r="Q21">
-        <v>-2.153854614480001</v>
+        <v>-2.289513278400001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1601130578027595</v>
+        <v>0.1615419710252941</v>
       </c>
       <c r="T21">
-        <v>1.663394277254827</v>
+        <v>1.684186705720513</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.02643057758713965</v>
+        <v>0.02510904870778267</v>
       </c>
       <c r="W21">
-        <v>0.2295676698049525</v>
+        <v>0.2298792863147049</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.1201389890324529</v>
+        <v>0.1141320395808304</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3293,22 +3293,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1752094340831762</v>
+        <v>0.1771094340831762</v>
       </c>
       <c r="C22">
-        <v>38.58117891505884</v>
+        <v>37.08650723590623</v>
       </c>
       <c r="D22">
-        <v>52.32277891505885</v>
+        <v>51.56568723590623</v>
       </c>
       <c r="E22">
-        <v>14.6936</v>
+        <v>15.43118</v>
       </c>
       <c r="F22">
-        <v>14.7516</v>
+        <v>15.48918</v>
       </c>
       <c r="G22">
         <v>1.01</v>
@@ -3329,37 +3329,37 @@
         <v>0.397</v>
       </c>
       <c r="M22">
-        <v>3.478427280000001</v>
+        <v>3.652348644000001</v>
       </c>
       <c r="N22">
-        <v>-3.081427280000001</v>
+        <v>-3.255348644000001</v>
       </c>
       <c r="O22">
-        <v>-0.6779140016000001</v>
+        <v>-0.7161767016800001</v>
       </c>
       <c r="P22">
-        <v>-2.403513278400001</v>
+        <v>-2.53917194232</v>
       </c>
       <c r="Q22">
-        <v>-2.289513278400001</v>
+        <v>-2.42517194232</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1615419710252941</v>
+        <v>0.1630070592661206</v>
       </c>
       <c r="T22">
-        <v>1.684186705720513</v>
+        <v>1.705505524780266</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.02510904870778267</v>
+        <v>0.02391337972169778</v>
       </c>
       <c r="W22">
-        <v>0.2298792863147049</v>
+        <v>0.2301612250616237</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.1141320395808304</v>
+        <v>0.1086971805531718</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3375,22 +3375,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1771094340831762</v>
+        <v>0.1790094340831762</v>
       </c>
       <c r="C23">
-        <v>37.08650723590624</v>
+        <v>35.6134327386693</v>
       </c>
       <c r="D23">
-        <v>51.56568723590625</v>
+        <v>50.8301927386693</v>
       </c>
       <c r="E23">
-        <v>15.43118</v>
+        <v>16.16876</v>
       </c>
       <c r="F23">
-        <v>15.48918</v>
+        <v>16.22676</v>
       </c>
       <c r="G23">
         <v>1.01</v>
@@ -3411,37 +3411,37 @@
         <v>0.397</v>
       </c>
       <c r="M23">
-        <v>3.652348644</v>
+        <v>3.826270008000001</v>
       </c>
       <c r="N23">
-        <v>-3.255348644000001</v>
+        <v>-3.429270008</v>
       </c>
       <c r="O23">
-        <v>-0.7161767016800001</v>
+        <v>-0.7544394017600001</v>
       </c>
       <c r="P23">
-        <v>-2.53917194232</v>
+        <v>-2.67483060624</v>
       </c>
       <c r="Q23">
-        <v>-2.42517194232</v>
+        <v>-2.560830606240001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1630070592661206</v>
+        <v>0.1645097138720965</v>
       </c>
       <c r="T23">
-        <v>1.705505524780266</v>
+        <v>1.727370980226167</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.02391337972169778</v>
+        <v>0.02282640791616606</v>
       </c>
       <c r="W23">
-        <v>0.2301612250616237</v>
+        <v>0.230417533013368</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.1086971805531717</v>
+        <v>0.1037563996189367</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3457,22 +3457,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1790094340831762</v>
+        <v>0.1809094340831762</v>
       </c>
       <c r="C24">
-        <v>35.6134327386693</v>
+        <v>34.1610442809267</v>
       </c>
       <c r="D24">
-        <v>50.8301927386693</v>
+        <v>50.1153842809267</v>
       </c>
       <c r="E24">
-        <v>16.16876</v>
+        <v>16.90634</v>
       </c>
       <c r="F24">
-        <v>16.22676</v>
+        <v>16.96434</v>
       </c>
       <c r="G24">
         <v>1.01</v>
@@ -3493,37 +3493,37 @@
         <v>0.397</v>
       </c>
       <c r="M24">
-        <v>3.826270008000001</v>
+        <v>4.000191372000001</v>
       </c>
       <c r="N24">
-        <v>-3.429270008</v>
+        <v>-3.603191372</v>
       </c>
       <c r="O24">
-        <v>-0.7544394017600001</v>
+        <v>-0.7927021018400001</v>
       </c>
       <c r="P24">
-        <v>-2.67483060624</v>
+        <v>-2.81048927016</v>
       </c>
       <c r="Q24">
-        <v>-2.560830606240001</v>
+        <v>-2.69648927016</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1645097138720965</v>
+        <v>0.166051398467838</v>
       </c>
       <c r="T24">
-        <v>1.727370980226167</v>
+        <v>1.749804369579753</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.02282640791616606</v>
+        <v>0.02183395539807189</v>
       </c>
       <c r="W24">
-        <v>0.230417533013368</v>
+        <v>0.2306515533171347</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1037563996189367</v>
+        <v>0.09924525180941768</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3539,22 +3539,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1809094340831762</v>
+        <v>0.1828094340831762</v>
       </c>
       <c r="C25">
-        <v>34.1610442809267</v>
+        <v>32.72848126190367</v>
       </c>
       <c r="D25">
-        <v>50.1153842809267</v>
+        <v>49.42040126190368</v>
       </c>
       <c r="E25">
-        <v>16.90634</v>
+        <v>17.64392</v>
       </c>
       <c r="F25">
-        <v>16.96434</v>
+        <v>17.70192</v>
       </c>
       <c r="G25">
         <v>1.01</v>
@@ -3575,37 +3575,37 @@
         <v>0.397</v>
       </c>
       <c r="M25">
-        <v>4.000191372000001</v>
+        <v>4.174112736000001</v>
       </c>
       <c r="N25">
-        <v>-3.603191372</v>
+        <v>-3.777112736000001</v>
       </c>
       <c r="O25">
-        <v>-0.7927021018400001</v>
+        <v>-0.8309648019200002</v>
       </c>
       <c r="P25">
-        <v>-2.81048927016</v>
+        <v>-2.946147934080001</v>
       </c>
       <c r="Q25">
-        <v>-2.69648927016</v>
+        <v>-2.832147934080001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.166051398467838</v>
+        <v>0.1676336537108358</v>
       </c>
       <c r="T25">
-        <v>1.749804369579753</v>
+        <v>1.77282811128475</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.02183395539807189</v>
+        <v>0.02092420725648556</v>
       </c>
       <c r="W25">
-        <v>0.2306515533171347</v>
+        <v>0.2308660719289207</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.09924525180941768</v>
+        <v>0.09511003298402532</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3621,22 +3621,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1828094340831762</v>
+        <v>0.1847094340831762</v>
       </c>
       <c r="C26">
-        <v>32.7284812619037</v>
+        <v>31.31493016593483</v>
       </c>
       <c r="D26">
-        <v>49.4204012619037</v>
+        <v>48.74443016593484</v>
       </c>
       <c r="E26">
-        <v>17.64392</v>
+        <v>18.3815</v>
       </c>
       <c r="F26">
-        <v>17.70192</v>
+        <v>18.4395</v>
       </c>
       <c r="G26">
         <v>1.01</v>
@@ -3657,37 +3657,37 @@
         <v>0.397</v>
       </c>
       <c r="M26">
-        <v>4.174112736000001</v>
+        <v>4.3480341</v>
       </c>
       <c r="N26">
-        <v>-3.777112736</v>
+        <v>-3.9510341</v>
       </c>
       <c r="O26">
-        <v>-0.8309648019200001</v>
+        <v>-0.8692275020000001</v>
       </c>
       <c r="P26">
-        <v>-2.94614793408</v>
+        <v>-3.081806598</v>
       </c>
       <c r="Q26">
-        <v>-2.83214793408</v>
+        <v>-2.967806598</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1676336537108358</v>
+        <v>0.1692581024269803</v>
       </c>
       <c r="T26">
-        <v>1.77282811128475</v>
+        <v>1.796465819435213</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.02092420725648556</v>
+        <v>0.02008723896622614</v>
       </c>
       <c r="W26">
-        <v>0.2308660719289207</v>
+        <v>0.2310634290517639</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.09511003298402532</v>
+        <v>0.09130563166466432</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3703,22 +3703,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1847094340831762</v>
+        <v>0.1866094340831762</v>
       </c>
       <c r="C27">
-        <v>31.31493016593483</v>
+        <v>29.91962138576965</v>
       </c>
       <c r="D27">
-        <v>48.74443016593484</v>
+        <v>48.08670138576966</v>
       </c>
       <c r="E27">
-        <v>18.3815</v>
+        <v>19.11908</v>
       </c>
       <c r="F27">
-        <v>18.4395</v>
+        <v>19.17708</v>
       </c>
       <c r="G27">
         <v>1.01</v>
@@ -3739,37 +3739,37 @@
         <v>0.397</v>
       </c>
       <c r="M27">
-        <v>4.3480341</v>
+        <v>4.521955464000001</v>
       </c>
       <c r="N27">
-        <v>-3.9510341</v>
+        <v>-4.124955464000001</v>
       </c>
       <c r="O27">
-        <v>-0.8692275020000001</v>
+        <v>-0.9074902020800002</v>
       </c>
       <c r="P27">
-        <v>-3.081806598</v>
+        <v>-3.217465261920001</v>
       </c>
       <c r="Q27">
-        <v>-2.967806598</v>
+        <v>-3.103465261920001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1692581024269803</v>
+        <v>0.1709264551624801</v>
       </c>
       <c r="T27">
-        <v>1.796465819435213</v>
+        <v>1.820742384562716</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.02008723896622614</v>
+        <v>0.01931465285214051</v>
       </c>
       <c r="W27">
-        <v>0.2310634290517639</v>
+        <v>0.2312456048574653</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.09130563166466432</v>
+        <v>0.08779387660063875</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3785,22 +3785,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1866094340831762</v>
+        <v>0.1885094340831762</v>
       </c>
       <c r="C28">
-        <v>29.91962138576965</v>
+        <v>28.54182629964079</v>
       </c>
       <c r="D28">
-        <v>48.08670138576966</v>
+        <v>47.4464862996408</v>
       </c>
       <c r="E28">
-        <v>19.11908</v>
+        <v>19.85666000000001</v>
       </c>
       <c r="F28">
-        <v>19.17708</v>
+        <v>19.91466</v>
       </c>
       <c r="G28">
         <v>1.01</v>
@@ -3821,37 +3821,37 @@
         <v>0.397</v>
       </c>
       <c r="M28">
-        <v>4.521955464000001</v>
+        <v>4.695876828000001</v>
       </c>
       <c r="N28">
-        <v>-4.124955464000001</v>
+        <v>-4.298876828000001</v>
       </c>
       <c r="O28">
-        <v>-0.9074902020800002</v>
+        <v>-0.9457529021600002</v>
       </c>
       <c r="P28">
-        <v>-3.217465261920001</v>
+        <v>-3.353123925840001</v>
       </c>
       <c r="Q28">
-        <v>-3.103465261920001</v>
+        <v>-3.239123925840001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1709264551624801</v>
+        <v>0.1726405161921031</v>
       </c>
       <c r="T28">
-        <v>1.820742384562716</v>
+        <v>1.845684061063575</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.01931465285214051</v>
+        <v>0.01859929533909828</v>
       </c>
       <c r="W28">
-        <v>0.2312456048574653</v>
+        <v>0.2314142861590406</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.08779387660063875</v>
+        <v>0.08454225154135586</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3867,22 +3867,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1885094340831762</v>
+        <v>0.1904094340831762</v>
       </c>
       <c r="C29">
-        <v>28.54182629964079</v>
+        <v>27.18085457875578</v>
       </c>
       <c r="D29">
-        <v>47.4464862996408</v>
+        <v>46.82309457875579</v>
       </c>
       <c r="E29">
-        <v>19.85666000000001</v>
+        <v>20.59424000000001</v>
       </c>
       <c r="F29">
-        <v>19.91466</v>
+        <v>20.65224000000001</v>
       </c>
       <c r="G29">
         <v>1.01</v>
@@ -3903,37 +3903,37 @@
         <v>0.397</v>
       </c>
       <c r="M29">
-        <v>4.695876828000001</v>
+        <v>4.869798192000002</v>
       </c>
       <c r="N29">
-        <v>-4.298876828000001</v>
+        <v>-4.472798192000002</v>
       </c>
       <c r="O29">
-        <v>-0.9457529021600002</v>
+        <v>-0.9840156022400004</v>
       </c>
       <c r="P29">
-        <v>-3.353123925840001</v>
+        <v>-3.488782589760001</v>
       </c>
       <c r="Q29">
-        <v>-3.239123925840001</v>
+        <v>-3.374782589760001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1726405161921031</v>
+        <v>0.1744021900281045</v>
       </c>
       <c r="T29">
-        <v>1.845684061063575</v>
+        <v>1.871318561911681</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.01859929533909828</v>
+        <v>0.01793503479127333</v>
       </c>
       <c r="W29">
-        <v>0.2314142861590406</v>
+        <v>0.2315709187962177</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.08454225154135586</v>
+        <v>0.08152288541487884</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3949,22 +3949,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1904094340831762</v>
+        <v>0.1923094340831762</v>
       </c>
       <c r="C30">
-        <v>27.18085457875578</v>
+        <v>25.83605170429481</v>
       </c>
       <c r="D30">
-        <v>46.82309457875579</v>
+        <v>46.21587170429482</v>
       </c>
       <c r="E30">
-        <v>20.59424000000001</v>
+        <v>21.33182</v>
       </c>
       <c r="F30">
-        <v>20.65224000000001</v>
+        <v>21.38982</v>
       </c>
       <c r="G30">
         <v>1.01</v>
@@ -3985,37 +3985,37 @@
         <v>0.397</v>
       </c>
       <c r="M30">
-        <v>4.869798192000002</v>
+        <v>5.043719556000001</v>
       </c>
       <c r="N30">
-        <v>-4.472798192000002</v>
+        <v>-4.646719556000001</v>
       </c>
       <c r="O30">
-        <v>-0.9840156022400004</v>
+        <v>-1.02227830232</v>
       </c>
       <c r="P30">
-        <v>-3.488782589760001</v>
+        <v>-3.624441253680001</v>
       </c>
       <c r="Q30">
-        <v>-3.374782589760001</v>
+        <v>-3.510441253680001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1744021900281045</v>
+        <v>0.1762134884792046</v>
       </c>
       <c r="T30">
-        <v>1.871318561911681</v>
+        <v>1.897675161375225</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.01793503479127333</v>
+        <v>0.01731658531571218</v>
       </c>
       <c r="W30">
-        <v>0.2315709187962177</v>
+        <v>0.2317167491825551</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.08152288541487884</v>
+        <v>0.07871175143505549</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1923094340831762</v>
+        <v>0.1942094340831762</v>
       </c>
       <c r="C31">
-        <v>25.83605170429483</v>
+        <v>24.50679667513901</v>
       </c>
       <c r="D31">
-        <v>46.21587170429483</v>
+        <v>45.62419667513902</v>
       </c>
       <c r="E31">
-        <v>21.33182</v>
+        <v>22.0694</v>
       </c>
       <c r="F31">
-        <v>21.38982</v>
+        <v>22.1274</v>
       </c>
       <c r="G31">
         <v>1.01</v>
@@ -4067,37 +4067,37 @@
         <v>0.397</v>
       </c>
       <c r="M31">
-        <v>5.043719556</v>
+        <v>5.217640920000001</v>
       </c>
       <c r="N31">
-        <v>-4.646719556</v>
+        <v>-4.820640920000001</v>
       </c>
       <c r="O31">
-        <v>-1.02227830232</v>
+        <v>-1.0605410024</v>
       </c>
       <c r="P31">
-        <v>-3.62444125368</v>
+        <v>-3.760099917600001</v>
       </c>
       <c r="Q31">
-        <v>-3.51044125368</v>
+        <v>-3.646099917600001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1762134884792045</v>
+        <v>0.1780765383146218</v>
       </c>
       <c r="T31">
-        <v>1.897675161375225</v>
+        <v>1.924784806537729</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.01731658531571219</v>
+        <v>0.01673936580518845</v>
       </c>
       <c r="W31">
-        <v>0.2317167491825551</v>
+        <v>0.2318528575431366</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.07871175143505549</v>
+        <v>0.07608802638722023</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4113,22 +4113,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1942094340831762</v>
+        <v>0.1961094340831762</v>
       </c>
       <c r="C32">
-        <v>24.50679667513901</v>
+        <v>23.1924998894528</v>
       </c>
       <c r="D32">
-        <v>45.62419667513902</v>
+        <v>45.0474798894528</v>
       </c>
       <c r="E32">
-        <v>22.0694</v>
+        <v>22.80698</v>
       </c>
       <c r="F32">
-        <v>22.1274</v>
+        <v>22.86498</v>
       </c>
       <c r="G32">
         <v>1.01</v>
@@ -4149,37 +4149,37 @@
         <v>0.397</v>
       </c>
       <c r="M32">
-        <v>5.217640920000001</v>
+        <v>5.391562284000001</v>
       </c>
       <c r="N32">
-        <v>-4.820640920000001</v>
+        <v>-4.994562284000001</v>
       </c>
       <c r="O32">
-        <v>-1.0605410024</v>
+        <v>-1.09880370248</v>
       </c>
       <c r="P32">
-        <v>-3.760099917600001</v>
+        <v>-3.89575858152</v>
       </c>
       <c r="Q32">
-        <v>-3.646099917600001</v>
+        <v>-3.781758581520001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1780765383146218</v>
+        <v>0.1799935895945438</v>
       </c>
       <c r="T32">
-        <v>1.924784806537729</v>
+        <v>1.952680238516536</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.01673936580518845</v>
+        <v>0.01619938626308559</v>
       </c>
       <c r="W32">
-        <v>0.2318528575431366</v>
+        <v>0.2319801847191644</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.07608802638722023</v>
+        <v>0.07363357392311642</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4195,22 +4195,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1961094340831762</v>
+        <v>0.1980094340831762</v>
       </c>
       <c r="C33">
-        <v>23.1924998894528</v>
+        <v>21.89260118492894</v>
       </c>
       <c r="D33">
-        <v>45.0474798894528</v>
+        <v>44.48516118492895</v>
       </c>
       <c r="E33">
-        <v>22.80698</v>
+        <v>23.54456</v>
       </c>
       <c r="F33">
-        <v>22.86498</v>
+        <v>23.60256</v>
       </c>
       <c r="G33">
         <v>1.01</v>
@@ -4231,37 +4231,37 @@
         <v>0.397</v>
       </c>
       <c r="M33">
-        <v>5.391562284000001</v>
+        <v>5.565483648000001</v>
       </c>
       <c r="N33">
-        <v>-4.994562284000001</v>
+        <v>-5.168483648</v>
       </c>
       <c r="O33">
-        <v>-1.09880370248</v>
+        <v>-1.13706640256</v>
       </c>
       <c r="P33">
-        <v>-3.89575858152</v>
+        <v>-4.03141724544</v>
       </c>
       <c r="Q33">
-        <v>-3.781758581520001</v>
+        <v>-3.91741724544</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1799935895945438</v>
+        <v>0.1819670247356401</v>
       </c>
       <c r="T33">
-        <v>1.952680238516536</v>
+        <v>1.981396124377073</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.01619938626308559</v>
+        <v>0.01569315544236417</v>
       </c>
       <c r="W33">
-        <v>0.2319801847191644</v>
+        <v>0.2320995539466905</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.07363357392311642</v>
+        <v>0.07133252473801899</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4277,22 +4277,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1980094340831762</v>
+        <v>0.1999094340831762</v>
       </c>
       <c r="C34">
-        <v>21.89260118492894</v>
+        <v>20.6065680240034</v>
       </c>
       <c r="D34">
-        <v>44.48516118492895</v>
+        <v>43.93670802400341</v>
       </c>
       <c r="E34">
-        <v>23.54456</v>
+        <v>24.28214000000001</v>
       </c>
       <c r="F34">
-        <v>23.60256</v>
+        <v>24.34014000000001</v>
       </c>
       <c r="G34">
         <v>1.01</v>
@@ -4313,37 +4313,37 @@
         <v>0.397</v>
       </c>
       <c r="M34">
-        <v>5.565483648000001</v>
+        <v>5.739405012000002</v>
       </c>
       <c r="N34">
-        <v>-5.168483648</v>
+        <v>-5.342405012000001</v>
       </c>
       <c r="O34">
-        <v>-1.13706640256</v>
+        <v>-1.17532910264</v>
       </c>
       <c r="P34">
-        <v>-4.03141724544</v>
+        <v>-4.167075909360001</v>
       </c>
       <c r="Q34">
-        <v>-3.91741724544</v>
+        <v>-4.053075909360001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1819670247356401</v>
+        <v>0.1839993683884108</v>
       </c>
       <c r="T34">
-        <v>1.981396124377073</v>
+        <v>2.010969200860313</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.01569315544236417</v>
+        <v>0.01521760527744404</v>
       </c>
       <c r="W34">
-        <v>0.2320995539466905</v>
+        <v>0.2322116886755787</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.07133252473801899</v>
+        <v>0.06917093307929112</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4359,22 +4359,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1999094340831762</v>
+        <v>0.2018094340831762</v>
       </c>
       <c r="C35">
-        <v>20.6065680240034</v>
+        <v>19.33389381168096</v>
       </c>
       <c r="D35">
-        <v>43.93670802400341</v>
+        <v>43.40161381168097</v>
       </c>
       <c r="E35">
-        <v>24.28214000000001</v>
+        <v>25.01972000000001</v>
       </c>
       <c r="F35">
-        <v>24.34014000000001</v>
+        <v>25.07772000000001</v>
       </c>
       <c r="G35">
         <v>1.01</v>
@@ -4395,37 +4395,37 @@
         <v>0.397</v>
       </c>
       <c r="M35">
-        <v>5.739405012000002</v>
+        <v>5.913326376000001</v>
       </c>
       <c r="N35">
-        <v>-5.342405012000001</v>
+        <v>-5.516326376000001</v>
       </c>
       <c r="O35">
-        <v>-1.17532910264</v>
+        <v>-1.21359180272</v>
       </c>
       <c r="P35">
-        <v>-4.167075909360001</v>
+        <v>-4.30273457328</v>
       </c>
       <c r="Q35">
-        <v>-4.053075909360001</v>
+        <v>-4.188734573280001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1839993683884108</v>
+        <v>0.1860932982124776</v>
       </c>
       <c r="T35">
-        <v>2.010969200860313</v>
+        <v>2.041438431176379</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.01521760527744404</v>
+        <v>0.01477002865163687</v>
       </c>
       <c r="W35">
-        <v>0.2322116886755787</v>
+        <v>0.232317227243944</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.06917093307929112</v>
+        <v>0.06713649387107667</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4441,22 +4441,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2018094340831762</v>
+        <v>0.2037094340831762</v>
       </c>
       <c r="C36">
-        <v>19.33389381168096</v>
+        <v>18.07409633480267</v>
       </c>
       <c r="D36">
-        <v>43.40161381168097</v>
+        <v>42.87939633480268</v>
       </c>
       <c r="E36">
-        <v>25.01972000000001</v>
+        <v>25.7573</v>
       </c>
       <c r="F36">
-        <v>25.07772000000001</v>
+        <v>25.8153</v>
       </c>
       <c r="G36">
         <v>1.01</v>
@@ -4477,37 +4477,37 @@
         <v>0.397</v>
       </c>
       <c r="M36">
-        <v>5.913326376000001</v>
+        <v>6.087247740000001</v>
       </c>
       <c r="N36">
-        <v>-5.516326376000001</v>
+        <v>-5.690247740000001</v>
       </c>
       <c r="O36">
-        <v>-1.21359180272</v>
+        <v>-1.2518545028</v>
       </c>
       <c r="P36">
-        <v>-4.30273457328</v>
+        <v>-4.438393237200001</v>
       </c>
       <c r="Q36">
-        <v>-4.188734573280001</v>
+        <v>-4.324393237200001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1860932982124776</v>
+        <v>0.1882516566465157</v>
       </c>
       <c r="T36">
-        <v>2.041438431176379</v>
+        <v>2.0728451762714</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.01477002865163687</v>
+        <v>0.01434802783301867</v>
       </c>
       <c r="W36">
-        <v>0.232317227243944</v>
+        <v>0.2324167350369742</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.06713649387107667</v>
+        <v>0.06521830833190312</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4523,22 +4523,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2037094340831762</v>
+        <v>0.2056094340831762</v>
       </c>
       <c r="C37">
-        <v>18.07409633480267</v>
+        <v>16.82671631264801</v>
       </c>
       <c r="D37">
-        <v>42.87939633480268</v>
+        <v>42.36959631264802</v>
       </c>
       <c r="E37">
-        <v>25.7573</v>
+        <v>26.49488000000001</v>
       </c>
       <c r="F37">
-        <v>25.8153</v>
+        <v>26.55288000000001</v>
       </c>
       <c r="G37">
         <v>1.01</v>
@@ -4559,37 +4559,37 @@
         <v>0.397</v>
       </c>
       <c r="M37">
-        <v>6.087247740000001</v>
+        <v>6.261169104000001</v>
       </c>
       <c r="N37">
-        <v>-5.690247740000001</v>
+        <v>-5.864169104000001</v>
       </c>
       <c r="O37">
-        <v>-1.2518545028</v>
+        <v>-1.29011720288</v>
       </c>
       <c r="P37">
-        <v>-4.438393237200001</v>
+        <v>-4.574051901120001</v>
       </c>
       <c r="Q37">
-        <v>-4.324393237200001</v>
+        <v>-4.460051901120001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1882516566465157</v>
+        <v>0.1904774637816176</v>
       </c>
       <c r="T37">
-        <v>2.0728451762714</v>
+        <v>2.105233382150641</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.01434802783301867</v>
+        <v>0.01394947150432371</v>
       </c>
       <c r="W37">
-        <v>0.2324167350369742</v>
+        <v>0.2325107146192805</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.06521830833190312</v>
+        <v>0.06340668865601684</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4605,22 +4605,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2056094340831762</v>
+        <v>0.2075094340831762</v>
       </c>
       <c r="C38">
-        <v>16.82671631264802</v>
+        <v>15.59131604971503</v>
       </c>
       <c r="D38">
-        <v>42.36959631264802</v>
+        <v>41.87177604971504</v>
       </c>
       <c r="E38">
-        <v>26.49488</v>
+        <v>27.23246</v>
       </c>
       <c r="F38">
-        <v>26.55288</v>
+        <v>27.29046</v>
       </c>
       <c r="G38">
         <v>1.01</v>
@@ -4641,37 +4641,37 @@
         <v>0.397</v>
       </c>
       <c r="M38">
-        <v>6.261169104</v>
+        <v>6.435090468000001</v>
       </c>
       <c r="N38">
-        <v>-5.864169104</v>
+        <v>-6.038090468000001</v>
       </c>
       <c r="O38">
-        <v>-1.29011720288</v>
+        <v>-1.32837990296</v>
       </c>
       <c r="P38">
-        <v>-4.57405190112</v>
+        <v>-4.709710565040001</v>
       </c>
       <c r="Q38">
-        <v>-4.46005190112</v>
+        <v>-4.595710565040001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1904774637816176</v>
+        <v>0.1927739314606909</v>
       </c>
       <c r="T38">
-        <v>2.105233382150641</v>
+        <v>2.138649785041921</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.01394947150432371</v>
+        <v>0.01357245876096361</v>
       </c>
       <c r="W38">
-        <v>0.2325107146192805</v>
+        <v>0.2325996142241648</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.06340668865601684</v>
+        <v>0.06169299436801645</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4687,22 +4687,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2075094340831762</v>
+        <v>0.2094094340831762</v>
       </c>
       <c r="C39">
-        <v>15.59131604971503</v>
+        <v>14.36747818237217</v>
       </c>
       <c r="D39">
-        <v>41.87177604971504</v>
+        <v>41.38551818237217</v>
       </c>
       <c r="E39">
-        <v>27.23246</v>
+        <v>27.97004</v>
       </c>
       <c r="F39">
-        <v>27.29046</v>
+        <v>28.02804</v>
       </c>
       <c r="G39">
         <v>1.01</v>
@@ -4723,37 +4723,37 @@
         <v>0.397</v>
       </c>
       <c r="M39">
-        <v>6.435090468000001</v>
+        <v>6.609011832000001</v>
       </c>
       <c r="N39">
-        <v>-6.038090468000001</v>
+        <v>-6.212011832000001</v>
       </c>
       <c r="O39">
-        <v>-1.32837990296</v>
+        <v>-1.36664260304</v>
       </c>
       <c r="P39">
-        <v>-4.709710565040001</v>
+        <v>-4.845369228960001</v>
       </c>
       <c r="Q39">
-        <v>-4.595710565040001</v>
+        <v>-4.731369228960001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1927739314606909</v>
+        <v>0.1951444787423149</v>
       </c>
       <c r="T39">
-        <v>2.138649785041921</v>
+        <v>2.173144136413565</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.01357245876096361</v>
+        <v>0.01321528879356983</v>
       </c>
       <c r="W39">
-        <v>0.2325996142241648</v>
+        <v>0.2326838349024762</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.06169299436801645</v>
+        <v>0.06006949451622656</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4769,22 +4769,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2094094340831762</v>
+        <v>0.2113094340831762</v>
       </c>
       <c r="C40">
-        <v>14.36747818237217</v>
+        <v>13.15480451183863</v>
       </c>
       <c r="D40">
-        <v>41.38551818237217</v>
+        <v>40.91042451183863</v>
       </c>
       <c r="E40">
-        <v>27.97004</v>
+        <v>28.70762000000001</v>
       </c>
       <c r="F40">
-        <v>28.02804</v>
+        <v>28.76562000000001</v>
       </c>
       <c r="G40">
         <v>1.01</v>
@@ -4805,37 +4805,37 @@
         <v>0.397</v>
       </c>
       <c r="M40">
-        <v>6.609011832000001</v>
+        <v>6.782933196000002</v>
       </c>
       <c r="N40">
-        <v>-6.212011832000001</v>
+        <v>-6.385933196000002</v>
       </c>
       <c r="O40">
-        <v>-1.36664260304</v>
+        <v>-1.40490530312</v>
       </c>
       <c r="P40">
-        <v>-4.845369228960001</v>
+        <v>-4.981027892880001</v>
       </c>
       <c r="Q40">
-        <v>-4.731369228960001</v>
+        <v>-4.867027892880001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1951444787423149</v>
+        <v>0.1975927488856315</v>
       </c>
       <c r="T40">
-        <v>2.173144136413565</v>
+        <v>2.208769450125262</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.01321528879356983</v>
+        <v>0.01287643523476034</v>
       </c>
       <c r="W40">
-        <v>0.2326838349024762</v>
+        <v>0.2327637365716435</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.06006949451622656</v>
+        <v>0.0585292510670925</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4851,22 +4851,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2113094340831762</v>
+        <v>0.2132094340831762</v>
       </c>
       <c r="C41">
-        <v>13.15480451183863</v>
+        <v>11.95291491663459</v>
       </c>
       <c r="D41">
-        <v>40.91042451183863</v>
+        <v>40.4461149166346</v>
       </c>
       <c r="E41">
-        <v>28.70762000000001</v>
+        <v>29.44520000000001</v>
       </c>
       <c r="F41">
-        <v>28.76562000000001</v>
+        <v>29.50320000000001</v>
       </c>
       <c r="G41">
         <v>1.01</v>
@@ -4887,37 +4887,37 @@
         <v>0.397</v>
       </c>
       <c r="M41">
-        <v>6.782933196000002</v>
+        <v>6.956854560000002</v>
       </c>
       <c r="N41">
-        <v>-6.385933196000002</v>
+        <v>-6.559854560000002</v>
       </c>
       <c r="O41">
-        <v>-1.40490530312</v>
+        <v>-1.4431680032</v>
       </c>
       <c r="P41">
-        <v>-4.981027892880001</v>
+        <v>-5.116686556800001</v>
       </c>
       <c r="Q41">
-        <v>-4.867027892880001</v>
+        <v>-5.002686556800001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1975927488856315</v>
+        <v>0.2001226280337254</v>
       </c>
       <c r="T41">
-        <v>2.208769450125262</v>
+        <v>2.245582274294017</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.01287643523476034</v>
+        <v>0.01255452435389133</v>
       </c>
       <c r="W41">
-        <v>0.2327637365716435</v>
+        <v>0.2328396431573524</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.0585292510670925</v>
+        <v>0.05706601979041515</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4933,22 +4933,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2132094340831762</v>
+        <v>0.2151094340831762</v>
       </c>
       <c r="C42">
-        <v>11.95291491663459</v>
+        <v>10.7614463382589</v>
       </c>
       <c r="D42">
-        <v>40.4461149166346</v>
+        <v>39.99222633825891</v>
       </c>
       <c r="E42">
-        <v>29.44520000000001</v>
+        <v>30.18278000000001</v>
       </c>
       <c r="F42">
-        <v>29.50320000000001</v>
+        <v>30.24078000000001</v>
       </c>
       <c r="G42">
         <v>1.01</v>
@@ -4969,37 +4969,37 @@
         <v>0.397</v>
       </c>
       <c r="M42">
-        <v>6.956854560000002</v>
+        <v>7.130775924000003</v>
       </c>
       <c r="N42">
-        <v>-6.559854560000002</v>
+        <v>-6.733775924000002</v>
       </c>
       <c r="O42">
-        <v>-1.4431680032</v>
+        <v>-1.48143070328</v>
       </c>
       <c r="P42">
-        <v>-5.116686556800001</v>
+        <v>-5.252345220720002</v>
       </c>
       <c r="Q42">
-        <v>-5.002686556800001</v>
+        <v>-5.138345220720002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2001226280337254</v>
+        <v>0.2027382657970089</v>
       </c>
       <c r="T42">
-        <v>2.245582274294017</v>
+        <v>2.283642990807475</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.01255452435389133</v>
+        <v>0.01224831644282081</v>
       </c>
       <c r="W42">
-        <v>0.2328396431573524</v>
+        <v>0.2329118469827829</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.05706601979041515</v>
+        <v>0.05567416564918559</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5015,22 +5015,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2151094340831762</v>
+        <v>0.2170094340831762</v>
       </c>
       <c r="C43">
-        <v>10.7614463382589</v>
+        <v>9.580051834405236</v>
       </c>
       <c r="D43">
-        <v>39.99222633825891</v>
+        <v>39.54841183440524</v>
       </c>
       <c r="E43">
-        <v>30.18278000000001</v>
+        <v>30.92036000000001</v>
       </c>
       <c r="F43">
-        <v>30.24078000000001</v>
+        <v>30.97836000000001</v>
       </c>
       <c r="G43">
         <v>1.01</v>
@@ -5051,37 +5051,37 @@
         <v>0.397</v>
       </c>
       <c r="M43">
-        <v>7.130775924000003</v>
+        <v>7.304697288000002</v>
       </c>
       <c r="N43">
-        <v>-6.733775924000002</v>
+        <v>-6.907697288000001</v>
       </c>
       <c r="O43">
-        <v>-1.48143070328</v>
+        <v>-1.51969340336</v>
       </c>
       <c r="P43">
-        <v>-5.252345220720002</v>
+        <v>-5.388003884640002</v>
       </c>
       <c r="Q43">
-        <v>-5.138345220720002</v>
+        <v>-5.274003884640002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2027382657970089</v>
+        <v>0.2054440979659228</v>
       </c>
       <c r="T43">
-        <v>2.283642990807475</v>
+        <v>2.323016145821397</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.01224831644282081</v>
+        <v>0.01195668986084889</v>
       </c>
       <c r="W43">
-        <v>0.2329118469827829</v>
+        <v>0.2329806125308118</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.05567416564918559</v>
+        <v>0.0543485902765859</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2170094340831762</v>
+        <v>0.2189094340831762</v>
       </c>
       <c r="C44">
-        <v>9.580051834405239</v>
+        <v>8.408399694528306</v>
       </c>
       <c r="D44">
-        <v>39.54841183440524</v>
+        <v>39.11433969452831</v>
       </c>
       <c r="E44">
-        <v>30.92036</v>
+        <v>31.65794</v>
       </c>
       <c r="F44">
-        <v>30.97836</v>
+        <v>31.71594</v>
       </c>
       <c r="G44">
         <v>1.01</v>
@@ -5133,37 +5133,37 @@
         <v>0.397</v>
       </c>
       <c r="M44">
-        <v>7.304697288000001</v>
+        <v>7.478618652000002</v>
       </c>
       <c r="N44">
-        <v>-6.907697288</v>
+        <v>-7.081618652000001</v>
       </c>
       <c r="O44">
-        <v>-1.51969340336</v>
+        <v>-1.55795610344</v>
       </c>
       <c r="P44">
-        <v>-5.388003884640001</v>
+        <v>-5.523662548560001</v>
       </c>
       <c r="Q44">
-        <v>-5.274003884640001</v>
+        <v>-5.409662548560001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2054440979659228</v>
+        <v>0.2082448716144478</v>
       </c>
       <c r="T44">
-        <v>2.323016145821396</v>
+        <v>2.363770815046333</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.01195668986084889</v>
+        <v>0.01167862730594543</v>
       </c>
       <c r="W44">
-        <v>0.2329806125308118</v>
+        <v>0.2330461796812581</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.0543485902765859</v>
+        <v>0.05308466957247926</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5179,22 +5179,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2189094340831762</v>
+        <v>0.2208094340831762</v>
       </c>
       <c r="C45">
-        <v>8.408399694528306</v>
+        <v>7.246172613021351</v>
       </c>
       <c r="D45">
-        <v>39.11433969452831</v>
+        <v>38.68969261302136</v>
       </c>
       <c r="E45">
-        <v>31.65794</v>
+        <v>32.39552</v>
       </c>
       <c r="F45">
-        <v>31.71594</v>
+        <v>32.45352</v>
       </c>
       <c r="G45">
         <v>1.01</v>
@@ -5215,37 +5215,37 @@
         <v>0.397</v>
       </c>
       <c r="M45">
-        <v>7.478618652000002</v>
+        <v>7.652540016000001</v>
       </c>
       <c r="N45">
-        <v>-7.081618652000001</v>
+        <v>-7.255540016000001</v>
       </c>
       <c r="O45">
-        <v>-1.55795610344</v>
+        <v>-1.59621880352</v>
       </c>
       <c r="P45">
-        <v>-5.523662548560001</v>
+        <v>-5.659321212480001</v>
       </c>
       <c r="Q45">
-        <v>-5.409662548560001</v>
+        <v>-5.545321212480001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2082448716144478</v>
+        <v>0.2111456728932772</v>
       </c>
       <c r="T45">
-        <v>2.363770815046333</v>
+        <v>2.405981008172161</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.01167862730594543</v>
+        <v>0.01141320395808303</v>
       </c>
       <c r="W45">
-        <v>0.2330461796812581</v>
+        <v>0.2331087665066841</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.05308466957247926</v>
+        <v>0.05187819980946839</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5261,22 +5261,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2208094340831762</v>
+        <v>0.2227094340831762</v>
       </c>
       <c r="C46">
-        <v>7.246172613021351</v>
+        <v>6.09306691567398</v>
       </c>
       <c r="D46">
-        <v>38.68969261302136</v>
+        <v>38.27416691567399</v>
       </c>
       <c r="E46">
-        <v>32.39552</v>
+        <v>33.13310000000001</v>
       </c>
       <c r="F46">
-        <v>32.45352</v>
+        <v>33.19110000000001</v>
       </c>
       <c r="G46">
         <v>1.01</v>
@@ -5297,37 +5297,37 @@
         <v>0.397</v>
       </c>
       <c r="M46">
-        <v>7.652540016000001</v>
+        <v>7.826461380000001</v>
       </c>
       <c r="N46">
-        <v>-7.255540016000001</v>
+        <v>-7.429461380000001</v>
       </c>
       <c r="O46">
-        <v>-1.59621880352</v>
+        <v>-1.6344815036</v>
       </c>
       <c r="P46">
-        <v>-5.659321212480001</v>
+        <v>-5.794979876400001</v>
       </c>
       <c r="Q46">
-        <v>-5.545321212480001</v>
+        <v>-5.680979876400001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2111456728932772</v>
+        <v>0.2141519578549732</v>
       </c>
       <c r="T46">
-        <v>2.405981008172161</v>
+        <v>2.449726117411654</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.01141320395808303</v>
+        <v>0.01115957720345897</v>
       </c>
       <c r="W46">
-        <v>0.2331087665066841</v>
+        <v>0.2331685716954244</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.05187819980946839</v>
+        <v>0.05072535092481345</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5343,22 +5343,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2227094340831762</v>
+        <v>0.2246094340831762</v>
       </c>
       <c r="C47">
-        <v>6.09306691567398</v>
+        <v>4.948791835447089</v>
       </c>
       <c r="D47">
-        <v>38.27416691567399</v>
+        <v>37.8674718354471</v>
       </c>
       <c r="E47">
-        <v>33.13310000000001</v>
+        <v>33.87068000000001</v>
       </c>
       <c r="F47">
-        <v>33.19110000000001</v>
+        <v>33.92868000000001</v>
       </c>
       <c r="G47">
         <v>1.01</v>
@@ -5379,37 +5379,37 @@
         <v>0.397</v>
       </c>
       <c r="M47">
-        <v>7.826461380000001</v>
+        <v>8.000382744000001</v>
       </c>
       <c r="N47">
-        <v>-7.429461380000001</v>
+        <v>-7.603382744000001</v>
       </c>
       <c r="O47">
-        <v>-1.6344815036</v>
+        <v>-1.67274420368</v>
       </c>
       <c r="P47">
-        <v>-5.794979876400001</v>
+        <v>-5.93063854032</v>
       </c>
       <c r="Q47">
-        <v>-5.680979876400001</v>
+        <v>-5.81663854032</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2141519578549732</v>
+        <v>0.2172695867041393</v>
       </c>
       <c r="T47">
-        <v>2.449726117411654</v>
+        <v>2.495091415882241</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.01115957720345897</v>
+        <v>0.01091697769903594</v>
       </c>
       <c r="W47">
-        <v>0.2331685716954244</v>
+        <v>0.2332257766585673</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.05072535092481345</v>
+        <v>0.04962262590470889</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5425,22 +5425,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2246094340831762</v>
+        <v>0.2265094340831762</v>
       </c>
       <c r="C48">
-        <v>4.948791835447089</v>
+        <v>3.813068833935446</v>
       </c>
       <c r="D48">
-        <v>37.8674718354471</v>
+        <v>37.46932883393546</v>
       </c>
       <c r="E48">
-        <v>33.87068000000001</v>
+        <v>34.60826000000001</v>
       </c>
       <c r="F48">
-        <v>33.92868000000001</v>
+        <v>34.66626000000001</v>
       </c>
       <c r="G48">
         <v>1.01</v>
@@ -5461,37 +5461,37 @@
         <v>0.397</v>
       </c>
       <c r="M48">
-        <v>8.000382744000001</v>
+        <v>8.174304108000003</v>
       </c>
       <c r="N48">
-        <v>-7.603382744000001</v>
+        <v>-7.777304108000003</v>
       </c>
       <c r="O48">
-        <v>-1.67274420368</v>
+        <v>-1.711006903760001</v>
       </c>
       <c r="P48">
-        <v>-5.93063854032</v>
+        <v>-6.066297204240002</v>
       </c>
       <c r="Q48">
-        <v>-5.81663854032</v>
+        <v>-5.952297204240002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2172695867041393</v>
+        <v>0.2205048619249722</v>
       </c>
       <c r="T48">
-        <v>2.495091415882241</v>
+        <v>2.542168612408321</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.01091697769903594</v>
+        <v>0.01068470157777986</v>
       </c>
       <c r="W48">
-        <v>0.2332257766585673</v>
+        <v>0.2332805473679595</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.04962262590470889</v>
+        <v>0.04856682535354484</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5507,22 +5507,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2265094340831762</v>
+        <v>0.2284094340831762</v>
       </c>
       <c r="C49">
-        <v>3.813068833935446</v>
+        <v>2.685630965190001</v>
       </c>
       <c r="D49">
-        <v>37.46932883393546</v>
+        <v>37.07947096519001</v>
       </c>
       <c r="E49">
-        <v>34.60826000000001</v>
+        <v>35.34584000000001</v>
       </c>
       <c r="F49">
-        <v>34.66626000000001</v>
+        <v>35.40384000000001</v>
       </c>
       <c r="G49">
         <v>1.01</v>
@@ -5543,37 +5543,37 @@
         <v>0.397</v>
       </c>
       <c r="M49">
-        <v>8.174304108000003</v>
+        <v>8.348225472000003</v>
       </c>
       <c r="N49">
-        <v>-7.777304108000003</v>
+        <v>-7.951225472000003</v>
       </c>
       <c r="O49">
-        <v>-1.711006903760001</v>
+        <v>-1.749269603840001</v>
       </c>
       <c r="P49">
-        <v>-6.066297204240002</v>
+        <v>-6.201955868160002</v>
       </c>
       <c r="Q49">
-        <v>-5.952297204240002</v>
+        <v>-6.087955868160003</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2205048619249722</v>
+        <v>0.2238645708081447</v>
       </c>
       <c r="T49">
-        <v>2.542168612408321</v>
+        <v>2.59105647033925</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01068470157777986</v>
+        <v>0.01046210362824278</v>
       </c>
       <c r="W49">
-        <v>0.2332805473679595</v>
+        <v>0.2333330359644604</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.04856682535354484</v>
+        <v>0.04755501649201266</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5589,22 +5589,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2284094340831762</v>
+        <v>0.2303094340831762</v>
       </c>
       <c r="C50">
-        <v>2.685630965190008</v>
+        <v>1.566222278847057</v>
       </c>
       <c r="D50">
-        <v>37.07947096519001</v>
+        <v>36.69764227884706</v>
       </c>
       <c r="E50">
-        <v>35.34584</v>
+        <v>36.08342</v>
       </c>
       <c r="F50">
-        <v>35.40384</v>
+        <v>36.14142</v>
       </c>
       <c r="G50">
         <v>1.01</v>
@@ -5625,37 +5625,37 @@
         <v>0.397</v>
       </c>
       <c r="M50">
-        <v>8.348225472000001</v>
+        <v>8.522146836000001</v>
       </c>
       <c r="N50">
-        <v>-7.951225472000001</v>
+        <v>-8.125146836000001</v>
       </c>
       <c r="O50">
-        <v>-1.74926960384</v>
+        <v>-1.78753230392</v>
       </c>
       <c r="P50">
-        <v>-6.201955868160001</v>
+        <v>-6.337614532080001</v>
       </c>
       <c r="Q50">
-        <v>-6.087955868160001</v>
+        <v>-6.223614532080001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2238645708081447</v>
+        <v>0.2273560329808534</v>
       </c>
       <c r="T50">
-        <v>2.59105647033925</v>
+        <v>2.641861499169431</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01046210362824278</v>
+        <v>0.01024859130929905</v>
       </c>
       <c r="W50">
-        <v>0.2333330359644604</v>
+        <v>0.2333833821692673</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.04755501649201266</v>
+        <v>0.04658450595135932</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5671,22 +5671,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2303094340831762</v>
+        <v>0.2322094340831762</v>
       </c>
       <c r="C51">
-        <v>1.566222278847057</v>
+        <v>0.454597259759133</v>
       </c>
       <c r="D51">
-        <v>36.69764227884706</v>
+        <v>36.32359725975914</v>
       </c>
       <c r="E51">
-        <v>36.08342</v>
+        <v>36.82100000000001</v>
       </c>
       <c r="F51">
-        <v>36.14142</v>
+        <v>36.879</v>
       </c>
       <c r="G51">
         <v>1.01</v>
@@ -5707,37 +5707,37 @@
         <v>0.397</v>
       </c>
       <c r="M51">
-        <v>8.522146836000001</v>
+        <v>8.696068200000001</v>
       </c>
       <c r="N51">
-        <v>-8.125146836000001</v>
+        <v>-8.299068200000001</v>
       </c>
       <c r="O51">
-        <v>-1.78753230392</v>
+        <v>-1.825795004</v>
       </c>
       <c r="P51">
-        <v>-6.337614532080001</v>
+        <v>-6.473273196000001</v>
       </c>
       <c r="Q51">
-        <v>-6.223614532080001</v>
+        <v>-6.359273196000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2273560329808534</v>
+        <v>0.2309871536404705</v>
       </c>
       <c r="T51">
-        <v>2.641861499169431</v>
+        <v>2.69469872915282</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01024859130929905</v>
+        <v>0.01004361948311307</v>
       </c>
       <c r="W51">
-        <v>0.2333833821692673</v>
+        <v>0.233431714525882</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.04658450595135932</v>
+        <v>0.04565281583233216</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5753,22 +5753,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2322094340831762</v>
+        <v>0.2341094340831762</v>
       </c>
       <c r="C52">
-        <v>0.454597259759133</v>
+        <v>-0.6494796984498663</v>
       </c>
       <c r="D52">
-        <v>36.32359725975914</v>
+        <v>35.95710030155014</v>
       </c>
       <c r="E52">
-        <v>36.82100000000001</v>
+        <v>37.55858000000001</v>
       </c>
       <c r="F52">
-        <v>36.879</v>
+        <v>37.61658000000001</v>
       </c>
       <c r="G52">
         <v>1.01</v>
@@ -5789,37 +5789,37 @@
         <v>0.397</v>
       </c>
       <c r="M52">
-        <v>8.696068200000001</v>
+        <v>8.869989564000003</v>
       </c>
       <c r="N52">
-        <v>-8.299068200000001</v>
+        <v>-8.472989564000002</v>
       </c>
       <c r="O52">
-        <v>-1.825795004</v>
+        <v>-1.864057704080001</v>
       </c>
       <c r="P52">
-        <v>-6.473273196000001</v>
+        <v>-6.608931859920002</v>
       </c>
       <c r="Q52">
-        <v>-6.359273196000001</v>
+        <v>-6.494931859920002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2309871536404705</v>
+        <v>0.2347664833066025</v>
       </c>
       <c r="T52">
-        <v>2.69469872915282</v>
+        <v>2.749692580768183</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01004361948311307</v>
+        <v>0.009846685767757908</v>
       </c>
       <c r="W52">
-        <v>0.233431714525882</v>
+        <v>0.2334781514959627</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.04565281583233216</v>
+        <v>0.04475766258071778</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5835,22 +5835,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2341094340831762</v>
+        <v>0.2360094340831762</v>
       </c>
       <c r="C53">
-        <v>-0.6494796984498663</v>
+        <v>-1.74623478827781</v>
       </c>
       <c r="D53">
-        <v>35.95710030155014</v>
+        <v>35.5979252117222</v>
       </c>
       <c r="E53">
-        <v>37.55858000000001</v>
+        <v>38.29616000000001</v>
       </c>
       <c r="F53">
-        <v>37.61658000000001</v>
+        <v>38.35416000000001</v>
       </c>
       <c r="G53">
         <v>1.01</v>
@@ -5871,37 +5871,37 @@
         <v>0.397</v>
       </c>
       <c r="M53">
-        <v>8.869989564000003</v>
+        <v>9.043910928000003</v>
       </c>
       <c r="N53">
-        <v>-8.472989564000002</v>
+        <v>-8.646910928000002</v>
       </c>
       <c r="O53">
-        <v>-1.864057704080001</v>
+        <v>-1.902320404160001</v>
       </c>
       <c r="P53">
-        <v>-6.608931859920002</v>
+        <v>-6.744590523840001</v>
       </c>
       <c r="Q53">
-        <v>-6.494931859920002</v>
+        <v>-6.630590523840001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2347664833066025</v>
+        <v>0.2387032850421568</v>
       </c>
       <c r="T53">
-        <v>2.749692580768183</v>
+        <v>2.806977842867521</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.009846685767757908</v>
+        <v>0.009657326426070256</v>
       </c>
       <c r="W53">
-        <v>0.2334781514959627</v>
+        <v>0.2335228024287327</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.04475766258071778</v>
+        <v>0.04389693830031938</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5917,22 +5917,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2360094340831762</v>
+        <v>0.2379094340831762</v>
       </c>
       <c r="C54">
-        <v>-1.74623478827781</v>
+        <v>-2.835885253869769</v>
       </c>
       <c r="D54">
-        <v>35.5979252117222</v>
+        <v>35.24585474613024</v>
       </c>
       <c r="E54">
-        <v>38.29616000000001</v>
+        <v>39.03374000000001</v>
       </c>
       <c r="F54">
-        <v>38.35416000000001</v>
+        <v>39.09174000000001</v>
       </c>
       <c r="G54">
         <v>1.01</v>
@@ -5953,37 +5953,37 @@
         <v>0.397</v>
       </c>
       <c r="M54">
-        <v>9.043910928000003</v>
+        <v>9.217832292000002</v>
       </c>
       <c r="N54">
-        <v>-8.646910928000002</v>
+        <v>-8.820832292000002</v>
       </c>
       <c r="O54">
-        <v>-1.902320404160001</v>
+        <v>-1.940583104240001</v>
       </c>
       <c r="P54">
-        <v>-6.744590523840001</v>
+        <v>-6.880249187760001</v>
       </c>
       <c r="Q54">
-        <v>-6.630590523840001</v>
+        <v>-6.766249187760002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2387032850421568</v>
+        <v>0.2428076102558197</v>
       </c>
       <c r="T54">
-        <v>2.806977842867521</v>
+        <v>2.86670077569449</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.009657326426070256</v>
+        <v>0.009475112719917987</v>
       </c>
       <c r="W54">
-        <v>0.2335228024287327</v>
+        <v>0.2335657684206434</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.04389693830031938</v>
+        <v>0.04306869418144543</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5999,22 +5999,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2379094340831762</v>
+        <v>0.2398094340831762</v>
       </c>
       <c r="C55">
-        <v>-2.835885253869769</v>
+        <v>-3.918639829189331</v>
       </c>
       <c r="D55">
-        <v>35.24585474613024</v>
+        <v>34.90068017081068</v>
       </c>
       <c r="E55">
-        <v>39.03374000000001</v>
+        <v>39.77132000000001</v>
       </c>
       <c r="F55">
-        <v>39.09174000000001</v>
+        <v>39.82932000000001</v>
       </c>
       <c r="G55">
         <v>1.01</v>
@@ -6035,37 +6035,37 @@
         <v>0.397</v>
       </c>
       <c r="M55">
-        <v>9.217832292000002</v>
+        <v>9.391753656000002</v>
       </c>
       <c r="N55">
-        <v>-8.820832292000002</v>
+        <v>-8.994753656000002</v>
       </c>
       <c r="O55">
-        <v>-1.940583104240001</v>
+        <v>-1.978845804320001</v>
       </c>
       <c r="P55">
-        <v>-6.880249187760001</v>
+        <v>-7.015907851680002</v>
       </c>
       <c r="Q55">
-        <v>-6.766249187760002</v>
+        <v>-6.901907851680002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2428076102558197</v>
+        <v>0.2470903843918158</v>
       </c>
       <c r="T55">
-        <v>2.86670077569449</v>
+        <v>2.929020357774805</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.009475112719917987</v>
+        <v>0.009299647669549138</v>
       </c>
       <c r="W55">
-        <v>0.2335657684206434</v>
+        <v>0.2336071430795203</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.04306869418144543</v>
+        <v>0.04227112577067793</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6081,22 +6081,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2398094340831762</v>
+        <v>0.2417094340831762</v>
       </c>
       <c r="C56">
-        <v>-3.918639829189331</v>
+        <v>-4.994699150692483</v>
       </c>
       <c r="D56">
-        <v>34.90068017081068</v>
+        <v>34.56220084930753</v>
       </c>
       <c r="E56">
-        <v>39.77132000000001</v>
+        <v>40.50890000000001</v>
       </c>
       <c r="F56">
-        <v>39.82932000000001</v>
+        <v>40.56690000000001</v>
       </c>
       <c r="G56">
         <v>1.01</v>
@@ -6117,37 +6117,37 @@
         <v>0.397</v>
       </c>
       <c r="M56">
-        <v>9.391753656000002</v>
+        <v>9.565675020000002</v>
       </c>
       <c r="N56">
-        <v>-8.994753656000002</v>
+        <v>-9.168675020000002</v>
       </c>
       <c r="O56">
-        <v>-1.978845804320001</v>
+        <v>-2.0171085044</v>
       </c>
       <c r="P56">
-        <v>-7.015907851680002</v>
+        <v>-7.151566515600002</v>
       </c>
       <c r="Q56">
-        <v>-6.901907851680002</v>
+        <v>-7.037566515600002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2470903843918158</v>
+        <v>0.2515635040449672</v>
       </c>
       <c r="T56">
-        <v>2.929020357774805</v>
+        <v>2.99410969905869</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.009299647669549138</v>
+        <v>0.009130563166466425</v>
       </c>
       <c r="W56">
-        <v>0.2336071430795203</v>
+        <v>0.2336470132053472</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.04227112577067793</v>
+        <v>0.04150255984757467</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2417094340831762</v>
+        <v>0.2436094340831762</v>
       </c>
       <c r="C57">
-        <v>-4.994699150692483</v>
+        <v>-6.064256146218746</v>
       </c>
       <c r="D57">
-        <v>34.56220084930753</v>
+        <v>34.23022385378127</v>
       </c>
       <c r="E57">
-        <v>40.50890000000001</v>
+        <v>41.24648000000001</v>
       </c>
       <c r="F57">
-        <v>40.56690000000001</v>
+        <v>41.30448000000001</v>
       </c>
       <c r="G57">
         <v>1.01</v>
@@ -6199,37 +6199,37 @@
         <v>0.397</v>
       </c>
       <c r="M57">
-        <v>9.565675020000002</v>
+        <v>9.739596384000004</v>
       </c>
       <c r="N57">
-        <v>-9.168675020000002</v>
+        <v>-9.342596384000004</v>
       </c>
       <c r="O57">
-        <v>-2.0171085044</v>
+        <v>-2.055371204480001</v>
       </c>
       <c r="P57">
-        <v>-7.151566515600002</v>
+        <v>-7.287225179520003</v>
       </c>
       <c r="Q57">
-        <v>-7.037566515600002</v>
+        <v>-7.173225179520003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2515635040449672</v>
+        <v>0.2562399473187165</v>
       </c>
       <c r="T57">
-        <v>2.99410969905869</v>
+        <v>3.062157646764569</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.009130563166466425</v>
+        <v>0.008967517395636667</v>
       </c>
       <c r="W57">
-        <v>0.2336470132053472</v>
+        <v>0.2336854593981089</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.04150255984757467</v>
+        <v>0.04076144270743942</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6245,22 +6245,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2436094340831762</v>
+        <v>0.2455094340831762</v>
       </c>
       <c r="C58">
-        <v>-6.064256146218746</v>
+        <v>-7.127496401683182</v>
       </c>
       <c r="D58">
-        <v>34.23022385378127</v>
+        <v>33.90456359831683</v>
       </c>
       <c r="E58">
-        <v>41.24648000000001</v>
+        <v>41.98406000000001</v>
       </c>
       <c r="F58">
-        <v>41.30448000000001</v>
+        <v>42.04206000000001</v>
       </c>
       <c r="G58">
         <v>1.01</v>
@@ -6281,37 +6281,37 @@
         <v>0.397</v>
       </c>
       <c r="M58">
-        <v>9.739596384000004</v>
+        <v>9.913517748000004</v>
       </c>
       <c r="N58">
-        <v>-9.342596384000004</v>
+        <v>-9.516517748000004</v>
       </c>
       <c r="O58">
-        <v>-2.055371204480001</v>
+        <v>-2.093633904560001</v>
       </c>
       <c r="P58">
-        <v>-7.287225179520003</v>
+        <v>-7.422883843440003</v>
       </c>
       <c r="Q58">
-        <v>-7.173225179520003</v>
+        <v>-7.308883843440003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2562399473187165</v>
+        <v>0.2611338995819424</v>
       </c>
       <c r="T58">
-        <v>3.062157646764569</v>
+        <v>3.133370615293977</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.008967517395636667</v>
+        <v>0.008810192529046549</v>
       </c>
       <c r="W58">
-        <v>0.2336854593981089</v>
+        <v>0.2337225566016508</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.04076144270743942</v>
+        <v>0.04004632967748434</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6327,22 +6327,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2455094340831762</v>
+        <v>0.2474094340831762</v>
       </c>
       <c r="C59">
-        <v>-7.127496401683182</v>
+        <v>-8.18459850703379</v>
       </c>
       <c r="D59">
-        <v>33.90456359831683</v>
+        <v>33.58504149296622</v>
       </c>
       <c r="E59">
-        <v>41.98406000000001</v>
+        <v>42.72164000000001</v>
       </c>
       <c r="F59">
-        <v>42.04206000000001</v>
+        <v>42.77964000000001</v>
       </c>
       <c r="G59">
         <v>1.01</v>
@@ -6363,37 +6363,37 @@
         <v>0.397</v>
       </c>
       <c r="M59">
-        <v>9.913517748000004</v>
+        <v>10.087439112</v>
       </c>
       <c r="N59">
-        <v>-9.516517748000004</v>
+        <v>-9.690439112000002</v>
       </c>
       <c r="O59">
-        <v>-2.093633904560001</v>
+        <v>-2.131896604640001</v>
       </c>
       <c r="P59">
-        <v>-7.422883843440003</v>
+        <v>-7.558542507360001</v>
       </c>
       <c r="Q59">
-        <v>-7.308883843440003</v>
+        <v>-7.444542507360001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2611338995819424</v>
+        <v>0.2662608971910363</v>
       </c>
       <c r="T59">
-        <v>3.133370615293977</v>
+        <v>3.207974677562881</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.008810192529046549</v>
+        <v>0.008658292657856092</v>
       </c>
       <c r="W59">
-        <v>0.2337225566016508</v>
+        <v>0.2337583745912775</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.04004632967748434</v>
+        <v>0.03935587571752774</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6409,22 +6409,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2474094340831762</v>
+        <v>0.2493094340831762</v>
       </c>
       <c r="C60">
-        <v>-8.184598507033769</v>
+        <v>-9.235734382829463</v>
       </c>
       <c r="D60">
-        <v>33.58504149296623</v>
+        <v>33.27148561717054</v>
       </c>
       <c r="E60">
-        <v>42.72164</v>
+        <v>43.45922</v>
       </c>
       <c r="F60">
-        <v>42.77964</v>
+        <v>43.51722</v>
       </c>
       <c r="G60">
         <v>1.01</v>
@@ -6445,37 +6445,37 @@
         <v>0.397</v>
       </c>
       <c r="M60">
-        <v>10.087439112</v>
+        <v>10.261360476</v>
       </c>
       <c r="N60">
-        <v>-9.690439112</v>
+        <v>-9.864360476</v>
       </c>
       <c r="O60">
-        <v>-2.13189660464</v>
+        <v>-2.17015930472</v>
       </c>
       <c r="P60">
-        <v>-7.55854250736</v>
+        <v>-7.69420117128</v>
       </c>
       <c r="Q60">
-        <v>-7.44454250736</v>
+        <v>-7.58020117128</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2662608971910362</v>
+        <v>0.2716379922444761</v>
       </c>
       <c r="T60">
-        <v>3.20797467756288</v>
+        <v>3.286217962381487</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.008658292657856094</v>
+        <v>0.008511541934841584</v>
       </c>
       <c r="W60">
-        <v>0.2337583745912775</v>
+        <v>0.2337929784117644</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.03935587571752774</v>
+        <v>0.03868882697655263</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6491,22 +6491,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2493094340831762</v>
+        <v>0.2512094340831762</v>
       </c>
       <c r="C61">
-        <v>-9.235734382829463</v>
+        <v>-10.28106958869322</v>
       </c>
       <c r="D61">
-        <v>33.27148561717054</v>
+        <v>32.96373041130678</v>
       </c>
       <c r="E61">
-        <v>43.45922</v>
+        <v>44.1968</v>
       </c>
       <c r="F61">
-        <v>43.51722</v>
+        <v>44.2548</v>
       </c>
       <c r="G61">
         <v>1.01</v>
@@ -6527,37 +6527,37 @@
         <v>0.397</v>
       </c>
       <c r="M61">
-        <v>10.261360476</v>
+        <v>10.43528184</v>
       </c>
       <c r="N61">
-        <v>-9.864360476</v>
+        <v>-10.03828184</v>
       </c>
       <c r="O61">
-        <v>-2.17015930472</v>
+        <v>-2.208422004800001</v>
       </c>
       <c r="P61">
-        <v>-7.69420117128</v>
+        <v>-7.829859835200001</v>
       </c>
       <c r="Q61">
-        <v>-7.58020117128</v>
+        <v>-7.715859835200001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2716379922444761</v>
+        <v>0.277283942050588</v>
       </c>
       <c r="T61">
-        <v>3.286217962381487</v>
+        <v>3.368373411441024</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.008511541934841584</v>
+        <v>0.008369682902594223</v>
       </c>
       <c r="W61">
-        <v>0.2337929784117644</v>
+        <v>0.2338264287715683</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.03868882697655263</v>
+        <v>0.03804401319361017</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6573,22 +6573,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2512094340831762</v>
+        <v>0.2531094340831762</v>
       </c>
       <c r="C62">
-        <v>-10.28106958869322</v>
+        <v>-11.32076361480336</v>
       </c>
       <c r="D62">
-        <v>32.96373041130678</v>
+        <v>32.66161638519664</v>
       </c>
       <c r="E62">
-        <v>44.1968</v>
+        <v>44.93438</v>
       </c>
       <c r="F62">
-        <v>44.2548</v>
+        <v>44.99238</v>
       </c>
       <c r="G62">
         <v>1.01</v>
@@ -6609,37 +6609,37 @@
         <v>0.397</v>
       </c>
       <c r="M62">
-        <v>10.43528184</v>
+        <v>10.609203204</v>
       </c>
       <c r="N62">
-        <v>-10.03828184</v>
+        <v>-10.212203204</v>
       </c>
       <c r="O62">
-        <v>-2.208422004800001</v>
+        <v>-2.24668470488</v>
       </c>
       <c r="P62">
-        <v>-7.829859835200001</v>
+        <v>-7.965518499120002</v>
       </c>
       <c r="Q62">
-        <v>-7.715859835200001</v>
+        <v>-7.851518499120002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.277283942050588</v>
+        <v>0.2832194277441929</v>
       </c>
       <c r="T62">
-        <v>3.368373411441024</v>
+        <v>3.454741960452333</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.008369682902594223</v>
+        <v>0.008232474986158252</v>
       </c>
       <c r="W62">
-        <v>0.2338264287715683</v>
+        <v>0.2338587823982639</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.03804401319361017</v>
+        <v>0.03742034084617385</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6655,22 +6655,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2531094340831762</v>
+        <v>0.2550094340831762</v>
       </c>
       <c r="C63">
-        <v>-11.32076361480336</v>
+        <v>-12.35497015750125</v>
       </c>
       <c r="D63">
-        <v>32.66161638519664</v>
+        <v>32.36498984249876</v>
       </c>
       <c r="E63">
-        <v>44.93438</v>
+        <v>45.67196000000001</v>
       </c>
       <c r="F63">
-        <v>44.99238</v>
+        <v>45.72996000000001</v>
       </c>
       <c r="G63">
         <v>1.01</v>
@@ -6691,37 +6691,37 @@
         <v>0.397</v>
       </c>
       <c r="M63">
-        <v>10.609203204</v>
+        <v>10.783124568</v>
       </c>
       <c r="N63">
-        <v>-10.212203204</v>
+        <v>-10.386124568</v>
       </c>
       <c r="O63">
-        <v>-2.24668470488</v>
+        <v>-2.28494740496</v>
       </c>
       <c r="P63">
-        <v>-7.965518499120002</v>
+        <v>-8.101177163040001</v>
       </c>
       <c r="Q63">
-        <v>-7.851518499120002</v>
+        <v>-7.987177163040001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2832194277441929</v>
+        <v>0.2894673074216716</v>
       </c>
       <c r="T63">
-        <v>3.454741960452333</v>
+        <v>3.5456562225695</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.008232474986158252</v>
+        <v>0.008099693131542797</v>
       </c>
       <c r="W63">
-        <v>0.2338587823982639</v>
+        <v>0.2338900923595822</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.03742034084617385</v>
+        <v>0.03681678696155821</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6737,22 +6737,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2550094340831762</v>
+        <v>0.2569094340831762</v>
       </c>
       <c r="C64">
-        <v>-12.35497015750125</v>
+        <v>-13.38383738001599</v>
       </c>
       <c r="D64">
-        <v>32.36498984249876</v>
+        <v>32.07370261998402</v>
       </c>
       <c r="E64">
-        <v>45.67196000000001</v>
+        <v>46.40954000000001</v>
       </c>
       <c r="F64">
-        <v>45.72996000000001</v>
+        <v>46.46754000000001</v>
       </c>
       <c r="G64">
         <v>1.01</v>
@@ -6773,37 +6773,37 @@
         <v>0.397</v>
       </c>
       <c r="M64">
-        <v>10.783124568</v>
+        <v>10.957045932</v>
       </c>
       <c r="N64">
-        <v>-10.386124568</v>
+        <v>-10.560045932</v>
       </c>
       <c r="O64">
-        <v>-2.28494740496</v>
+        <v>-2.32321010504</v>
       </c>
       <c r="P64">
-        <v>-8.101177163040001</v>
+        <v>-8.23683582696</v>
       </c>
       <c r="Q64">
-        <v>-7.987177163040001</v>
+        <v>-8.122835826959999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2894673074216716</v>
+        <v>0.2960529103249601</v>
       </c>
       <c r="T64">
-        <v>3.5456562225695</v>
+        <v>3.641484769125432</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.008099693131542797</v>
+        <v>0.007971126573899262</v>
       </c>
       <c r="W64">
-        <v>0.2338900923595822</v>
+        <v>0.2339204083538746</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.03681678696155821</v>
+        <v>0.03623239351772389</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6819,22 +6819,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2569094340831762</v>
+        <v>0.2588094340831762</v>
       </c>
       <c r="C65">
-        <v>-13.38383738001599</v>
+        <v>-14.40750815923553</v>
       </c>
       <c r="D65">
-        <v>32.07370261998402</v>
+        <v>31.78761184076447</v>
       </c>
       <c r="E65">
-        <v>46.40954000000001</v>
+        <v>47.14712000000001</v>
       </c>
       <c r="F65">
-        <v>46.46754000000001</v>
+        <v>47.20512000000001</v>
       </c>
       <c r="G65">
         <v>1.01</v>
@@ -6855,37 +6855,37 @@
         <v>0.397</v>
       </c>
       <c r="M65">
-        <v>10.957045932</v>
+        <v>11.130967296</v>
       </c>
       <c r="N65">
-        <v>-10.560045932</v>
+        <v>-10.733967296</v>
       </c>
       <c r="O65">
-        <v>-2.32321010504</v>
+        <v>-2.36147280512</v>
       </c>
       <c r="P65">
-        <v>-8.23683582696</v>
+        <v>-8.372494490880001</v>
       </c>
       <c r="Q65">
-        <v>-8.122835826959999</v>
+        <v>-8.25849449088</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2960529103249601</v>
+        <v>0.3030043800562089</v>
       </c>
       <c r="T65">
-        <v>3.641484769125432</v>
+        <v>3.742637123823361</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.007971126573899262</v>
+        <v>0.007846577721182085</v>
       </c>
       <c r="W65">
-        <v>0.2339204083538746</v>
+        <v>0.2339497769733453</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.03623239351772389</v>
+        <v>0.03566626236900949</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6901,22 +6901,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2588094340831762</v>
+        <v>0.2607094340831763</v>
       </c>
       <c r="C66">
-        <v>-14.40750815923553</v>
+        <v>-15.42612031938761</v>
       </c>
       <c r="D66">
-        <v>31.78761184076447</v>
+        <v>31.5065796806124</v>
       </c>
       <c r="E66">
-        <v>47.14712000000001</v>
+        <v>47.88470000000001</v>
       </c>
       <c r="F66">
-        <v>47.20512000000001</v>
+        <v>47.94270000000001</v>
       </c>
       <c r="G66">
         <v>1.01</v>
@@ -6937,37 +6937,37 @@
         <v>0.397</v>
       </c>
       <c r="M66">
-        <v>11.130967296</v>
+        <v>11.30488866</v>
       </c>
       <c r="N66">
-        <v>-10.733967296</v>
+        <v>-10.90788866</v>
       </c>
       <c r="O66">
-        <v>-2.36147280512</v>
+        <v>-2.399735505200001</v>
       </c>
       <c r="P66">
-        <v>-8.372494490880001</v>
+        <v>-8.508153154800002</v>
       </c>
       <c r="Q66">
-        <v>-8.25849449088</v>
+        <v>-8.394153154800001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3030043800562089</v>
+        <v>0.3103530766292436</v>
       </c>
       <c r="T66">
-        <v>3.742637123823361</v>
+        <v>3.849569613075458</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.007846577721182085</v>
+        <v>0.007725861140856205</v>
       </c>
       <c r="W66">
-        <v>0.2339497769733453</v>
+        <v>0.2339782419429861</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.03566626236900949</v>
+        <v>0.03511755064025546</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6983,22 +6983,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2607094340831763</v>
+        <v>0.2626094340831762</v>
       </c>
       <c r="C67">
-        <v>-15.42612031938761</v>
+        <v>-16.43980685343352</v>
       </c>
       <c r="D67">
-        <v>31.5065796806124</v>
+        <v>31.23047314656649</v>
       </c>
       <c r="E67">
-        <v>47.88470000000001</v>
+        <v>48.62228000000001</v>
       </c>
       <c r="F67">
-        <v>47.94270000000001</v>
+        <v>48.68028000000001</v>
       </c>
       <c r="G67">
         <v>1.01</v>
@@ -7019,37 +7019,37 @@
         <v>0.397</v>
       </c>
       <c r="M67">
-        <v>11.30488866</v>
+        <v>11.478810024</v>
       </c>
       <c r="N67">
-        <v>-10.90788866</v>
+        <v>-11.081810024</v>
       </c>
       <c r="O67">
-        <v>-2.399735505200001</v>
+        <v>-2.43799820528</v>
       </c>
       <c r="P67">
-        <v>-8.508153154800002</v>
+        <v>-8.643811818720003</v>
       </c>
       <c r="Q67">
-        <v>-8.394153154800001</v>
+        <v>-8.529811818720002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3103530766292436</v>
+        <v>0.3181340494712801</v>
       </c>
       <c r="T67">
-        <v>3.849569613075458</v>
+        <v>3.962792248754147</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.007725861140856205</v>
+        <v>0.00760880263872202</v>
       </c>
       <c r="W67">
-        <v>0.2339782419429861</v>
+        <v>0.2340058443377894</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.03511755064025546</v>
+        <v>0.03458546653964556</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7065,22 +7065,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2626094340831762</v>
+        <v>0.2645094340831762</v>
       </c>
       <c r="C68">
-        <v>-16.43980685343352</v>
+        <v>-17.44869613292218</v>
       </c>
       <c r="D68">
-        <v>31.23047314656649</v>
+        <v>30.95916386707783</v>
       </c>
       <c r="E68">
-        <v>48.62228000000001</v>
+        <v>49.35986000000001</v>
       </c>
       <c r="F68">
-        <v>48.68028000000001</v>
+        <v>49.41786000000001</v>
       </c>
       <c r="G68">
         <v>1.01</v>
@@ -7101,37 +7101,37 @@
         <v>0.397</v>
       </c>
       <c r="M68">
-        <v>11.478810024</v>
+        <v>11.652731388</v>
       </c>
       <c r="N68">
-        <v>-11.081810024</v>
+        <v>-11.255731388</v>
       </c>
       <c r="O68">
-        <v>-2.43799820528</v>
+        <v>-2.476260905360001</v>
       </c>
       <c r="P68">
-        <v>-8.643811818720003</v>
+        <v>-8.779470482640003</v>
       </c>
       <c r="Q68">
-        <v>-8.529811818720002</v>
+        <v>-8.665470482640002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3181340494712801</v>
+        <v>0.3263865964249553</v>
       </c>
       <c r="T68">
-        <v>3.962792248754147</v>
+        <v>4.082876862352758</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.00760880263872202</v>
+        <v>0.007495238420233633</v>
       </c>
       <c r="W68">
-        <v>0.2340058443377894</v>
+        <v>0.2340326227805089</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.03458546653964556</v>
+        <v>0.03406926554651657</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7147,22 +7147,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2645094340831762</v>
+        <v>0.2664094340831762</v>
       </c>
       <c r="C69">
-        <v>-17.44869613292218</v>
+        <v>-18.45291210699965</v>
       </c>
       <c r="D69">
-        <v>30.95916386707783</v>
+        <v>30.69252789300036</v>
       </c>
       <c r="E69">
-        <v>49.35986000000001</v>
+        <v>50.09744000000001</v>
       </c>
       <c r="F69">
-        <v>49.41786000000001</v>
+        <v>50.15544000000001</v>
       </c>
       <c r="G69">
         <v>1.01</v>
@@ -7183,37 +7183,37 @@
         <v>0.397</v>
       </c>
       <c r="M69">
-        <v>11.652731388</v>
+        <v>11.826652752</v>
       </c>
       <c r="N69">
-        <v>-11.255731388</v>
+        <v>-11.429652752</v>
       </c>
       <c r="O69">
-        <v>-2.476260905360001</v>
+        <v>-2.51452360544</v>
       </c>
       <c r="P69">
-        <v>-8.779470482640003</v>
+        <v>-8.915129146560002</v>
       </c>
       <c r="Q69">
-        <v>-8.665470482640002</v>
+        <v>-8.801129146560001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3263865964249553</v>
+        <v>0.3351549275632352</v>
       </c>
       <c r="T69">
-        <v>4.082876862352758</v>
+        <v>4.210466764301282</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.007495238420233633</v>
+        <v>0.007385014325818433</v>
       </c>
       <c r="W69">
-        <v>0.2340326227805089</v>
+        <v>0.234058613621972</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.03406926554651657</v>
+        <v>0.03356824693553839</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7229,22 +7229,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2664094340831762</v>
+        <v>0.2683094340831762</v>
       </c>
       <c r="C70">
-        <v>-18.45291210699965</v>
+        <v>-19.45257449122297</v>
       </c>
       <c r="D70">
-        <v>30.69252789300036</v>
+        <v>30.43044550877704</v>
       </c>
       <c r="E70">
-        <v>50.09744000000001</v>
+        <v>50.83502000000001</v>
       </c>
       <c r="F70">
-        <v>50.15544000000001</v>
+        <v>50.89302000000001</v>
       </c>
       <c r="G70">
         <v>1.01</v>
@@ -7265,37 +7265,37 @@
         <v>0.397</v>
       </c>
       <c r="M70">
-        <v>11.826652752</v>
+        <v>12.000574116</v>
       </c>
       <c r="N70">
-        <v>-11.429652752</v>
+        <v>-11.603574116</v>
       </c>
       <c r="O70">
-        <v>-2.51452360544</v>
+        <v>-2.552786305520001</v>
       </c>
       <c r="P70">
-        <v>-8.915129146560002</v>
+        <v>-9.050787810480003</v>
       </c>
       <c r="Q70">
-        <v>-8.801129146560001</v>
+        <v>-8.936787810480002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3351549275632352</v>
+        <v>0.3444889574846299</v>
       </c>
       <c r="T70">
-        <v>4.210466764301282</v>
+        <v>4.34628827282713</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.007385014325818433</v>
+        <v>0.007277985132690628</v>
       </c>
       <c r="W70">
-        <v>0.234058613621972</v>
+        <v>0.2340838511057116</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.03356824693553839</v>
+        <v>0.03308175060313923</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7311,22 +7311,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2683094340831762</v>
+        <v>0.2702094340831763</v>
       </c>
       <c r="C71">
-        <v>-19.45257449122297</v>
+        <v>-20.44779894678203</v>
       </c>
       <c r="D71">
-        <v>30.43044550877704</v>
+        <v>30.17280105321797</v>
       </c>
       <c r="E71">
-        <v>50.83502000000001</v>
+        <v>51.57260000000001</v>
       </c>
       <c r="F71">
-        <v>50.89302000000001</v>
+        <v>51.63060000000001</v>
       </c>
       <c r="G71">
         <v>1.01</v>
@@ -7347,37 +7347,37 @@
         <v>0.397</v>
       </c>
       <c r="M71">
-        <v>12.000574116</v>
+        <v>12.17449548</v>
       </c>
       <c r="N71">
-        <v>-11.603574116</v>
+        <v>-11.77749548</v>
       </c>
       <c r="O71">
-        <v>-2.552786305520001</v>
+        <v>-2.5910490056</v>
       </c>
       <c r="P71">
-        <v>-9.050787810480003</v>
+        <v>-9.186446474400002</v>
       </c>
       <c r="Q71">
-        <v>-8.936787810480002</v>
+        <v>-9.072446474400001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3444889574846299</v>
+        <v>0.3544452560674509</v>
       </c>
       <c r="T71">
-        <v>4.34628827282713</v>
+        <v>4.491164548588034</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.007277985132690628</v>
+        <v>0.007174013916509334</v>
       </c>
       <c r="W71">
-        <v>0.2340838511057116</v>
+        <v>0.2341083675184871</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.03308175060313923</v>
+        <v>0.03260915416595156</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7393,22 +7393,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2702094340831763</v>
+        <v>0.2721094340831762</v>
       </c>
       <c r="C72">
-        <v>-20.44779894678203</v>
+        <v>-21.43869725069349</v>
       </c>
       <c r="D72">
-        <v>30.17280105321797</v>
+        <v>29.91948274930651</v>
       </c>
       <c r="E72">
-        <v>51.57260000000001</v>
+        <v>52.31018000000001</v>
       </c>
       <c r="F72">
-        <v>51.63060000000001</v>
+        <v>52.36818000000001</v>
       </c>
       <c r="G72">
         <v>1.01</v>
@@ -7429,37 +7429,37 @@
         <v>0.397</v>
       </c>
       <c r="M72">
-        <v>12.17449548</v>
+        <v>12.348416844</v>
       </c>
       <c r="N72">
-        <v>-11.77749548</v>
+        <v>-11.951416844</v>
       </c>
       <c r="O72">
-        <v>-2.5910490056</v>
+        <v>-2.629311705680001</v>
       </c>
       <c r="P72">
-        <v>-9.186446474400002</v>
+        <v>-9.322105138320001</v>
       </c>
       <c r="Q72">
-        <v>-9.072446474400001</v>
+        <v>-9.208105138320001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3544452560674509</v>
+        <v>0.3650881959318457</v>
       </c>
       <c r="T72">
-        <v>4.491164548588034</v>
+        <v>4.646032291642794</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.007174013916509334</v>
+        <v>0.007072971466981035</v>
       </c>
       <c r="W72">
-        <v>0.2341083675184871</v>
+        <v>0.2341321933280859</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.03260915416595156</v>
+        <v>0.03214987030445926</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7475,22 +7475,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2721094340831762</v>
+        <v>0.2740094340831762</v>
       </c>
       <c r="C73">
-        <v>-21.43869725069349</v>
+        <v>-22.42537745749283</v>
       </c>
       <c r="D73">
-        <v>29.91948274930651</v>
+        <v>29.67038254250717</v>
       </c>
       <c r="E73">
-        <v>52.31018</v>
+        <v>53.04776</v>
       </c>
       <c r="F73">
-        <v>52.36818</v>
+        <v>53.10576</v>
       </c>
       <c r="G73">
         <v>1.01</v>
@@ -7511,37 +7511,37 @@
         <v>0.397</v>
       </c>
       <c r="M73">
-        <v>12.348416844</v>
+        <v>12.522338208</v>
       </c>
       <c r="N73">
-        <v>-11.951416844</v>
+        <v>-12.125338208</v>
       </c>
       <c r="O73">
-        <v>-2.62931170568</v>
+        <v>-2.66757440576</v>
       </c>
       <c r="P73">
-        <v>-9.322105138320001</v>
+        <v>-9.457763802240001</v>
       </c>
       <c r="Q73">
-        <v>-9.208105138320001</v>
+        <v>-9.34376380224</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3650881959318456</v>
+        <v>0.3764913457865544</v>
       </c>
       <c r="T73">
-        <v>4.646032291642793</v>
+        <v>4.811962016344321</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.007072971466981035</v>
+        <v>0.006974735752161854</v>
       </c>
       <c r="W73">
-        <v>0.2341321933280859</v>
+        <v>0.2341553573096402</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.03214987030445926</v>
+        <v>0.03170334432800848</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7557,22 +7557,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2740094340831762</v>
+        <v>0.2759094340831763</v>
       </c>
       <c r="C74">
-        <v>-22.42537745749283</v>
+        <v>-23.40794405291589</v>
       </c>
       <c r="D74">
-        <v>29.67038254250717</v>
+        <v>29.42539594708411</v>
       </c>
       <c r="E74">
-        <v>53.04776</v>
+        <v>53.78534000000001</v>
       </c>
       <c r="F74">
-        <v>53.10576</v>
+        <v>53.84334</v>
       </c>
       <c r="G74">
         <v>1.01</v>
@@ -7593,37 +7593,37 @@
         <v>0.397</v>
       </c>
       <c r="M74">
-        <v>12.522338208</v>
+        <v>12.696259572</v>
       </c>
       <c r="N74">
-        <v>-12.125338208</v>
+        <v>-12.299259572</v>
       </c>
       <c r="O74">
-        <v>-2.66757440576</v>
+        <v>-2.705837105840001</v>
       </c>
       <c r="P74">
-        <v>-9.457763802240001</v>
+        <v>-9.593422466160002</v>
       </c>
       <c r="Q74">
-        <v>-9.34376380224</v>
+        <v>-9.479422466160001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3764913457865544</v>
+        <v>0.3887391734082786</v>
       </c>
       <c r="T74">
-        <v>4.811962016344321</v>
+        <v>4.990182831764481</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.006974735752161854</v>
+        <v>0.006879191426789773</v>
       </c>
       <c r="W74">
-        <v>0.2341553573096402</v>
+        <v>0.234177886661563</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.03170334432800848</v>
+        <v>0.03126905193995355</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7639,22 +7639,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2759094340831763</v>
+        <v>0.2778094340831762</v>
       </c>
       <c r="C75">
-        <v>-23.40794405291589</v>
+        <v>-24.38649810002907</v>
       </c>
       <c r="D75">
-        <v>29.42539594708411</v>
+        <v>29.18442189997094</v>
       </c>
       <c r="E75">
-        <v>53.78534000000001</v>
+        <v>54.52292000000001</v>
       </c>
       <c r="F75">
-        <v>53.84334</v>
+        <v>54.58092000000001</v>
       </c>
       <c r="G75">
         <v>1.01</v>
@@ -7675,37 +7675,37 @@
         <v>0.397</v>
       </c>
       <c r="M75">
-        <v>12.696259572</v>
+        <v>12.870180936</v>
       </c>
       <c r="N75">
-        <v>-12.299259572</v>
+        <v>-12.473180936</v>
       </c>
       <c r="O75">
-        <v>-2.705837105840001</v>
+        <v>-2.74409980592</v>
       </c>
       <c r="P75">
-        <v>-9.593422466160002</v>
+        <v>-9.729081130080001</v>
       </c>
       <c r="Q75">
-        <v>-9.479422466160001</v>
+        <v>-9.61508113008</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3887391734082786</v>
+        <v>0.4019291416162893</v>
       </c>
       <c r="T75">
-        <v>4.990182831764481</v>
+        <v>5.1821129406785</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.006879191426789773</v>
+        <v>0.006786229380481803</v>
       </c>
       <c r="W75">
-        <v>0.234177886661563</v>
+        <v>0.2341998071120824</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.03126905193995355</v>
+        <v>0.03084649718400823</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7721,22 +7721,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2778094340831762</v>
+        <v>0.2797094340831762</v>
       </c>
       <c r="C76">
-        <v>-24.38649810002907</v>
+        <v>-25.36113737823769</v>
       </c>
       <c r="D76">
-        <v>29.18442189997094</v>
+        <v>28.94736262176232</v>
       </c>
       <c r="E76">
-        <v>54.52292000000001</v>
+        <v>55.26050000000001</v>
       </c>
       <c r="F76">
-        <v>54.58092000000001</v>
+        <v>55.31850000000001</v>
       </c>
       <c r="G76">
         <v>1.01</v>
@@ -7757,37 +7757,37 @@
         <v>0.397</v>
       </c>
       <c r="M76">
-        <v>12.870180936</v>
+        <v>13.0441023</v>
       </c>
       <c r="N76">
-        <v>-12.473180936</v>
+        <v>-12.6471023</v>
       </c>
       <c r="O76">
-        <v>-2.74409980592</v>
+        <v>-2.782362506000001</v>
       </c>
       <c r="P76">
-        <v>-9.729081130080001</v>
+        <v>-9.864739794000002</v>
       </c>
       <c r="Q76">
-        <v>-9.61508113008</v>
+        <v>-9.750739794000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4019291416162893</v>
+        <v>0.4161743072809409</v>
       </c>
       <c r="T76">
-        <v>5.1821129406785</v>
+        <v>5.389397458305639</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.006786229380481803</v>
+        <v>0.006695746322075378</v>
       </c>
       <c r="W76">
-        <v>0.2341998071120824</v>
+        <v>0.2342211430172546</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.03084649718400823</v>
+        <v>0.03043521055488807</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7803,22 +7803,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2797094340831762</v>
+        <v>0.2816094340831762</v>
       </c>
       <c r="C77">
-        <v>-25.36113737823769</v>
+        <v>-26.33195651557411</v>
       </c>
       <c r="D77">
-        <v>28.94736262176232</v>
+        <v>28.71412348442589</v>
       </c>
       <c r="E77">
-        <v>55.26050000000001</v>
+        <v>55.99808000000001</v>
       </c>
       <c r="F77">
-        <v>55.31850000000001</v>
+        <v>56.05608000000001</v>
       </c>
       <c r="G77">
         <v>1.01</v>
@@ -7839,37 +7839,37 @@
         <v>0.397</v>
       </c>
       <c r="M77">
-        <v>13.0441023</v>
+        <v>13.218023664</v>
       </c>
       <c r="N77">
-        <v>-12.6471023</v>
+        <v>-12.821023664</v>
       </c>
       <c r="O77">
-        <v>-2.782362506000001</v>
+        <v>-2.82062520608</v>
       </c>
       <c r="P77">
-        <v>-9.864739794000002</v>
+        <v>-10.00039845792</v>
       </c>
       <c r="Q77">
-        <v>-9.750739794000001</v>
+        <v>-9.88639845792</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4161743072809409</v>
+        <v>0.4316065700843135</v>
       </c>
       <c r="T77">
-        <v>5.389397458305639</v>
+        <v>5.613955685735042</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.006695746322075378</v>
+        <v>0.006607644396784913</v>
       </c>
       <c r="W77">
-        <v>0.2342211430172546</v>
+        <v>0.2342419174512381</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.03043521055488807</v>
+        <v>0.03003474725811328</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7885,22 +7885,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2816094340831762</v>
+        <v>0.2835094340831762</v>
       </c>
       <c r="C78">
-        <v>-26.33195651557411</v>
+        <v>-27.29904711464153</v>
       </c>
       <c r="D78">
-        <v>28.71412348442589</v>
+        <v>28.48461288535848</v>
       </c>
       <c r="E78">
-        <v>55.99808000000001</v>
+        <v>56.73566000000001</v>
       </c>
       <c r="F78">
-        <v>56.05608000000001</v>
+        <v>56.79366000000001</v>
       </c>
       <c r="G78">
         <v>1.01</v>
@@ -7921,37 +7921,37 @@
         <v>0.397</v>
       </c>
       <c r="M78">
-        <v>13.218023664</v>
+        <v>13.391945028</v>
       </c>
       <c r="N78">
-        <v>-12.821023664</v>
+        <v>-12.994945028</v>
       </c>
       <c r="O78">
-        <v>-2.82062520608</v>
+        <v>-2.858887906160001</v>
       </c>
       <c r="P78">
-        <v>-10.00039845792</v>
+        <v>-10.13605712184</v>
       </c>
       <c r="Q78">
-        <v>-9.88639845792</v>
+        <v>-10.02205712184</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4316065700843135</v>
+        <v>0.4483807687836314</v>
       </c>
       <c r="T78">
-        <v>5.613955685735042</v>
+        <v>5.858040715549608</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.006607644396784913</v>
+        <v>0.006521830833190304</v>
       </c>
       <c r="W78">
-        <v>0.2342419174512381</v>
+        <v>0.2342621522895337</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.03003474725811328</v>
+        <v>0.02964468560541045</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7967,22 +7967,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2835094340831762</v>
+        <v>0.2854094340831762</v>
       </c>
       <c r="C79">
-        <v>-27.29904711464153</v>
+        <v>-28.26249787256584</v>
       </c>
       <c r="D79">
-        <v>28.48461288535848</v>
+        <v>28.25874212743417</v>
       </c>
       <c r="E79">
-        <v>56.73566000000001</v>
+        <v>57.47324000000001</v>
       </c>
       <c r="F79">
-        <v>56.79366000000001</v>
+        <v>57.53124000000001</v>
       </c>
       <c r="G79">
         <v>1.01</v>
@@ -8003,37 +8003,37 @@
         <v>0.397</v>
       </c>
       <c r="M79">
-        <v>13.391945028</v>
+        <v>13.565866392</v>
       </c>
       <c r="N79">
-        <v>-12.994945028</v>
+        <v>-13.168866392</v>
       </c>
       <c r="O79">
-        <v>-2.858887906160001</v>
+        <v>-2.897150606240001</v>
       </c>
       <c r="P79">
-        <v>-10.13605712184</v>
+        <v>-10.27171578576</v>
       </c>
       <c r="Q79">
-        <v>-10.02205712184</v>
+        <v>-10.15771578576</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4483807687836314</v>
+        <v>0.4666798946374329</v>
       </c>
       <c r="T79">
-        <v>5.858040715549608</v>
+        <v>6.124315293529137</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.006521830833190304</v>
+        <v>0.006438217617380172</v>
       </c>
       <c r="W79">
-        <v>0.2342621522895337</v>
+        <v>0.2342818682858218</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.02964468560541045</v>
+        <v>0.02926462553354625</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8049,22 +8049,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2854094340831762</v>
+        <v>0.2873094340831762</v>
       </c>
       <c r="C80">
-        <v>-28.26249787256584</v>
+        <v>-29.22239469528522</v>
       </c>
       <c r="D80">
-        <v>28.25874212743417</v>
+        <v>28.03642530471479</v>
       </c>
       <c r="E80">
-        <v>57.47324000000001</v>
+        <v>58.21082000000001</v>
       </c>
       <c r="F80">
-        <v>57.53124000000001</v>
+        <v>58.26882000000001</v>
       </c>
       <c r="G80">
         <v>1.01</v>
@@ -8085,37 +8085,37 @@
         <v>0.397</v>
       </c>
       <c r="M80">
-        <v>13.565866392</v>
+        <v>13.739787756</v>
       </c>
       <c r="N80">
-        <v>-13.168866392</v>
+        <v>-13.342787756</v>
       </c>
       <c r="O80">
-        <v>-2.897150606240001</v>
+        <v>-2.935413306320001</v>
       </c>
       <c r="P80">
-        <v>-10.27171578576</v>
+        <v>-10.40737444968</v>
       </c>
       <c r="Q80">
-        <v>-10.15771578576</v>
+        <v>-10.29337444968</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4666798946374329</v>
+        <v>0.4867217943820726</v>
       </c>
       <c r="T80">
-        <v>6.124315293529137</v>
+        <v>6.415949355125763</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.006438217617380172</v>
+        <v>0.006356721191843713</v>
       </c>
       <c r="W80">
-        <v>0.2342818682858218</v>
+        <v>0.2343010851429633</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.02926462553354625</v>
+        <v>0.02889418723565329</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8131,22 +8131,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2873094340831762</v>
+        <v>0.2892094340831762</v>
       </c>
       <c r="C81">
-        <v>-29.22239469528522</v>
+        <v>-30.17882080648712</v>
       </c>
       <c r="D81">
-        <v>28.03642530471479</v>
+        <v>27.81757919351289</v>
       </c>
       <c r="E81">
-        <v>58.21082000000001</v>
+        <v>58.94840000000001</v>
       </c>
       <c r="F81">
-        <v>58.26882000000001</v>
+        <v>59.00640000000001</v>
       </c>
       <c r="G81">
         <v>1.01</v>
@@ -8167,37 +8167,37 @@
         <v>0.397</v>
       </c>
       <c r="M81">
-        <v>13.739787756</v>
+        <v>13.91370912</v>
       </c>
       <c r="N81">
-        <v>-13.342787756</v>
+        <v>-13.51670912</v>
       </c>
       <c r="O81">
-        <v>-2.935413306320001</v>
+        <v>-2.973676006400001</v>
       </c>
       <c r="P81">
-        <v>-10.40737444968</v>
+        <v>-10.5430331136</v>
       </c>
       <c r="Q81">
-        <v>-10.29337444968</v>
+        <v>-10.4290331136</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4867217943820726</v>
+        <v>0.5087678841011762</v>
       </c>
       <c r="T81">
-        <v>6.415949355125763</v>
+        <v>6.736746822882052</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.006356721191843713</v>
+        <v>0.006277262176945667</v>
       </c>
       <c r="W81">
-        <v>0.2343010851429633</v>
+        <v>0.2343198215786762</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.02889418723565329</v>
+        <v>0.02853300989520757</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8213,22 +8213,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2892094340831762</v>
+        <v>0.2911094340831762</v>
       </c>
       <c r="C82">
-        <v>-30.17882080648712</v>
+        <v>-31.13185685148274</v>
       </c>
       <c r="D82">
-        <v>27.81757919351289</v>
+        <v>27.60212314851727</v>
       </c>
       <c r="E82">
-        <v>58.94840000000001</v>
+        <v>59.68598000000001</v>
       </c>
       <c r="F82">
-        <v>59.00640000000001</v>
+        <v>59.74398000000001</v>
       </c>
       <c r="G82">
         <v>1.01</v>
@@ -8249,37 +8249,37 @@
         <v>0.397</v>
       </c>
       <c r="M82">
-        <v>13.91370912</v>
+        <v>14.087630484</v>
       </c>
       <c r="N82">
-        <v>-13.51670912</v>
+        <v>-13.690630484</v>
       </c>
       <c r="O82">
-        <v>-2.973676006400001</v>
+        <v>-3.011938706480001</v>
       </c>
       <c r="P82">
-        <v>-10.5430331136</v>
+        <v>-10.67869177752</v>
       </c>
       <c r="Q82">
-        <v>-10.4290331136</v>
+        <v>-10.56469177752</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5087678841011762</v>
+        <v>0.5331346148433435</v>
       </c>
       <c r="T82">
-        <v>6.736746822882052</v>
+        <v>7.091312445139001</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.006277262176945667</v>
+        <v>0.006199765113032758</v>
       </c>
       <c r="W82">
-        <v>0.2343198215786762</v>
+        <v>0.2343380953863469</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.02853300989520757</v>
+        <v>0.02818075051378532</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8295,22 +8295,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2911094340831762</v>
+        <v>0.2930094340831762</v>
       </c>
       <c r="C83">
-        <v>-31.13185685148274</v>
+        <v>-32.08158099629129</v>
       </c>
       <c r="D83">
-        <v>27.60212314851727</v>
+        <v>27.38997900370872</v>
       </c>
       <c r="E83">
-        <v>59.68598000000001</v>
+        <v>60.42356000000002</v>
       </c>
       <c r="F83">
-        <v>59.74398000000001</v>
+        <v>60.48156000000002</v>
       </c>
       <c r="G83">
         <v>1.01</v>
@@ -8331,37 +8331,37 @@
         <v>0.397</v>
       </c>
       <c r="M83">
-        <v>14.087630484</v>
+        <v>14.26155184800001</v>
       </c>
       <c r="N83">
-        <v>-13.690630484</v>
+        <v>-13.864551848</v>
       </c>
       <c r="O83">
-        <v>-3.011938706480001</v>
+        <v>-3.050201406560001</v>
       </c>
       <c r="P83">
-        <v>-10.67869177752</v>
+        <v>-10.81435044144</v>
       </c>
       <c r="Q83">
-        <v>-10.56469177752</v>
+        <v>-10.70035044144</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5331346148433435</v>
+        <v>0.560208760112418</v>
       </c>
       <c r="T83">
-        <v>7.091312445139001</v>
+        <v>7.485274247646724</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.006199765113032758</v>
+        <v>0.006124158221410406</v>
       </c>
       <c r="W83">
-        <v>0.2343380953863469</v>
+        <v>0.2343559234913914</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.02818075051378532</v>
+        <v>0.02783708282459274</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8377,22 +8377,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2930094340831762</v>
+        <v>0.2949094340831762</v>
       </c>
       <c r="C84">
-        <v>-32.08158099629129</v>
+        <v>-33.02806902218994</v>
       </c>
       <c r="D84">
-        <v>27.38997900370872</v>
+        <v>27.18107097781007</v>
       </c>
       <c r="E84">
-        <v>60.42356000000002</v>
+        <v>61.16114000000001</v>
       </c>
       <c r="F84">
-        <v>60.48156000000002</v>
+        <v>61.21914000000001</v>
       </c>
       <c r="G84">
         <v>1.01</v>
@@ -8413,37 +8413,37 @@
         <v>0.397</v>
       </c>
       <c r="M84">
-        <v>14.26155184800001</v>
+        <v>14.435473212</v>
       </c>
       <c r="N84">
-        <v>-13.864551848</v>
+        <v>-14.038473212</v>
       </c>
       <c r="O84">
-        <v>-3.050201406560001</v>
+        <v>-3.08846410664</v>
       </c>
       <c r="P84">
-        <v>-10.81435044144</v>
+        <v>-10.95000910536</v>
       </c>
       <c r="Q84">
-        <v>-10.70035044144</v>
+        <v>-10.83600910536</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.560208760112418</v>
+        <v>0.5904680989425604</v>
       </c>
       <c r="T84">
-        <v>7.485274247646724</v>
+        <v>7.925584497508297</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.006124158221410406</v>
+        <v>0.006050373182598233</v>
       </c>
       <c r="W84">
-        <v>0.2343559234913914</v>
+        <v>0.2343733220035433</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.02783708282459274</v>
+        <v>0.02750169628453747</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8459,22 +8459,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2949094340831762</v>
+        <v>0.2968094340831762</v>
       </c>
       <c r="C85">
-        <v>-33.02806902218994</v>
+        <v>-33.97139441596954</v>
       </c>
       <c r="D85">
-        <v>27.18107097781007</v>
+        <v>26.97532558403046</v>
       </c>
       <c r="E85">
-        <v>61.16114000000001</v>
+        <v>61.89872000000001</v>
       </c>
       <c r="F85">
-        <v>61.21914000000001</v>
+        <v>61.95672000000001</v>
       </c>
       <c r="G85">
         <v>1.01</v>
@@ -8495,37 +8495,37 @@
         <v>0.397</v>
       </c>
       <c r="M85">
-        <v>14.435473212</v>
+        <v>14.609394576</v>
       </c>
       <c r="N85">
-        <v>-14.038473212</v>
+        <v>-14.212394576</v>
       </c>
       <c r="O85">
-        <v>-3.08846410664</v>
+        <v>-3.126726806720001</v>
       </c>
       <c r="P85">
-        <v>-10.95000910536</v>
+        <v>-11.08566776928</v>
       </c>
       <c r="Q85">
-        <v>-10.83600910536</v>
+        <v>-10.97166776928</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5904680989425604</v>
+        <v>0.6245098551264704</v>
       </c>
       <c r="T85">
-        <v>7.925584497508297</v>
+        <v>8.420933528602566</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.006050373182598233</v>
+        <v>0.005978344930424446</v>
       </c>
       <c r="W85">
-        <v>0.2343733220035433</v>
+        <v>0.2343903062654059</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.02750169628453747</v>
+        <v>0.02717429513829295</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8541,22 +8541,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2968094340831762</v>
+        <v>0.2987094340831762</v>
       </c>
       <c r="C86">
-        <v>-33.97139441596954</v>
+        <v>-34.91162845612212</v>
       </c>
       <c r="D86">
-        <v>26.97532558403046</v>
+        <v>26.77267154387788</v>
       </c>
       <c r="E86">
-        <v>61.89872</v>
+        <v>62.63630000000001</v>
       </c>
       <c r="F86">
-        <v>61.95672</v>
+        <v>62.69430000000001</v>
       </c>
       <c r="G86">
         <v>1.01</v>
@@ -8577,37 +8577,37 @@
         <v>0.397</v>
       </c>
       <c r="M86">
-        <v>14.609394576</v>
+        <v>14.78331594</v>
       </c>
       <c r="N86">
-        <v>-14.212394576</v>
+        <v>-14.38631594</v>
       </c>
       <c r="O86">
-        <v>-3.12672680672</v>
+        <v>-3.1649895068</v>
       </c>
       <c r="P86">
-        <v>-11.08566776928</v>
+        <v>-11.2213264332</v>
       </c>
       <c r="Q86">
-        <v>-10.97166776928</v>
+        <v>-11.1073264332</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6245098551264701</v>
+        <v>0.6630905121349013</v>
       </c>
       <c r="T86">
-        <v>8.420933528602561</v>
+        <v>8.982329097176065</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.005978344930424446</v>
+        <v>0.005908011460654746</v>
       </c>
       <c r="W86">
-        <v>0.2343903062654059</v>
+        <v>0.2344068908975776</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.02717429513829295</v>
+        <v>0.02685459754843067</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8623,22 +8623,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2987094340831762</v>
+        <v>0.3006094340831762</v>
       </c>
       <c r="C87">
-        <v>-34.91162845612212</v>
+        <v>-35.84884029517233</v>
       </c>
       <c r="D87">
-        <v>26.77267154387788</v>
+        <v>26.57303970482767</v>
       </c>
       <c r="E87">
-        <v>62.63630000000001</v>
+        <v>63.37388000000001</v>
       </c>
       <c r="F87">
-        <v>62.69430000000001</v>
+        <v>63.43188000000001</v>
       </c>
       <c r="G87">
         <v>1.01</v>
@@ -8659,37 +8659,37 @@
         <v>0.397</v>
       </c>
       <c r="M87">
-        <v>14.78331594</v>
+        <v>14.957237304</v>
       </c>
       <c r="N87">
-        <v>-14.38631594</v>
+        <v>-14.560237304</v>
       </c>
       <c r="O87">
-        <v>-3.1649895068</v>
+        <v>-3.203252206880001</v>
       </c>
       <c r="P87">
-        <v>-11.2213264332</v>
+        <v>-11.35698509712</v>
       </c>
       <c r="Q87">
-        <v>-11.1073264332</v>
+        <v>-11.24298509712</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6630905121349013</v>
+        <v>0.7071826915731086</v>
       </c>
       <c r="T87">
-        <v>8.982329097176065</v>
+        <v>9.623924032688642</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.005908011460654746</v>
+        <v>0.005839313652972714</v>
       </c>
       <c r="W87">
-        <v>0.2344068908975776</v>
+        <v>0.234423089840629</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.02685459754843067</v>
+        <v>0.02654233478623957</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8705,22 +8705,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3006094340831762</v>
+        <v>0.3025094340831762</v>
       </c>
       <c r="C88">
-        <v>-35.84884029517233</v>
+        <v>-36.78309703835278</v>
       </c>
       <c r="D88">
-        <v>26.57303970482767</v>
+        <v>26.37636296164724</v>
       </c>
       <c r="E88">
-        <v>63.37388000000001</v>
+        <v>64.11146000000001</v>
       </c>
       <c r="F88">
-        <v>63.43188000000001</v>
+        <v>64.16946000000002</v>
       </c>
       <c r="G88">
         <v>1.01</v>
@@ -8741,37 +8741,37 @@
         <v>0.397</v>
       </c>
       <c r="M88">
-        <v>14.957237304</v>
+        <v>15.131158668</v>
       </c>
       <c r="N88">
-        <v>-14.560237304</v>
+        <v>-14.734158668</v>
       </c>
       <c r="O88">
-        <v>-3.203252206880001</v>
+        <v>-3.241514906960001</v>
       </c>
       <c r="P88">
-        <v>-11.35698509712</v>
+        <v>-11.49264376104</v>
       </c>
       <c r="Q88">
-        <v>-11.24298509712</v>
+        <v>-11.37864376104</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7071826915731086</v>
+        <v>0.7580582832325786</v>
       </c>
       <c r="T88">
-        <v>9.623924032688642</v>
+        <v>10.364225881357</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.005839313652972714</v>
+        <v>0.005772195105237394</v>
       </c>
       <c r="W88">
-        <v>0.234423089840629</v>
+        <v>0.234438916394185</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.02654233478623957</v>
+        <v>0.02623725047835179</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8787,22 +8787,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3025094340831762</v>
+        <v>0.3044094340831762</v>
       </c>
       <c r="C89">
-        <v>-36.78309703835278</v>
+        <v>-37.7144638188111</v>
       </c>
       <c r="D89">
-        <v>26.37636296164724</v>
+        <v>26.1825761811889</v>
       </c>
       <c r="E89">
-        <v>64.11146000000001</v>
+        <v>64.84904</v>
       </c>
       <c r="F89">
-        <v>64.16946000000002</v>
+        <v>64.90704000000001</v>
       </c>
       <c r="G89">
         <v>1.01</v>
@@ -8823,37 +8823,37 @@
         <v>0.397</v>
       </c>
       <c r="M89">
-        <v>15.131158668</v>
+        <v>15.305080032</v>
       </c>
       <c r="N89">
-        <v>-14.734158668</v>
+        <v>-14.908080032</v>
       </c>
       <c r="O89">
-        <v>-3.241514906960001</v>
+        <v>-3.279777607040001</v>
       </c>
       <c r="P89">
-        <v>-11.49264376104</v>
+        <v>-11.62830242496</v>
       </c>
       <c r="Q89">
-        <v>-11.37864376104</v>
+        <v>-11.51430242496</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7580582832325786</v>
+        <v>0.817413140168627</v>
       </c>
       <c r="T89">
-        <v>10.364225881357</v>
+        <v>11.22791137147008</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.005772195105237394</v>
+        <v>0.005706601979041516</v>
       </c>
       <c r="W89">
-        <v>0.234438916394185</v>
+        <v>0.234454383253342</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.02623725047835179</v>
+        <v>0.0259390999047342</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8869,22 +8869,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3044094340831762</v>
+        <v>0.3063094340831762</v>
       </c>
       <c r="C90">
-        <v>-37.7144638188111</v>
+        <v>-38.6430038695261</v>
       </c>
       <c r="D90">
-        <v>26.1825761811889</v>
+        <v>25.9916161304739</v>
       </c>
       <c r="E90">
-        <v>64.84904</v>
+        <v>65.58662</v>
       </c>
       <c r="F90">
-        <v>64.90704000000001</v>
+        <v>65.64462</v>
       </c>
       <c r="G90">
         <v>1.01</v>
@@ -8905,37 +8905,37 @@
         <v>0.397</v>
       </c>
       <c r="M90">
-        <v>15.305080032</v>
+        <v>15.479001396</v>
       </c>
       <c r="N90">
-        <v>-14.908080032</v>
+        <v>-15.082001396</v>
       </c>
       <c r="O90">
-        <v>-3.279777607040001</v>
+        <v>-3.31804030712</v>
       </c>
       <c r="P90">
-        <v>-11.62830242496</v>
+        <v>-11.76396108888</v>
       </c>
       <c r="Q90">
-        <v>-11.51430242496</v>
+        <v>-11.64996108888</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.817413140168627</v>
+        <v>0.8875597892748658</v>
       </c>
       <c r="T90">
-        <v>11.22791137147008</v>
+        <v>12.24863058705827</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.005706601979041516</v>
+        <v>0.005642482855681499</v>
       </c>
       <c r="W90">
-        <v>0.234454383253342</v>
+        <v>0.2344695025426303</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.0259390999047342</v>
+        <v>0.02564764934400687</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8951,22 +8951,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3063094340831762</v>
+        <v>0.3082094340831762</v>
       </c>
       <c r="C91">
-        <v>-38.6430038695261</v>
+        <v>-39.56877859209941</v>
       </c>
       <c r="D91">
-        <v>25.9916161304739</v>
+        <v>25.8034214079006</v>
       </c>
       <c r="E91">
-        <v>65.58662</v>
+        <v>66.3242</v>
       </c>
       <c r="F91">
-        <v>65.64462</v>
+        <v>66.38220000000001</v>
       </c>
       <c r="G91">
         <v>1.01</v>
@@ -8987,37 +8987,37 @@
         <v>0.397</v>
       </c>
       <c r="M91">
-        <v>15.479001396</v>
+        <v>15.65292276</v>
       </c>
       <c r="N91">
-        <v>-15.082001396</v>
+        <v>-15.25592276</v>
       </c>
       <c r="O91">
-        <v>-3.31804030712</v>
+        <v>-3.356303007200001</v>
       </c>
       <c r="P91">
-        <v>-11.76396108888</v>
+        <v>-11.8996197528</v>
       </c>
       <c r="Q91">
-        <v>-11.64996108888</v>
+        <v>-11.7856197528</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8875597892748658</v>
+        <v>0.9717357682023525</v>
       </c>
       <c r="T91">
-        <v>12.24863058705827</v>
+        <v>13.4734936457641</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.005642482855681499</v>
+        <v>0.005579788601729483</v>
       </c>
       <c r="W91">
-        <v>0.2344695025426303</v>
+        <v>0.2344842858477122</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.02564764934400687</v>
+        <v>0.02536267546240678</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9033,22 +9033,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3082094340831762</v>
+        <v>0.3101094340831762</v>
       </c>
       <c r="C92">
-        <v>-39.56877859209941</v>
+        <v>-40.49184762258018</v>
       </c>
       <c r="D92">
-        <v>25.8034214079006</v>
+        <v>25.61793237741983</v>
       </c>
       <c r="E92">
-        <v>66.3242</v>
+        <v>67.06178</v>
       </c>
       <c r="F92">
-        <v>66.38220000000001</v>
+        <v>67.11978000000001</v>
       </c>
       <c r="G92">
         <v>1.01</v>
@@ -9069,37 +9069,37 @@
         <v>0.397</v>
       </c>
       <c r="M92">
-        <v>15.65292276</v>
+        <v>15.826844124</v>
       </c>
       <c r="N92">
-        <v>-15.25592276</v>
+        <v>-15.429844124</v>
       </c>
       <c r="O92">
-        <v>-3.356303007200001</v>
+        <v>-3.39456570728</v>
       </c>
       <c r="P92">
-        <v>-11.8996197528</v>
+        <v>-12.03527841672</v>
       </c>
       <c r="Q92">
-        <v>-11.7856197528</v>
+        <v>-11.92127841672</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9717357682023525</v>
+        <v>1.074617520224836</v>
       </c>
       <c r="T92">
-        <v>13.4734936457641</v>
+        <v>14.97054849529345</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.005579788601729483</v>
+        <v>0.005518472243468718</v>
       </c>
       <c r="W92">
-        <v>0.2344842858477122</v>
+        <v>0.2344987442449901</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.02536267546240678</v>
+        <v>0.02508396474303964</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9115,22 +9115,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3101094340831762</v>
+        <v>0.3120094340831762</v>
       </c>
       <c r="C93">
-        <v>-40.49184762258018</v>
+        <v>-41.41226889447098</v>
       </c>
       <c r="D93">
-        <v>25.61793237741983</v>
+        <v>25.43509110552903</v>
       </c>
       <c r="E93">
-        <v>67.06178</v>
+        <v>67.79936000000001</v>
       </c>
       <c r="F93">
-        <v>67.11978000000001</v>
+        <v>67.85736000000001</v>
       </c>
       <c r="G93">
         <v>1.01</v>
@@ -9151,37 +9151,37 @@
         <v>0.397</v>
       </c>
       <c r="M93">
-        <v>15.826844124</v>
+        <v>16.000765488</v>
       </c>
       <c r="N93">
-        <v>-15.429844124</v>
+        <v>-15.603765488</v>
       </c>
       <c r="O93">
-        <v>-3.39456570728</v>
+        <v>-3.432828407360001</v>
       </c>
       <c r="P93">
-        <v>-12.03527841672</v>
+        <v>-12.17093708064</v>
       </c>
       <c r="Q93">
-        <v>-11.92127841672</v>
+        <v>-12.05693708064</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.074617520224836</v>
+        <v>1.203219710252941</v>
       </c>
       <c r="T93">
-        <v>14.97054849529345</v>
+        <v>16.84186705720514</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.005518472243468718</v>
+        <v>0.005458488849517972</v>
       </c>
       <c r="W93">
-        <v>0.2344987442449901</v>
+        <v>0.2345128883292837</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.02508396474303964</v>
+        <v>0.02481131295235439</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9197,22 +9197,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3120094340831762</v>
+        <v>0.3139094340831762</v>
       </c>
       <c r="C94">
-        <v>-41.41226889447098</v>
+        <v>-42.33009869905456</v>
       </c>
       <c r="D94">
-        <v>25.43509110552903</v>
+        <v>25.25484130094545</v>
       </c>
       <c r="E94">
-        <v>67.79936000000001</v>
+        <v>68.53694</v>
       </c>
       <c r="F94">
-        <v>67.85736000000001</v>
+        <v>68.59494000000001</v>
       </c>
       <c r="G94">
         <v>1.01</v>
@@ -9233,37 +9233,37 @@
         <v>0.397</v>
       </c>
       <c r="M94">
-        <v>16.000765488</v>
+        <v>16.174686852</v>
       </c>
       <c r="N94">
-        <v>-15.603765488</v>
+        <v>-15.777686852</v>
       </c>
       <c r="O94">
-        <v>-3.432828407360001</v>
+        <v>-3.471091107440001</v>
       </c>
       <c r="P94">
-        <v>-12.17093708064</v>
+        <v>-12.30659574456</v>
       </c>
       <c r="Q94">
-        <v>-12.05693708064</v>
+        <v>-12.19259574456</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.203219710252941</v>
+        <v>1.368565383146219</v>
       </c>
       <c r="T94">
-        <v>16.84186705720514</v>
+        <v>19.2478480653773</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.005458488849517972</v>
+        <v>0.00539979542102853</v>
       </c>
       <c r="W94">
-        <v>0.2345128883292837</v>
+        <v>0.2345267282397215</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.02481131295235439</v>
+        <v>0.02454452464103885</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9279,22 +9279,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3139094340831762</v>
+        <v>0.3158094340831762</v>
       </c>
       <c r="C95">
-        <v>-42.33009869905456</v>
+        <v>-43.24539174317367</v>
       </c>
       <c r="D95">
-        <v>25.25484130094545</v>
+        <v>25.07712825682635</v>
       </c>
       <c r="E95">
-        <v>68.53694</v>
+        <v>69.27452000000001</v>
       </c>
       <c r="F95">
-        <v>68.59494000000001</v>
+        <v>69.33252000000002</v>
       </c>
       <c r="G95">
         <v>1.01</v>
@@ -9315,37 +9315,37 @@
         <v>0.397</v>
       </c>
       <c r="M95">
-        <v>16.174686852</v>
+        <v>16.34860821600001</v>
       </c>
       <c r="N95">
-        <v>-15.777686852</v>
+        <v>-15.95160821600001</v>
       </c>
       <c r="O95">
-        <v>-3.471091107440001</v>
+        <v>-3.509353807520001</v>
       </c>
       <c r="P95">
-        <v>-12.30659574456</v>
+        <v>-12.44225440848</v>
       </c>
       <c r="Q95">
-        <v>-12.19259574456</v>
+        <v>-12.32825440848</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.368565383146219</v>
+        <v>1.589026280337255</v>
       </c>
       <c r="T95">
-        <v>19.2478480653773</v>
+        <v>22.45582274294019</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.00539979542102853</v>
+        <v>0.005342350788889928</v>
       </c>
       <c r="W95">
-        <v>0.2345267282397215</v>
+        <v>0.2345402736839798</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.02454452464103885</v>
+        <v>0.02428341267677236</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9361,22 +9361,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3158094340831762</v>
+        <v>0.3177094340831762</v>
       </c>
       <c r="C96">
-        <v>-43.24539174317367</v>
+        <v>-44.15820120458835</v>
       </c>
       <c r="D96">
-        <v>25.07712825682635</v>
+        <v>24.90189879541166</v>
       </c>
       <c r="E96">
-        <v>69.27452000000001</v>
+        <v>70.0121</v>
       </c>
       <c r="F96">
-        <v>69.33252000000002</v>
+        <v>70.07010000000001</v>
       </c>
       <c r="G96">
         <v>1.01</v>
@@ -9397,37 +9397,37 @@
         <v>0.397</v>
       </c>
       <c r="M96">
-        <v>16.34860821600001</v>
+        <v>16.52252958</v>
       </c>
       <c r="N96">
-        <v>-15.95160821600001</v>
+        <v>-16.12552958000001</v>
       </c>
       <c r="O96">
-        <v>-3.509353807520001</v>
+        <v>-3.547616507600001</v>
       </c>
       <c r="P96">
-        <v>-12.44225440848</v>
+        <v>-12.5779130724</v>
       </c>
       <c r="Q96">
-        <v>-12.32825440848</v>
+        <v>-12.4639130724</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.589026280337255</v>
+        <v>1.897671536404707</v>
       </c>
       <c r="T96">
-        <v>22.45582274294019</v>
+        <v>26.94698729152823</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.005342350788889928</v>
+        <v>0.00528611551742793</v>
       </c>
       <c r="W96">
-        <v>0.2345402736839798</v>
+        <v>0.2345535339609905</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.02428341267677236</v>
+        <v>0.02402779780649045</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9443,22 +9443,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3177094340831762</v>
+        <v>0.3196094340831762</v>
       </c>
       <c r="C97">
-        <v>-44.15820120458835</v>
+        <v>-45.06857878502859</v>
       </c>
       <c r="D97">
-        <v>24.90189879541166</v>
+        <v>24.72910121497143</v>
       </c>
       <c r="E97">
-        <v>70.0121</v>
+        <v>70.74968000000001</v>
       </c>
       <c r="F97">
-        <v>70.07010000000001</v>
+        <v>70.80768000000002</v>
       </c>
       <c r="G97">
         <v>1.01</v>
@@ -9479,37 +9479,37 @@
         <v>0.397</v>
       </c>
       <c r="M97">
-        <v>16.52252958</v>
+        <v>16.69645094400001</v>
       </c>
       <c r="N97">
-        <v>-16.12552958000001</v>
+        <v>-16.29945094400001</v>
       </c>
       <c r="O97">
-        <v>-3.547616507600001</v>
+        <v>-3.585879207680001</v>
       </c>
       <c r="P97">
-        <v>-12.5779130724</v>
+        <v>-12.71357173632001</v>
       </c>
       <c r="Q97">
-        <v>-12.4639130724</v>
+        <v>-12.59957173632001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.897671536404707</v>
+        <v>2.360639420505885</v>
       </c>
       <c r="T97">
-        <v>26.94698729152823</v>
+        <v>33.68373411441031</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.00528611551742793</v>
+        <v>0.005231051814121389</v>
       </c>
       <c r="W97">
-        <v>0.2345535339609905</v>
+        <v>0.2345665179822302</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.02402779780649045</v>
+        <v>0.02377750824600622</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9525,22 +9525,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3196094340831762</v>
+        <v>0.3215094340831762</v>
       </c>
       <c r="C98">
-        <v>-45.06857878502858</v>
+        <v>-45.97657476105307</v>
       </c>
       <c r="D98">
-        <v>24.72910121497143</v>
+        <v>24.55868523894694</v>
       </c>
       <c r="E98">
-        <v>70.74968</v>
+        <v>71.48726000000001</v>
       </c>
       <c r="F98">
-        <v>70.80768</v>
+        <v>71.54526000000001</v>
       </c>
       <c r="G98">
         <v>1.01</v>
@@ -9561,37 +9561,37 @@
         <v>0.397</v>
       </c>
       <c r="M98">
-        <v>16.696450944</v>
+        <v>16.870372308</v>
       </c>
       <c r="N98">
-        <v>-16.299450944</v>
+        <v>-16.47337230800001</v>
       </c>
       <c r="O98">
-        <v>-3.585879207680001</v>
+        <v>-3.624141907760001</v>
       </c>
       <c r="P98">
-        <v>-12.71357173632</v>
+        <v>-12.84923040024</v>
       </c>
       <c r="Q98">
-        <v>-12.59957173632</v>
+        <v>-12.73523040024</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.360639420505878</v>
+        <v>3.132252560674505</v>
       </c>
       <c r="T98">
-        <v>33.68373411441022</v>
+        <v>44.91164548588029</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.005231051814121391</v>
+        <v>0.005177123444903643</v>
       </c>
       <c r="W98">
-        <v>0.2345665179822302</v>
+        <v>0.2345792342916917</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.02377750824600622</v>
+        <v>0.0235323792950165</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9607,22 +9607,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3215094340831762</v>
+        <v>0.3234094340831762</v>
       </c>
       <c r="C99">
-        <v>-45.97657476105307</v>
+        <v>-46.88223803281977</v>
       </c>
       <c r="D99">
-        <v>24.55868523894694</v>
+        <v>24.39060196718024</v>
       </c>
       <c r="E99">
-        <v>71.48726000000001</v>
+        <v>72.22484</v>
       </c>
       <c r="F99">
-        <v>71.54526000000001</v>
+        <v>72.28284000000001</v>
       </c>
       <c r="G99">
         <v>1.01</v>
@@ -9643,37 +9643,37 @@
         <v>0.397</v>
       </c>
       <c r="M99">
-        <v>16.870372308</v>
+        <v>17.044293672</v>
       </c>
       <c r="N99">
-        <v>-16.47337230800001</v>
+        <v>-16.647293672</v>
       </c>
       <c r="O99">
-        <v>-3.624141907760001</v>
+        <v>-3.662404607840001</v>
       </c>
       <c r="P99">
-        <v>-12.84923040024</v>
+        <v>-12.98488906416</v>
       </c>
       <c r="Q99">
-        <v>-12.73523040024</v>
+        <v>-12.87088906416</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.132252560674505</v>
+        <v>4.675478841011757</v>
       </c>
       <c r="T99">
-        <v>44.91164548588029</v>
+        <v>67.36746822882044</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.005177123444903643</v>
+        <v>0.005124295654649525</v>
       </c>
       <c r="W99">
-        <v>0.2345792342916917</v>
+        <v>0.2345916910846337</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.0235323792950165</v>
+        <v>0.02329225297567961</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9689,22 +9689,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3234094340831762</v>
+        <v>0.3253094340831761</v>
       </c>
       <c r="C100">
-        <v>-46.88223803281977</v>
+        <v>-47.78561617086706</v>
       </c>
       <c r="D100">
-        <v>24.39060196718024</v>
+        <v>24.22480382913296</v>
       </c>
       <c r="E100">
-        <v>72.22484</v>
+        <v>72.96242000000001</v>
       </c>
       <c r="F100">
-        <v>72.28284000000001</v>
+        <v>73.02042000000002</v>
       </c>
       <c r="G100">
         <v>1.01</v>
@@ -9725,37 +9725,37 @@
         <v>0.397</v>
       </c>
       <c r="M100">
-        <v>17.044293672</v>
+        <v>17.218215036</v>
       </c>
       <c r="N100">
-        <v>-16.647293672</v>
+        <v>-16.82121503600001</v>
       </c>
       <c r="O100">
-        <v>-3.662404607840001</v>
+        <v>-3.700667307920001</v>
       </c>
       <c r="P100">
-        <v>-12.98488906416</v>
+        <v>-13.12054772808</v>
       </c>
       <c r="Q100">
-        <v>-12.87088906416</v>
+        <v>-13.00654772808</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.675478841011757</v>
+        <v>9.305157682023513</v>
       </c>
       <c r="T100">
-        <v>67.36746822882044</v>
+        <v>134.7349364576409</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.005124295654649525</v>
+        <v>0.005072535092481348</v>
       </c>
       <c r="W100">
-        <v>0.2345916910846337</v>
+        <v>0.2346038962251929</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9763,91 +9763,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.02329225297567961</v>
+        <v>0.02305697769309689</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3253094340831761</v>
-      </c>
-      <c r="C101">
-        <v>-47.78561617086706</v>
-      </c>
-      <c r="D101">
-        <v>24.22480382913296</v>
-      </c>
-      <c r="E101">
-        <v>72.96242000000001</v>
-      </c>
-      <c r="F101">
-        <v>73.02042000000002</v>
-      </c>
-      <c r="G101">
-        <v>1.01</v>
-      </c>
-      <c r="H101">
-        <v>73.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.511</v>
-      </c>
-      <c r="K101">
-        <v>0.114</v>
-      </c>
-      <c r="L101">
-        <v>0.397</v>
-      </c>
-      <c r="M101">
-        <v>17.218215036</v>
-      </c>
-      <c r="N101">
-        <v>-16.82121503600001</v>
-      </c>
-      <c r="O101">
-        <v>-3.700667307920001</v>
-      </c>
-      <c r="P101">
-        <v>-13.12054772808</v>
-      </c>
-      <c r="Q101">
-        <v>-13.00654772808</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.305157682023513</v>
-      </c>
-      <c r="T101">
-        <v>134.7349364576409</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.005072535092481348</v>
-      </c>
-      <c r="W101">
-        <v>0.2346038962251929</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.02305697769309689</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
